--- a/data/teams/leagues/Averages_Sweden_Allsvenskan_2026.xlsx
+++ b/data/teams/leagues/Averages_Sweden_Allsvenskan_2026.xlsx
@@ -137,8 +137,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AveragesTable_Sweden_All" displayName="AveragesTable_Sweden_All" ref="A1:CZ11" headerRowCount="1">
-  <autoFilter ref="A1:CZ11"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AveragesTable_Sweden_All" displayName="AveragesTable_Sweden_All" ref="A1:CZ17" headerRowCount="1">
+  <autoFilter ref="A1:CZ17"/>
   <tableColumns count="104">
     <tableColumn id="1" name="team_name"/>
     <tableColumn id="2" name="total_games"/>
@@ -538,10 +538,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CZ11"/>
+  <dimension ref="A1:CZ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15.6" customWidth="1" min="1" max="1"/>
+    <col width="19.2" customWidth="1" min="1" max="1"/>
     <col width="15.6" customWidth="1" min="2" max="2"/>
     <col width="14.4" customWidth="1" min="3" max="3"/>
     <col width="14.4" customWidth="1" min="4" max="4"/>
@@ -1430,158 +1430,158 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr"/>
+      <c r="AF3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>56</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL3" t="n">
         <v>3</v>
       </c>
-      <c r="H3" t="n">
-        <v>93</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K3" t="n">
-        <v>6</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>49</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
+      <c r="AM3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>37</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP3" t="n">
         <v>3</v>
       </c>
-      <c r="P3" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>11</v>
-      </c>
-      <c r="R3" t="n">
-        <v>10</v>
-      </c>
-      <c r="S3" t="n">
+      <c r="AQ3" t="n">
+        <v>17</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>13</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>7</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>39</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB3" t="n">
         <v>3</v>
       </c>
-      <c r="T3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X3" t="n">
-        <v>47</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>6</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>24</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF3" t="inlineStr"/>
-      <c r="AG3" t="inlineStr"/>
-      <c r="AH3" t="inlineStr"/>
-      <c r="AI3" t="inlineStr"/>
-      <c r="AJ3" t="inlineStr"/>
-      <c r="AK3" t="inlineStr"/>
-      <c r="AL3" t="inlineStr"/>
-      <c r="AM3" t="inlineStr"/>
-      <c r="AN3" t="inlineStr"/>
-      <c r="AO3" t="inlineStr"/>
-      <c r="AP3" t="inlineStr"/>
-      <c r="AQ3" t="inlineStr"/>
-      <c r="AR3" t="inlineStr"/>
-      <c r="AS3" t="inlineStr"/>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AU3" t="inlineStr"/>
-      <c r="AV3" t="inlineStr"/>
-      <c r="AW3" t="inlineStr"/>
-      <c r="AX3" t="inlineStr"/>
-      <c r="AY3" t="inlineStr"/>
-      <c r="AZ3" t="inlineStr"/>
-      <c r="BA3" t="inlineStr"/>
-      <c r="BB3" t="inlineStr"/>
-      <c r="BC3" t="inlineStr"/>
-      <c r="BD3" t="inlineStr"/>
-      <c r="BE3" t="inlineStr"/>
-      <c r="BF3" t="inlineStr"/>
+      <c r="BC3" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>19</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>1</v>
+      </c>
       <c r="BG3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BH3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BI3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BJ3" t="n">
         <v>0</v>
       </c>
       <c r="BK3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BL3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BM3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BN3" t="n">
         <v>3</v>
       </c>
       <c r="BO3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BR3" t="n">
         <v>100</v>
@@ -1593,7 +1593,7 @@
         <v>100</v>
       </c>
       <c r="BU3" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="BV3" t="n">
         <v>0</v>
@@ -1602,236 +1602,236 @@
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY3" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="BZ3" t="n">
-        <v>3.6</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="BY3" t="inlineStr"/>
+      <c r="BZ3" t="inlineStr"/>
       <c r="CA3" t="n">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.43</v>
-      </c>
-      <c r="CC3" t="inlineStr"/>
-      <c r="CD3" t="inlineStr"/>
+        <v>4.1</v>
+      </c>
+      <c r="CC3" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="CD3" t="n">
+        <v>4.67</v>
+      </c>
       <c r="CE3" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.73</v>
+        <v>2.35</v>
       </c>
       <c r="CG3" t="n">
-        <v>3.13</v>
+        <v>3.34</v>
       </c>
       <c r="CH3" t="n">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="CI3" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="CL3" t="n">
-        <v>1.49</v>
+        <v>1.43</v>
       </c>
       <c r="CM3" t="n">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="CN3" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="CO3" t="n">
-        <v>1.28</v>
+        <v>1.17</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.91</v>
+        <v>1.56</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.2</v>
+        <v>2.12</v>
       </c>
       <c r="CR3" t="inlineStr"/>
-      <c r="CS3" t="inlineStr"/>
+      <c r="CS3" t="n">
+        <v>2.49</v>
+      </c>
       <c r="CT3" t="inlineStr"/>
-      <c r="CU3" t="inlineStr"/>
-      <c r="CV3" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="CW3" t="n">
-        <v>2.52</v>
-      </c>
+      <c r="CU3" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="CV3" t="inlineStr"/>
+      <c r="CW3" t="inlineStr"/>
       <c r="CX3" t="n">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="CY3" t="n">
-        <v>1.92</v>
+        <v>1.66</v>
       </c>
       <c r="CZ3" t="n">
-        <v>3.14</v>
+        <v>2.62</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="inlineStr"/>
-      <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="inlineStr"/>
-      <c r="AD4" t="inlineStr"/>
-      <c r="AE4" t="inlineStr"/>
-      <c r="AF4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>80</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
         <v>3</v>
       </c>
-      <c r="AM4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>33</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>14</v>
-      </c>
-      <c r="AR4" t="n">
+      <c r="H4" t="n">
+        <v>93</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>6</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>49</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>3</v>
+      </c>
+      <c r="P4" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q4" t="n">
         <v>11</v>
       </c>
-      <c r="AS4" t="n">
+      <c r="R4" t="n">
         <v>10</v>
       </c>
-      <c r="AT4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>44</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>11</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>4</v>
-      </c>
-      <c r="BC4" t="n">
+      <c r="S4" t="n">
+        <v>3</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>47</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
         <v>7</v>
       </c>
-      <c r="BD4" t="n">
-        <v>13</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>1</v>
-      </c>
+      <c r="AA4" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>24</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr"/>
+      <c r="AJ4" t="inlineStr"/>
+      <c r="AK4" t="inlineStr"/>
+      <c r="AL4" t="inlineStr"/>
+      <c r="AM4" t="inlineStr"/>
+      <c r="AN4" t="inlineStr"/>
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr"/>
+      <c r="AQ4" t="inlineStr"/>
+      <c r="AR4" t="inlineStr"/>
+      <c r="AS4" t="inlineStr"/>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AU4" t="inlineStr"/>
+      <c r="AV4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr"/>
+      <c r="AX4" t="inlineStr"/>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr"/>
+      <c r="BA4" t="inlineStr"/>
+      <c r="BB4" t="inlineStr"/>
+      <c r="BC4" t="inlineStr"/>
+      <c r="BD4" t="inlineStr"/>
+      <c r="BE4" t="inlineStr"/>
+      <c r="BF4" t="inlineStr"/>
       <c r="BG4" t="n">
         <v>3</v>
       </c>
       <c r="BH4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="BI4" t="n">
         <v>3</v>
       </c>
       <c r="BJ4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BK4" t="n">
         <v>0</v>
       </c>
       <c r="BL4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BM4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BN4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BO4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP4" t="n">
+        <v>6</v>
+      </c>
+      <c r="BQ4" t="n">
         <v>4</v>
-      </c>
-      <c r="BQ4" t="n">
-        <v>1</v>
       </c>
       <c r="BR4" t="n">
         <v>100</v>
@@ -1852,253 +1852,245 @@
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>100</v>
-      </c>
-      <c r="BY4" t="inlineStr"/>
-      <c r="BZ4" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="BY4" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="BZ4" t="n">
+        <v>3.6</v>
+      </c>
       <c r="CA4" t="n">
-        <v>4.1</v>
+        <v>3.3</v>
       </c>
       <c r="CB4" t="n">
-        <v>4.21</v>
-      </c>
-      <c r="CC4" t="n">
-        <v>5.81</v>
-      </c>
-      <c r="CD4" t="n">
-        <v>5.43</v>
-      </c>
+        <v>3.43</v>
+      </c>
+      <c r="CC4" t="inlineStr"/>
+      <c r="CD4" t="inlineStr"/>
       <c r="CE4" t="n">
         <v>1.38</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.62</v>
+        <v>2.73</v>
       </c>
       <c r="CG4" t="n">
-        <v>2.98</v>
+        <v>3.13</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="CI4" t="n">
-        <v>1.71</v>
+        <v>2.14</v>
       </c>
       <c r="CJ4" t="n">
-        <v>1.98</v>
+        <v>1.7</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.37</v>
+        <v>1.29</v>
       </c>
       <c r="CL4" t="n">
-        <v>1.63</v>
+        <v>1.49</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.63</v>
+        <v>3.2</v>
       </c>
       <c r="CN4" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="CO4" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="CQ4" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="CR4" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="CS4" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="CT4" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="CU4" t="n">
-        <v>1.39</v>
-      </c>
+        <v>3.2</v>
+      </c>
+      <c r="CR4" t="inlineStr"/>
+      <c r="CS4" t="inlineStr"/>
+      <c r="CT4" t="inlineStr"/>
+      <c r="CU4" t="inlineStr"/>
       <c r="CV4" t="n">
-        <v>1.71</v>
+        <v>1.49</v>
       </c>
       <c r="CW4" t="n">
-        <v>2.06</v>
+        <v>2.52</v>
       </c>
       <c r="CX4" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="CY4" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="CZ4" t="n">
-        <v>3.41</v>
+        <v>3.14</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" t="n">
-        <v>105</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>2</v>
-      </c>
-      <c r="K5" t="n">
-        <v>2</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1</v>
-      </c>
-      <c r="M5" t="n">
-        <v>46</v>
-      </c>
-      <c r="N5" t="n">
-        <v>2</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1</v>
-      </c>
-      <c r="P5" t="n">
-        <v>17</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>16</v>
-      </c>
-      <c r="R5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>7</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>107</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>10</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>53</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS5" t="n">
         <v>8</v>
       </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" t="n">
-        <v>3</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="n">
-        <v>53</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>15</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>10</v>
-      </c>
-      <c r="AB5" t="n">
+      <c r="AT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>48</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>12</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC5" t="n">
         <v>5</v>
       </c>
-      <c r="AC5" t="n">
-        <v>11</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF5" t="inlineStr"/>
-      <c r="AG5" t="inlineStr"/>
-      <c r="AH5" t="inlineStr"/>
-      <c r="AI5" t="inlineStr"/>
-      <c r="AJ5" t="inlineStr"/>
-      <c r="AK5" t="inlineStr"/>
-      <c r="AL5" t="inlineStr"/>
-      <c r="AM5" t="inlineStr"/>
-      <c r="AN5" t="inlineStr"/>
-      <c r="AO5" t="inlineStr"/>
-      <c r="AP5" t="inlineStr"/>
-      <c r="AQ5" t="inlineStr"/>
-      <c r="AR5" t="inlineStr"/>
-      <c r="AS5" t="inlineStr"/>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AU5" t="inlineStr"/>
-      <c r="AV5" t="inlineStr"/>
-      <c r="AW5" t="inlineStr"/>
-      <c r="AX5" t="inlineStr"/>
-      <c r="AY5" t="inlineStr"/>
-      <c r="AZ5" t="inlineStr"/>
-      <c r="BA5" t="inlineStr"/>
-      <c r="BB5" t="inlineStr"/>
-      <c r="BC5" t="inlineStr"/>
-      <c r="BD5" t="inlineStr"/>
-      <c r="BE5" t="inlineStr"/>
-      <c r="BF5" t="inlineStr"/>
+      <c r="BD5" t="n">
+        <v>25</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>1</v>
+      </c>
       <c r="BG5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BH5" t="n">
+        <v>12</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP5" t="n">
         <v>5</v>
       </c>
-      <c r="BI5" t="n">
-        <v>3</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>2</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>1</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>1</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>2</v>
-      </c>
-      <c r="BP5" t="n">
-        <v>2</v>
-      </c>
       <c r="BQ5" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="BR5" t="n">
         <v>100</v>
       </c>
       <c r="BS5" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="BT5" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="BU5" t="n">
         <v>0</v>
@@ -2112,83 +2104,91 @@
       <c r="BX5" t="n">
         <v>0</v>
       </c>
-      <c r="BY5" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="BZ5" t="n">
-        <v>2.05</v>
-      </c>
+      <c r="BY5" t="inlineStr"/>
+      <c r="BZ5" t="inlineStr"/>
       <c r="CA5" t="n">
-        <v>3.48</v>
+        <v>3.14</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.51</v>
-      </c>
-      <c r="CC5" t="inlineStr"/>
-      <c r="CD5" t="inlineStr"/>
+        <v>3.24</v>
+      </c>
+      <c r="CC5" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="CD5" t="n">
+        <v>3.62</v>
+      </c>
       <c r="CE5" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="CF5" t="n">
         <v>2.65</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.89</v>
+        <v>2.81</v>
       </c>
       <c r="CH5" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CI5" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="CJ5" t="n">
         <v>1.65</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.39</v>
+        <v>1.31</v>
       </c>
       <c r="CL5" t="n">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.75</v>
+        <v>2.87</v>
       </c>
       <c r="CN5" t="n">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="CO5" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="CP5" t="n">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="CQ5" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="CR5" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="CS5" t="n">
         <v>3.1</v>
       </c>
-      <c r="CR5" t="inlineStr"/>
-      <c r="CS5" t="inlineStr"/>
-      <c r="CT5" t="inlineStr"/>
-      <c r="CU5" t="inlineStr"/>
+      <c r="CT5" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="CU5" t="n">
+        <v>1.38</v>
+      </c>
       <c r="CV5" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="CW5" t="n">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="CX5" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="CY5" t="n">
-        <v>1.89</v>
+        <v>2.06</v>
       </c>
       <c r="CZ5" t="n">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -2207,10 +2207,10 @@
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -2219,10 +2219,10 @@
         <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
         <v>47</v>
@@ -2231,52 +2231,52 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P6" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q6" t="n">
         <v>7</v>
       </c>
-      <c r="P6" t="n">
+      <c r="R6" t="n">
+        <v>11</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>40</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
         <v>15</v>
       </c>
-      <c r="Q6" t="n">
-        <v>20</v>
-      </c>
-      <c r="R6" t="n">
-        <v>6</v>
-      </c>
-      <c r="S6" t="n">
-        <v>1</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" t="n">
-        <v>0</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" t="n">
-        <v>59</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>16</v>
-      </c>
       <c r="AA6" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AB6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AC6" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.56</v>
+        <v>1.63</v>
       </c>
       <c r="AE6" t="n">
         <v>1</v>
@@ -2309,43 +2309,43 @@
       <c r="BE6" t="inlineStr"/>
       <c r="BF6" t="inlineStr"/>
       <c r="BG6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BH6" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="BI6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BJ6" t="n">
         <v>0</v>
       </c>
       <c r="BK6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BL6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BM6" t="n">
         <v>0</v>
       </c>
       <c r="BN6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BO6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP6" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="BQ6" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="BR6" t="n">
         <v>100</v>
       </c>
       <c r="BS6" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="BT6" t="n">
         <v>0</v>
@@ -2363,243 +2363,239 @@
         <v>0</v>
       </c>
       <c r="BY6" t="n">
-        <v>2.12</v>
+        <v>2.37</v>
       </c>
       <c r="BZ6" t="n">
-        <v>2.14</v>
+        <v>2.26</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.35</v>
+        <v>3.16</v>
       </c>
       <c r="CC6" t="inlineStr"/>
       <c r="CD6" t="inlineStr"/>
       <c r="CE6" t="n">
-        <v>1.44</v>
+        <v>1.34</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.75</v>
+        <v>2.56</v>
       </c>
       <c r="CG6" t="n">
-        <v>2.5</v>
+        <v>3.35</v>
       </c>
       <c r="CH6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="CI6" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="CJ6" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="CK6" t="n">
         <v>1.39</v>
       </c>
-      <c r="CI6" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="CJ6" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="CK6" t="n">
-        <v>1.34</v>
-      </c>
       <c r="CL6" t="n">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.97</v>
+        <v>2.95</v>
       </c>
       <c r="CN6" t="n">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="CO6" t="n">
-        <v>1.4</v>
+        <v>1.19</v>
       </c>
       <c r="CP6" t="n">
-        <v>2.15</v>
+        <v>1.8</v>
       </c>
       <c r="CQ6" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="CR6" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="CS6" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="CT6" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="CU6" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="CV6" t="inlineStr"/>
-      <c r="CW6" t="inlineStr"/>
+        <v>2.76</v>
+      </c>
+      <c r="CR6" t="inlineStr"/>
+      <c r="CS6" t="inlineStr"/>
+      <c r="CT6" t="inlineStr"/>
+      <c r="CU6" t="inlineStr"/>
+      <c r="CV6" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="CW6" t="n">
+        <v>2.27</v>
+      </c>
       <c r="CX6" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="CY6" t="n">
-        <v>1.98</v>
+        <v>2.17</v>
       </c>
       <c r="CZ6" t="n">
-        <v>3.39</v>
+        <v>3.81</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
-      <c r="AA7" t="inlineStr"/>
-      <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="inlineStr"/>
-      <c r="AD7" t="inlineStr"/>
-      <c r="AE7" t="inlineStr"/>
-      <c r="AF7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>118</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2</v>
+      </c>
+      <c r="K7" t="n">
+        <v>2</v>
+      </c>
+      <c r="L7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M7" t="n">
+        <v>54</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1</v>
+      </c>
+      <c r="O7" t="n">
+        <v>2</v>
+      </c>
+      <c r="P7" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>7</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>52</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA7" t="n">
         <v>5</v>
       </c>
-      <c r="AI7" t="n">
-        <v>108</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>4</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>10</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>48</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP7" t="n">
+      <c r="AB7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>21</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="inlineStr"/>
+      <c r="AI7" t="inlineStr"/>
+      <c r="AJ7" t="inlineStr"/>
+      <c r="AK7" t="inlineStr"/>
+      <c r="AL7" t="inlineStr"/>
+      <c r="AM7" t="inlineStr"/>
+      <c r="AN7" t="inlineStr"/>
+      <c r="AO7" t="inlineStr"/>
+      <c r="AP7" t="inlineStr"/>
+      <c r="AQ7" t="inlineStr"/>
+      <c r="AR7" t="inlineStr"/>
+      <c r="AS7" t="inlineStr"/>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AU7" t="inlineStr"/>
+      <c r="AV7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr"/>
+      <c r="AX7" t="inlineStr"/>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr"/>
+      <c r="BA7" t="inlineStr"/>
+      <c r="BB7" t="inlineStr"/>
+      <c r="BC7" t="inlineStr"/>
+      <c r="BD7" t="inlineStr"/>
+      <c r="BE7" t="inlineStr"/>
+      <c r="BF7" t="inlineStr"/>
+      <c r="BG7" t="n">
+        <v>1</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>12</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>1</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP7" t="n">
         <v>5</v>
       </c>
-      <c r="AQ7" t="n">
-        <v>9</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>10</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>58</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>19</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>13</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>6</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>23</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>4</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>2</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>15</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>2</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>1</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>1</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>2</v>
-      </c>
-      <c r="BO7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP7" t="n">
-        <v>10</v>
-      </c>
       <c r="BQ7" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="BR7" t="n">
         <v>100</v>
       </c>
       <c r="BS7" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="BT7" t="n">
         <v>0</v>
@@ -2614,79 +2610,93 @@
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>100</v>
-      </c>
-      <c r="BY7" t="inlineStr"/>
-      <c r="BZ7" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>2.18</v>
+      </c>
       <c r="CA7" t="n">
-        <v>3.88</v>
+        <v>3.14</v>
       </c>
       <c r="CB7" t="n">
-        <v>4.09</v>
-      </c>
-      <c r="CC7" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="CD7" t="n">
-        <v>1.58</v>
-      </c>
+        <v>3.24</v>
+      </c>
+      <c r="CC7" t="inlineStr"/>
+      <c r="CD7" t="inlineStr"/>
       <c r="CE7" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.49</v>
+        <v>2.65</v>
       </c>
       <c r="CG7" t="n">
-        <v>3.04</v>
+        <v>2.81</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="CI7" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="CJ7" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="CK7" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="CL7" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="CM7" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="CN7" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="CO7" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="CP7" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="CQ7" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="CR7" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="CS7" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="CT7" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="CU7" t="n">
         <v>1.38</v>
       </c>
-      <c r="CL7" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="CM7" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="CN7" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="CO7" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="CP7" t="n">
+      <c r="CV7" t="n">
         <v>1.67</v>
       </c>
-      <c r="CQ7" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="CR7" t="inlineStr"/>
-      <c r="CS7" t="inlineStr"/>
-      <c r="CT7" t="inlineStr"/>
-      <c r="CU7" t="inlineStr"/>
-      <c r="CV7" t="n">
-        <v>1.68</v>
-      </c>
       <c r="CW7" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="CX7" t="inlineStr"/>
-      <c r="CY7" t="inlineStr"/>
-      <c r="CZ7" t="inlineStr"/>
+        <v>2.17</v>
+      </c>
+      <c r="CX7" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="CY7" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="CZ7" t="n">
+        <v>3.5</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -2729,82 +2739,82 @@
         <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AI8" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AJ8" t="n">
         <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AL8" t="n">
         <v>3</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN8" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="AO8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AQ8" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AR8" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="AS8" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>44</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA8" t="n">
         <v>11</v>
       </c>
-      <c r="AT8" t="n">
-        <v>3</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>47</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>14</v>
-      </c>
       <c r="BB8" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="BC8" t="n">
         <v>7</v>
       </c>
       <c r="BD8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.62</v>
+        <v>1.43</v>
       </c>
       <c r="BF8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BG8" t="n">
         <v>3</v>
@@ -2816,7 +2826,7 @@
         <v>3</v>
       </c>
       <c r="BJ8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BK8" t="n">
         <v>0</v>
@@ -2825,19 +2835,19 @@
         <v>1</v>
       </c>
       <c r="BM8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BN8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BO8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BP8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BQ8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BR8" t="n">
         <v>100</v>
@@ -2858,236 +2868,244 @@
         <v>0</v>
       </c>
       <c r="BX8" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="BY8" t="inlineStr"/>
       <c r="BZ8" t="inlineStr"/>
       <c r="CA8" t="n">
-        <v>3.48</v>
+        <v>4.1</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.51</v>
+        <v>4.21</v>
       </c>
       <c r="CC8" t="n">
-        <v>3.35</v>
+        <v>5.81</v>
       </c>
       <c r="CD8" t="n">
-        <v>3.69</v>
+        <v>5.43</v>
       </c>
       <c r="CE8" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="CG8" t="n">
-        <v>2.89</v>
+        <v>2.98</v>
       </c>
       <c r="CH8" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CI8" t="n">
-        <v>2.1</v>
+        <v>1.71</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.65</v>
+        <v>1.98</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="CL8" t="n">
-        <v>1.85</v>
+        <v>1.63</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="CN8" t="n">
         <v>2.1</v>
       </c>
       <c r="CO8" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="CP8" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="CQ8" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="CR8" t="inlineStr"/>
-      <c r="CS8" t="inlineStr"/>
-      <c r="CT8" t="inlineStr"/>
-      <c r="CU8" t="inlineStr"/>
+        <v>2.85</v>
+      </c>
+      <c r="CR8" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="CS8" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="CT8" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="CU8" t="n">
+        <v>1.39</v>
+      </c>
       <c r="CV8" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="CW8" t="n">
-        <v>2.09</v>
+        <v>2.06</v>
       </c>
       <c r="CX8" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="CY8" t="n">
-        <v>1.89</v>
+        <v>1.94</v>
       </c>
       <c r="CZ8" t="n">
-        <v>3.15</v>
+        <v>3.41</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
-      <c r="W9" t="inlineStr"/>
-      <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="inlineStr"/>
-      <c r="Z9" t="inlineStr"/>
-      <c r="AA9" t="inlineStr"/>
-      <c r="AB9" t="inlineStr"/>
-      <c r="AC9" t="inlineStr"/>
-      <c r="AD9" t="inlineStr"/>
-      <c r="AE9" t="inlineStr"/>
-      <c r="AF9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>85</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>4</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>38</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="n">
+        <v>105</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>46</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1</v>
+      </c>
+      <c r="P9" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>16</v>
+      </c>
+      <c r="R9" t="n">
+        <v>8</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
         <v>3</v>
       </c>
-      <c r="AQ9" t="n">
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>53</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC9" t="n">
         <v>11</v>
       </c>
-      <c r="AR9" t="n">
-        <v>19</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>6</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>3</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>53</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>7</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>3</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>4</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>23</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD9" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="inlineStr"/>
+      <c r="AH9" t="inlineStr"/>
+      <c r="AI9" t="inlineStr"/>
+      <c r="AJ9" t="inlineStr"/>
+      <c r="AK9" t="inlineStr"/>
+      <c r="AL9" t="inlineStr"/>
+      <c r="AM9" t="inlineStr"/>
+      <c r="AN9" t="inlineStr"/>
+      <c r="AO9" t="inlineStr"/>
+      <c r="AP9" t="inlineStr"/>
+      <c r="AQ9" t="inlineStr"/>
+      <c r="AR9" t="inlineStr"/>
+      <c r="AS9" t="inlineStr"/>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AU9" t="inlineStr"/>
+      <c r="AV9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr"/>
+      <c r="AX9" t="inlineStr"/>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr"/>
+      <c r="BA9" t="inlineStr"/>
+      <c r="BB9" t="inlineStr"/>
+      <c r="BC9" t="inlineStr"/>
+      <c r="BD9" t="inlineStr"/>
+      <c r="BE9" t="inlineStr"/>
+      <c r="BF9" t="inlineStr"/>
       <c r="BG9" t="n">
         <v>3</v>
       </c>
       <c r="BH9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="BI9" t="n">
         <v>3</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BK9" t="n">
         <v>0</v>
       </c>
       <c r="BL9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ9" t="n">
         <v>3</v>
-      </c>
-      <c r="BN9" t="n">
-        <v>3</v>
-      </c>
-      <c r="BO9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP9" t="n">
-        <v>6</v>
-      </c>
-      <c r="BQ9" t="n">
-        <v>4</v>
       </c>
       <c r="BR9" t="n">
         <v>100</v>
@@ -3110,210 +3128,210 @@
       <c r="BX9" t="n">
         <v>0</v>
       </c>
-      <c r="BY9" t="inlineStr"/>
-      <c r="BZ9" t="inlineStr"/>
+      <c r="BY9" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>2.05</v>
+      </c>
       <c r="CA9" t="n">
-        <v>3.3</v>
+        <v>3.48</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.43</v>
-      </c>
-      <c r="CC9" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="CD9" t="n">
-        <v>2.11</v>
-      </c>
+        <v>3.51</v>
+      </c>
+      <c r="CC9" t="inlineStr"/>
+      <c r="CD9" t="inlineStr"/>
       <c r="CE9" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.73</v>
+        <v>2.65</v>
       </c>
       <c r="CG9" t="n">
-        <v>3.13</v>
+        <v>2.89</v>
       </c>
       <c r="CH9" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="CI9" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="CL9" t="n">
-        <v>1.49</v>
+        <v>1.85</v>
       </c>
       <c r="CM9" t="n">
-        <v>3.2</v>
+        <v>2.75</v>
       </c>
       <c r="CN9" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="CO9" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="CP9" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="CQ9" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="CR9" t="inlineStr"/>
       <c r="CS9" t="inlineStr"/>
       <c r="CT9" t="inlineStr"/>
       <c r="CU9" t="inlineStr"/>
       <c r="CV9" t="n">
-        <v>1.49</v>
+        <v>1.7</v>
       </c>
       <c r="CW9" t="n">
-        <v>2.52</v>
+        <v>2.09</v>
       </c>
       <c r="CX9" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="CY9" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="CZ9" t="n">
-        <v>3.14</v>
+        <v>3.15</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr"/>
-      <c r="W10" t="inlineStr"/>
-      <c r="X10" t="inlineStr"/>
-      <c r="Y10" t="inlineStr"/>
-      <c r="Z10" t="inlineStr"/>
-      <c r="AA10" t="inlineStr"/>
-      <c r="AB10" t="inlineStr"/>
-      <c r="AC10" t="inlineStr"/>
-      <c r="AD10" t="inlineStr"/>
-      <c r="AE10" t="inlineStr"/>
-      <c r="AF10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>5</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>77</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2</v>
+      </c>
+      <c r="H10" t="n">
+        <v>130</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2</v>
+      </c>
+      <c r="K10" t="n">
+        <v>6</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="n">
+        <v>62</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>4</v>
+      </c>
+      <c r="P10" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>16</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>61</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>17</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>14</v>
+      </c>
+      <c r="AB10" t="n">
         <v>3</v>
       </c>
-      <c r="AL10" t="n">
-        <v>5</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>33</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>20</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>15</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>11</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>41</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>1</v>
-      </c>
-      <c r="BA10" t="n">
+      <c r="AC10" t="n">
+        <v>26</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="inlineStr"/>
+      <c r="AH10" t="inlineStr"/>
+      <c r="AI10" t="inlineStr"/>
+      <c r="AJ10" t="inlineStr"/>
+      <c r="AK10" t="inlineStr"/>
+      <c r="AL10" t="inlineStr"/>
+      <c r="AM10" t="inlineStr"/>
+      <c r="AN10" t="inlineStr"/>
+      <c r="AO10" t="inlineStr"/>
+      <c r="AP10" t="inlineStr"/>
+      <c r="AQ10" t="inlineStr"/>
+      <c r="AR10" t="inlineStr"/>
+      <c r="AS10" t="inlineStr"/>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AU10" t="inlineStr"/>
+      <c r="AV10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr"/>
+      <c r="AX10" t="inlineStr"/>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr"/>
+      <c r="BA10" t="inlineStr"/>
+      <c r="BB10" t="inlineStr"/>
+      <c r="BC10" t="inlineStr"/>
+      <c r="BD10" t="inlineStr"/>
+      <c r="BE10" t="inlineStr"/>
+      <c r="BF10" t="inlineStr"/>
+      <c r="BG10" t="n">
         <v>4</v>
       </c>
-      <c r="BB10" t="n">
-        <v>2</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>2</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>12</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>2</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>1</v>
-      </c>
       <c r="BH10" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="BI10" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BJ10" t="n">
         <v>0</v>
@@ -3322,13 +3340,13 @@
         <v>1</v>
       </c>
       <c r="BL10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BM10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BN10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BO10" t="n">
         <v>1</v>
@@ -3337,19 +3355,19 @@
         <v>7</v>
       </c>
       <c r="BQ10" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="BR10" t="n">
         <v>100</v>
       </c>
       <c r="BS10" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="BT10" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="BU10" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="BV10" t="n">
         <v>0</v>
@@ -3358,240 +3376,236 @@
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY10" t="inlineStr"/>
-      <c r="BZ10" t="inlineStr"/>
+        <v>100</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>1.7</v>
+      </c>
       <c r="CA10" t="n">
-        <v>3.2</v>
+        <v>4.5</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="CC10" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="CD10" t="n">
-        <v>3.4</v>
-      </c>
+        <v>4.1</v>
+      </c>
+      <c r="CC10" t="inlineStr"/>
+      <c r="CD10" t="inlineStr"/>
       <c r="CE10" t="n">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.75</v>
+        <v>2.35</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.5</v>
+        <v>3.34</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.39</v>
+        <v>1.57</v>
       </c>
       <c r="CI10" t="n">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.91</v>
+        <v>1.62</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.34</v>
+        <v>1.26</v>
       </c>
       <c r="CL10" t="n">
-        <v>1.72</v>
+        <v>1.43</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.97</v>
+        <v>3.28</v>
       </c>
       <c r="CN10" t="n">
-        <v>2.23</v>
+        <v>2.6</v>
       </c>
       <c r="CO10" t="n">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="CP10" t="n">
-        <v>2.15</v>
+        <v>1.56</v>
       </c>
       <c r="CQ10" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="CR10" t="n">
-        <v>1.38</v>
-      </c>
+        <v>2.12</v>
+      </c>
+      <c r="CR10" t="inlineStr"/>
       <c r="CS10" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="CT10" t="n">
-        <v>2.97</v>
-      </c>
+        <v>2.49</v>
+      </c>
+      <c r="CT10" t="inlineStr"/>
       <c r="CU10" t="n">
-        <v>1.39</v>
+        <v>1.55</v>
       </c>
       <c r="CV10" t="inlineStr"/>
       <c r="CW10" t="inlineStr"/>
       <c r="CX10" t="n">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="CY10" t="n">
-        <v>1.98</v>
+        <v>1.66</v>
       </c>
       <c r="CZ10" t="n">
-        <v>3.39</v>
+        <v>2.62</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>75</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" t="n">
-        <v>5</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr"/>
+      <c r="AE11" t="inlineStr"/>
+      <c r="AF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>96</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>7</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>42</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>12</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>11</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>60</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>12</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>11</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD11" t="n">
         <v>29</v>
       </c>
-      <c r="N11" t="n">
-        <v>1</v>
-      </c>
-      <c r="O11" t="n">
-        <v>5</v>
-      </c>
-      <c r="P11" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q11" t="n">
+      <c r="BE11" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>4</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>13</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>2</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>4</v>
+      </c>
+      <c r="BQ11" t="n">
         <v>9</v>
-      </c>
-      <c r="R11" t="n">
-        <v>16</v>
-      </c>
-      <c r="S11" t="n">
-        <v>1</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" t="n">
-        <v>0</v>
-      </c>
-      <c r="W11" t="n">
-        <v>0</v>
-      </c>
-      <c r="X11" t="n">
-        <v>42</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>14</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>7</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>21</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF11" t="inlineStr"/>
-      <c r="AG11" t="inlineStr"/>
-      <c r="AH11" t="inlineStr"/>
-      <c r="AI11" t="inlineStr"/>
-      <c r="AJ11" t="inlineStr"/>
-      <c r="AK11" t="inlineStr"/>
-      <c r="AL11" t="inlineStr"/>
-      <c r="AM11" t="inlineStr"/>
-      <c r="AN11" t="inlineStr"/>
-      <c r="AO11" t="inlineStr"/>
-      <c r="AP11" t="inlineStr"/>
-      <c r="AQ11" t="inlineStr"/>
-      <c r="AR11" t="inlineStr"/>
-      <c r="AS11" t="inlineStr"/>
-      <c r="AT11" t="inlineStr"/>
-      <c r="AU11" t="inlineStr"/>
-      <c r="AV11" t="inlineStr"/>
-      <c r="AW11" t="inlineStr"/>
-      <c r="AX11" t="inlineStr"/>
-      <c r="AY11" t="inlineStr"/>
-      <c r="AZ11" t="inlineStr"/>
-      <c r="BA11" t="inlineStr"/>
-      <c r="BB11" t="inlineStr"/>
-      <c r="BC11" t="inlineStr"/>
-      <c r="BD11" t="inlineStr"/>
-      <c r="BE11" t="inlineStr"/>
-      <c r="BF11" t="inlineStr"/>
-      <c r="BG11" t="n">
-        <v>2</v>
-      </c>
-      <c r="BH11" t="n">
-        <v>15</v>
-      </c>
-      <c r="BI11" t="n">
-        <v>2</v>
-      </c>
-      <c r="BJ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL11" t="n">
-        <v>1</v>
-      </c>
-      <c r="BM11" t="n">
-        <v>1</v>
-      </c>
-      <c r="BN11" t="n">
-        <v>2</v>
-      </c>
-      <c r="BO11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP11" t="n">
-        <v>10</v>
-      </c>
-      <c r="BQ11" t="n">
-        <v>5</v>
       </c>
       <c r="BR11" t="n">
         <v>100</v>
@@ -3612,74 +3626,1576 @@
         <v>0</v>
       </c>
       <c r="BX11" t="n">
-        <v>100</v>
-      </c>
-      <c r="BY11" t="n">
-        <v>5.21</v>
-      </c>
-      <c r="BZ11" t="n">
-        <v>5.43</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="BY11" t="inlineStr"/>
+      <c r="BZ11" t="inlineStr"/>
       <c r="CA11" t="n">
-        <v>3.88</v>
+        <v>3.6</v>
       </c>
       <c r="CB11" t="n">
-        <v>4.09</v>
-      </c>
-      <c r="CC11" t="inlineStr"/>
-      <c r="CD11" t="inlineStr"/>
+        <v>3.16</v>
+      </c>
+      <c r="CC11" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="CD11" t="n">
+        <v>3.51</v>
+      </c>
       <c r="CE11" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.49</v>
+        <v>2.56</v>
       </c>
       <c r="CG11" t="n">
-        <v>3.04</v>
+        <v>3.35</v>
       </c>
       <c r="CH11" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="CI11" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="CJ11" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CL11" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.83</v>
+        <v>2.95</v>
       </c>
       <c r="CN11" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="CO11" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="CP11" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="CQ11" t="n">
-        <v>2.64</v>
+        <v>2.76</v>
       </c>
       <c r="CR11" t="inlineStr"/>
       <c r="CS11" t="inlineStr"/>
       <c r="CT11" t="inlineStr"/>
       <c r="CU11" t="inlineStr"/>
       <c r="CV11" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="CW11" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="CX11" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="CY11" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="CZ11" t="n">
+        <v>3.81</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>7</v>
+      </c>
+      <c r="H12" t="n">
+        <v>95</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>14</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>47</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>7</v>
+      </c>
+      <c r="P12" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>20</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>58</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>16</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>13</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>18</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="inlineStr"/>
+      <c r="AH12" t="inlineStr"/>
+      <c r="AI12" t="inlineStr"/>
+      <c r="AJ12" t="inlineStr"/>
+      <c r="AK12" t="inlineStr"/>
+      <c r="AL12" t="inlineStr"/>
+      <c r="AM12" t="inlineStr"/>
+      <c r="AN12" t="inlineStr"/>
+      <c r="AO12" t="inlineStr"/>
+      <c r="AP12" t="inlineStr"/>
+      <c r="AQ12" t="inlineStr"/>
+      <c r="AR12" t="inlineStr"/>
+      <c r="AS12" t="inlineStr"/>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AU12" t="inlineStr"/>
+      <c r="AV12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr"/>
+      <c r="AX12" t="inlineStr"/>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr"/>
+      <c r="BA12" t="inlineStr"/>
+      <c r="BB12" t="inlineStr"/>
+      <c r="BC12" t="inlineStr"/>
+      <c r="BD12" t="inlineStr"/>
+      <c r="BE12" t="inlineStr"/>
+      <c r="BF12" t="inlineStr"/>
+      <c r="BG12" t="n">
+        <v>1</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>19</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>7</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>12</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>100</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY12" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BZ12" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="CA12" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="CB12" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="CC12" t="inlineStr"/>
+      <c r="CD12" t="inlineStr"/>
+      <c r="CE12" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="CF12" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="CG12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="CH12" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="CI12" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="CJ12" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="CK12" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="CL12" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="CM12" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="CN12" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="CO12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="CP12" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="CQ12" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="CR12" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="CS12" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="CT12" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="CU12" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="CV12" t="inlineStr"/>
+      <c r="CW12" t="inlineStr"/>
+      <c r="CX12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="CY12" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="CZ12" t="n">
+        <v>3.39</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Malmö FF</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr"/>
+      <c r="AD13" t="inlineStr"/>
+      <c r="AE13" t="inlineStr"/>
+      <c r="AF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>108</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>10</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>48</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>10</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>58</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>19</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>13</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>24</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>4</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>15</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>2</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>10</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>5</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>100</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>100</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX13" t="n">
+        <v>100</v>
+      </c>
+      <c r="BY13" t="inlineStr"/>
+      <c r="BZ13" t="inlineStr"/>
+      <c r="CA13" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="CB13" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="CC13" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="CD13" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="CE13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="CF13" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="CG13" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="CH13" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="CI13" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="CJ13" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="CK13" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="CL13" t="n">
         <v>1.68</v>
       </c>
-      <c r="CW11" t="n">
+      <c r="CM13" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="CN13" t="n">
         <v>2.12</v>
       </c>
-      <c r="CX11" t="inlineStr"/>
-      <c r="CY11" t="inlineStr"/>
-      <c r="CZ11" t="inlineStr"/>
+      <c r="CO13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="CP13" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="CQ13" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="CR13" t="inlineStr"/>
+      <c r="CS13" t="inlineStr"/>
+      <c r="CT13" t="inlineStr"/>
+      <c r="CU13" t="inlineStr"/>
+      <c r="CV13" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="CW13" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="CX13" t="inlineStr"/>
+      <c r="CY13" t="inlineStr"/>
+      <c r="CZ13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Mjällby</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr"/>
+      <c r="AD14" t="inlineStr"/>
+      <c r="AE14" t="inlineStr"/>
+      <c r="AF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>34</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>16</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>17</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>11</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>47</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>14</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>12</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>4</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>3</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>5</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>1</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>3</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>100</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>100</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>100</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY14" t="inlineStr"/>
+      <c r="BZ14" t="inlineStr"/>
+      <c r="CA14" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="CB14" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="CC14" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="CD14" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="CE14" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="CF14" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="CG14" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="CH14" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="CI14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="CJ14" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="CK14" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="CL14" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="CM14" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="CN14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="CO14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="CP14" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CQ14" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="CR14" t="inlineStr"/>
+      <c r="CS14" t="inlineStr"/>
+      <c r="CT14" t="inlineStr"/>
+      <c r="CU14" t="inlineStr"/>
+      <c r="CV14" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="CW14" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="CX14" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="CY14" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="CZ14" t="n">
+        <v>3.15</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Sirius</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr"/>
+      <c r="AC15" t="inlineStr"/>
+      <c r="AD15" t="inlineStr"/>
+      <c r="AE15" t="inlineStr"/>
+      <c r="AF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>85</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>38</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>19</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>6</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>53</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>23</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>3</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>10</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>6</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>4</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>100</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>100</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>100</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY15" t="inlineStr"/>
+      <c r="BZ15" t="inlineStr"/>
+      <c r="CA15" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="CB15" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="CC15" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="CD15" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="CE15" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="CF15" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="CG15" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="CH15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="CI15" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="CJ15" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="CK15" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="CL15" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="CM15" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="CN15" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="CO15" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="CP15" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="CQ15" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="CR15" t="inlineStr"/>
+      <c r="CS15" t="inlineStr"/>
+      <c r="CT15" t="inlineStr"/>
+      <c r="CU15" t="inlineStr"/>
+      <c r="CV15" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="CW15" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="CX15" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="CY15" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="CZ15" t="n">
+        <v>3.14</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Västerås SK</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr"/>
+      <c r="AC16" t="inlineStr"/>
+      <c r="AD16" t="inlineStr"/>
+      <c r="AE16" t="inlineStr"/>
+      <c r="AF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>77</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>33</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>20</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>15</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>11</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>42</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>12</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>1</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>19</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>7</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>12</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>100</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY16" t="inlineStr"/>
+      <c r="BZ16" t="inlineStr"/>
+      <c r="CA16" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="CB16" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="CC16" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="CD16" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="CE16" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="CF16" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="CG16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="CH16" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="CI16" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="CJ16" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="CK16" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="CL16" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="CM16" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="CN16" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="CO16" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="CP16" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="CQ16" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="CR16" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="CS16" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="CT16" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="CU16" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="CV16" t="inlineStr"/>
+      <c r="CW16" t="inlineStr"/>
+      <c r="CX16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="CY16" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="CZ16" t="n">
+        <v>3.39</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Örgryte</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>75</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>5</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>29</v>
+      </c>
+      <c r="N17" t="n">
+        <v>1</v>
+      </c>
+      <c r="O17" t="n">
+        <v>5</v>
+      </c>
+      <c r="P17" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>10</v>
+      </c>
+      <c r="R17" t="n">
+        <v>16</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>42</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>21</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="inlineStr"/>
+      <c r="AH17" t="inlineStr"/>
+      <c r="AI17" t="inlineStr"/>
+      <c r="AJ17" t="inlineStr"/>
+      <c r="AK17" t="inlineStr"/>
+      <c r="AL17" t="inlineStr"/>
+      <c r="AM17" t="inlineStr"/>
+      <c r="AN17" t="inlineStr"/>
+      <c r="AO17" t="inlineStr"/>
+      <c r="AP17" t="inlineStr"/>
+      <c r="AQ17" t="inlineStr"/>
+      <c r="AR17" t="inlineStr"/>
+      <c r="AS17" t="inlineStr"/>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AU17" t="inlineStr"/>
+      <c r="AV17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr"/>
+      <c r="AX17" t="inlineStr"/>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr"/>
+      <c r="BA17" t="inlineStr"/>
+      <c r="BB17" t="inlineStr"/>
+      <c r="BC17" t="inlineStr"/>
+      <c r="BD17" t="inlineStr"/>
+      <c r="BE17" t="inlineStr"/>
+      <c r="BF17" t="inlineStr"/>
+      <c r="BG17" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>15</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>2</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>10</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>5</v>
+      </c>
+      <c r="BR17" t="n">
+        <v>100</v>
+      </c>
+      <c r="BS17" t="n">
+        <v>100</v>
+      </c>
+      <c r="BT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX17" t="n">
+        <v>100</v>
+      </c>
+      <c r="BY17" t="n">
+        <v>5.21</v>
+      </c>
+      <c r="BZ17" t="n">
+        <v>5.43</v>
+      </c>
+      <c r="CA17" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="CB17" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="CC17" t="inlineStr"/>
+      <c r="CD17" t="inlineStr"/>
+      <c r="CE17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="CF17" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="CG17" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="CH17" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="CI17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="CJ17" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="CK17" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="CL17" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="CM17" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="CN17" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="CO17" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="CP17" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="CQ17" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="CR17" t="inlineStr"/>
+      <c r="CS17" t="inlineStr"/>
+      <c r="CT17" t="inlineStr"/>
+      <c r="CU17" t="inlineStr"/>
+      <c r="CV17" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="CW17" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="CX17" t="inlineStr"/>
+      <c r="CY17" t="inlineStr"/>
+      <c r="CZ17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/teams/leagues/Averages_Sweden_Allsvenskan_2026.xlsx
+++ b/data/teams/leagues/Averages_Sweden_Allsvenskan_2026.xlsx
@@ -1509,7 +1509,7 @@
         <v>13</v>
       </c>
       <c r="AS3" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AT3" t="n">
         <v>2</v>
@@ -3253,10 +3253,10 @@
         <v>13</v>
       </c>
       <c r="Q10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S10" t="n">
         <v>2</v>

--- a/data/teams/leagues/Averages_Sweden_Allsvenskan_2026.xlsx
+++ b/data/teams/leagues/Averages_Sweden_Allsvenskan_2026.xlsx
@@ -137,9 +137,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AveragesTable_Sweden_All" displayName="AveragesTable_Sweden_All" ref="A1:CZ17" headerRowCount="1">
-  <autoFilter ref="A1:CZ17"/>
-  <tableColumns count="104">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AveragesTable_Sweden_All" displayName="AveragesTable_Sweden_All" ref="A1:DY17" headerRowCount="1">
+  <autoFilter ref="A1:DY17"/>
+  <tableColumns count="129">
     <tableColumn id="1" name="team_name"/>
     <tableColumn id="2" name="total_games"/>
     <tableColumn id="3" name="home_games"/>
@@ -244,6 +244,31 @@
     <tableColumn id="102" name="avg_pinnacle_ft_over15_odd"/>
     <tableColumn id="103" name="avg_pinnacle_ft_over25_odd"/>
     <tableColumn id="104" name="avg_pinnacle_ft_over35_odd"/>
+    <tableColumn id="105" name="total_avg_0_10_min_goals"/>
+    <tableColumn id="106" name="total_avg_2h_cards"/>
+    <tableColumn id="107" name="total_avg_2h_corners"/>
+    <tableColumn id="108" name="total_avg_attacks"/>
+    <tableColumn id="109" name="total_avg_cards_0_10_min"/>
+    <tableColumn id="110" name="total_avg_cards_num"/>
+    <tableColumn id="111" name="total_avg_corners"/>
+    <tableColumn id="112" name="total_avg_corners_0_10_min"/>
+    <tableColumn id="113" name="total_avg_dangerous_attacks"/>
+    <tableColumn id="114" name="total_avg_fh_cards"/>
+    <tableColumn id="115" name="total_avg_fh_corners"/>
+    <tableColumn id="116" name="total_avg_fouls"/>
+    <tableColumn id="117" name="total_avg_freekicks"/>
+    <tableColumn id="118" name="total_avg_goalkicks"/>
+    <tableColumn id="119" name="total_avg_penalties_won"/>
+    <tableColumn id="120" name="total_avg_penalty_goals"/>
+    <tableColumn id="121" name="total_avg_penalty_missed"/>
+    <tableColumn id="122" name="total_avg_possession"/>
+    <tableColumn id="123" name="total_avg_red_cards"/>
+    <tableColumn id="124" name="total_avg_shots"/>
+    <tableColumn id="125" name="total_avg_shotsOffTarget"/>
+    <tableColumn id="126" name="total_avg_shotsOnTarget"/>
+    <tableColumn id="127" name="total_avg_throwins"/>
+    <tableColumn id="128" name="total_avg_xg"/>
+    <tableColumn id="129" name="total_avg_yellow_cards"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -538,7 +563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CZ17"/>
+  <dimension ref="A1:DY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19.2" customWidth="1" min="1" max="1"/>
@@ -645,6 +670,31 @@
     <col width="33.6" customWidth="1" min="102" max="102"/>
     <col width="33.6" customWidth="1" min="103" max="103"/>
     <col width="33.6" customWidth="1" min="104" max="104"/>
+    <col width="31.2" customWidth="1" min="105" max="105"/>
+    <col width="24" customWidth="1" min="106" max="106"/>
+    <col width="26.4" customWidth="1" min="107" max="107"/>
+    <col width="22.8" customWidth="1" min="108" max="108"/>
+    <col width="31.2" customWidth="1" min="109" max="109"/>
+    <col width="25.2" customWidth="1" min="110" max="110"/>
+    <col width="22.8" customWidth="1" min="111" max="111"/>
+    <col width="33.6" customWidth="1" min="112" max="112"/>
+    <col width="34.8" customWidth="1" min="113" max="113"/>
+    <col width="24" customWidth="1" min="114" max="114"/>
+    <col width="26.4" customWidth="1" min="115" max="115"/>
+    <col width="20.4" customWidth="1" min="116" max="116"/>
+    <col width="25.2" customWidth="1" min="117" max="117"/>
+    <col width="25.2" customWidth="1" min="118" max="118"/>
+    <col width="30" customWidth="1" min="119" max="119"/>
+    <col width="30" customWidth="1" min="120" max="120"/>
+    <col width="31.2" customWidth="1" min="121" max="121"/>
+    <col width="26.4" customWidth="1" min="122" max="122"/>
+    <col width="25.2" customWidth="1" min="123" max="123"/>
+    <col width="20.4" customWidth="1" min="124" max="124"/>
+    <col width="31.2" customWidth="1" min="125" max="125"/>
+    <col width="30" customWidth="1" min="126" max="126"/>
+    <col width="24" customWidth="1" min="127" max="127"/>
+    <col width="16.8" customWidth="1" min="128" max="128"/>
+    <col width="28.8" customWidth="1" min="129" max="129"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1166,6 +1216,131 @@
       <c r="CZ1" s="1" t="inlineStr">
         <is>
           <t>avg_pinnacle_ft_over35_odd</t>
+        </is>
+      </c>
+      <c r="DA1" s="1" t="inlineStr">
+        <is>
+          <t>total_avg_0_10_min_goals</t>
+        </is>
+      </c>
+      <c r="DB1" s="1" t="inlineStr">
+        <is>
+          <t>total_avg_2h_cards</t>
+        </is>
+      </c>
+      <c r="DC1" s="1" t="inlineStr">
+        <is>
+          <t>total_avg_2h_corners</t>
+        </is>
+      </c>
+      <c r="DD1" s="1" t="inlineStr">
+        <is>
+          <t>total_avg_attacks</t>
+        </is>
+      </c>
+      <c r="DE1" s="1" t="inlineStr">
+        <is>
+          <t>total_avg_cards_0_10_min</t>
+        </is>
+      </c>
+      <c r="DF1" s="1" t="inlineStr">
+        <is>
+          <t>total_avg_cards_num</t>
+        </is>
+      </c>
+      <c r="DG1" s="1" t="inlineStr">
+        <is>
+          <t>total_avg_corners</t>
+        </is>
+      </c>
+      <c r="DH1" s="1" t="inlineStr">
+        <is>
+          <t>total_avg_corners_0_10_min</t>
+        </is>
+      </c>
+      <c r="DI1" s="1" t="inlineStr">
+        <is>
+          <t>total_avg_dangerous_attacks</t>
+        </is>
+      </c>
+      <c r="DJ1" s="1" t="inlineStr">
+        <is>
+          <t>total_avg_fh_cards</t>
+        </is>
+      </c>
+      <c r="DK1" s="1" t="inlineStr">
+        <is>
+          <t>total_avg_fh_corners</t>
+        </is>
+      </c>
+      <c r="DL1" s="1" t="inlineStr">
+        <is>
+          <t>total_avg_fouls</t>
+        </is>
+      </c>
+      <c r="DM1" s="1" t="inlineStr">
+        <is>
+          <t>total_avg_freekicks</t>
+        </is>
+      </c>
+      <c r="DN1" s="1" t="inlineStr">
+        <is>
+          <t>total_avg_goalkicks</t>
+        </is>
+      </c>
+      <c r="DO1" s="1" t="inlineStr">
+        <is>
+          <t>total_avg_penalties_won</t>
+        </is>
+      </c>
+      <c r="DP1" s="1" t="inlineStr">
+        <is>
+          <t>total_avg_penalty_goals</t>
+        </is>
+      </c>
+      <c r="DQ1" s="1" t="inlineStr">
+        <is>
+          <t>total_avg_penalty_missed</t>
+        </is>
+      </c>
+      <c r="DR1" s="1" t="inlineStr">
+        <is>
+          <t>total_avg_possession</t>
+        </is>
+      </c>
+      <c r="DS1" s="1" t="inlineStr">
+        <is>
+          <t>total_avg_red_cards</t>
+        </is>
+      </c>
+      <c r="DT1" s="1" t="inlineStr">
+        <is>
+          <t>total_avg_shots</t>
+        </is>
+      </c>
+      <c r="DU1" s="1" t="inlineStr">
+        <is>
+          <t>total_avg_shotsOffTarget</t>
+        </is>
+      </c>
+      <c r="DV1" s="1" t="inlineStr">
+        <is>
+          <t>total_avg_shotsOnTarget</t>
+        </is>
+      </c>
+      <c r="DW1" s="1" t="inlineStr">
+        <is>
+          <t>total_avg_throwins</t>
+        </is>
+      </c>
+      <c r="DX1" s="1" t="inlineStr">
+        <is>
+          <t>total_avg_xg</t>
+        </is>
+      </c>
+      <c r="DY1" s="1" t="inlineStr">
+        <is>
+          <t>total_avg_yellow_cards</t>
         </is>
       </c>
     </row>
@@ -1426,6 +1601,31 @@
       <c r="CZ2" t="n">
         <v>3.41</v>
       </c>
+      <c r="DA2" t="inlineStr"/>
+      <c r="DB2" t="inlineStr"/>
+      <c r="DC2" t="inlineStr"/>
+      <c r="DD2" t="inlineStr"/>
+      <c r="DE2" t="inlineStr"/>
+      <c r="DF2" t="inlineStr"/>
+      <c r="DG2" t="inlineStr"/>
+      <c r="DH2" t="inlineStr"/>
+      <c r="DI2" t="inlineStr"/>
+      <c r="DJ2" t="inlineStr"/>
+      <c r="DK2" t="inlineStr"/>
+      <c r="DL2" t="inlineStr"/>
+      <c r="DM2" t="inlineStr"/>
+      <c r="DN2" t="inlineStr"/>
+      <c r="DO2" t="inlineStr"/>
+      <c r="DP2" t="inlineStr"/>
+      <c r="DQ2" t="inlineStr"/>
+      <c r="DR2" t="inlineStr"/>
+      <c r="DS2" t="inlineStr"/>
+      <c r="DT2" t="inlineStr"/>
+      <c r="DU2" t="inlineStr"/>
+      <c r="DV2" t="inlineStr"/>
+      <c r="DW2" t="inlineStr"/>
+      <c r="DX2" t="inlineStr"/>
+      <c r="DY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1676,6 +1876,31 @@
       <c r="CZ3" t="n">
         <v>2.62</v>
       </c>
+      <c r="DA3" t="inlineStr"/>
+      <c r="DB3" t="inlineStr"/>
+      <c r="DC3" t="inlineStr"/>
+      <c r="DD3" t="inlineStr"/>
+      <c r="DE3" t="inlineStr"/>
+      <c r="DF3" t="inlineStr"/>
+      <c r="DG3" t="inlineStr"/>
+      <c r="DH3" t="inlineStr"/>
+      <c r="DI3" t="inlineStr"/>
+      <c r="DJ3" t="inlineStr"/>
+      <c r="DK3" t="inlineStr"/>
+      <c r="DL3" t="inlineStr"/>
+      <c r="DM3" t="inlineStr"/>
+      <c r="DN3" t="inlineStr"/>
+      <c r="DO3" t="inlineStr"/>
+      <c r="DP3" t="inlineStr"/>
+      <c r="DQ3" t="inlineStr"/>
+      <c r="DR3" t="inlineStr"/>
+      <c r="DS3" t="inlineStr"/>
+      <c r="DT3" t="inlineStr"/>
+      <c r="DU3" t="inlineStr"/>
+      <c r="DV3" t="inlineStr"/>
+      <c r="DW3" t="inlineStr"/>
+      <c r="DX3" t="inlineStr"/>
+      <c r="DY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1926,6 +2151,31 @@
       <c r="CZ4" t="n">
         <v>3.14</v>
       </c>
+      <c r="DA4" t="inlineStr"/>
+      <c r="DB4" t="inlineStr"/>
+      <c r="DC4" t="inlineStr"/>
+      <c r="DD4" t="inlineStr"/>
+      <c r="DE4" t="inlineStr"/>
+      <c r="DF4" t="inlineStr"/>
+      <c r="DG4" t="inlineStr"/>
+      <c r="DH4" t="inlineStr"/>
+      <c r="DI4" t="inlineStr"/>
+      <c r="DJ4" t="inlineStr"/>
+      <c r="DK4" t="inlineStr"/>
+      <c r="DL4" t="inlineStr"/>
+      <c r="DM4" t="inlineStr"/>
+      <c r="DN4" t="inlineStr"/>
+      <c r="DO4" t="inlineStr"/>
+      <c r="DP4" t="inlineStr"/>
+      <c r="DQ4" t="inlineStr"/>
+      <c r="DR4" t="inlineStr"/>
+      <c r="DS4" t="inlineStr"/>
+      <c r="DT4" t="inlineStr"/>
+      <c r="DU4" t="inlineStr"/>
+      <c r="DV4" t="inlineStr"/>
+      <c r="DW4" t="inlineStr"/>
+      <c r="DX4" t="inlineStr"/>
+      <c r="DY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2184,6 +2434,31 @@
       <c r="CZ5" t="n">
         <v>3.5</v>
       </c>
+      <c r="DA5" t="inlineStr"/>
+      <c r="DB5" t="inlineStr"/>
+      <c r="DC5" t="inlineStr"/>
+      <c r="DD5" t="inlineStr"/>
+      <c r="DE5" t="inlineStr"/>
+      <c r="DF5" t="inlineStr"/>
+      <c r="DG5" t="inlineStr"/>
+      <c r="DH5" t="inlineStr"/>
+      <c r="DI5" t="inlineStr"/>
+      <c r="DJ5" t="inlineStr"/>
+      <c r="DK5" t="inlineStr"/>
+      <c r="DL5" t="inlineStr"/>
+      <c r="DM5" t="inlineStr"/>
+      <c r="DN5" t="inlineStr"/>
+      <c r="DO5" t="inlineStr"/>
+      <c r="DP5" t="inlineStr"/>
+      <c r="DQ5" t="inlineStr"/>
+      <c r="DR5" t="inlineStr"/>
+      <c r="DS5" t="inlineStr"/>
+      <c r="DT5" t="inlineStr"/>
+      <c r="DU5" t="inlineStr"/>
+      <c r="DV5" t="inlineStr"/>
+      <c r="DW5" t="inlineStr"/>
+      <c r="DX5" t="inlineStr"/>
+      <c r="DY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2192,13 +2467,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C6" t="n">
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -2281,41 +2556,95 @@
       <c r="AE6" t="n">
         <v>1</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
-      <c r="AG6" t="inlineStr"/>
-      <c r="AH6" t="inlineStr"/>
-      <c r="AI6" t="inlineStr"/>
-      <c r="AJ6" t="inlineStr"/>
-      <c r="AK6" t="inlineStr"/>
-      <c r="AL6" t="inlineStr"/>
-      <c r="AM6" t="inlineStr"/>
-      <c r="AN6" t="inlineStr"/>
-      <c r="AO6" t="inlineStr"/>
-      <c r="AP6" t="inlineStr"/>
-      <c r="AQ6" t="inlineStr"/>
-      <c r="AR6" t="inlineStr"/>
-      <c r="AS6" t="inlineStr"/>
-      <c r="AT6" t="inlineStr"/>
-      <c r="AU6" t="inlineStr"/>
-      <c r="AV6" t="inlineStr"/>
-      <c r="AW6" t="inlineStr"/>
-      <c r="AX6" t="inlineStr"/>
-      <c r="AY6" t="inlineStr"/>
-      <c r="AZ6" t="inlineStr"/>
-      <c r="BA6" t="inlineStr"/>
-      <c r="BB6" t="inlineStr"/>
-      <c r="BC6" t="inlineStr"/>
-      <c r="BD6" t="inlineStr"/>
-      <c r="BE6" t="inlineStr"/>
-      <c r="BF6" t="inlineStr"/>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>97</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>36</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>9</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>8</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>49</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>3</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>24</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>2</v>
+      </c>
       <c r="BG6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BH6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BI6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BJ6" t="n">
         <v>0</v>
@@ -2327,16 +2656,16 @@
         <v>2</v>
       </c>
       <c r="BM6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BN6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BO6" t="n">
         <v>0</v>
       </c>
       <c r="BP6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BQ6" t="n">
         <v>9</v>
@@ -2348,10 +2677,10 @@
         <v>100</v>
       </c>
       <c r="BT6" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BU6" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BV6" t="n">
         <v>0</v>
@@ -2360,7 +2689,7 @@
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BY6" t="n">
         <v>2.37</v>
@@ -2369,70 +2698,157 @@
         <v>2.26</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.6</v>
+        <v>3.53</v>
       </c>
       <c r="CB6" t="n">
         <v>3.16</v>
       </c>
-      <c r="CC6" t="inlineStr"/>
-      <c r="CD6" t="inlineStr"/>
+      <c r="CC6" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="CD6" t="n">
+        <v>2.49</v>
+      </c>
       <c r="CE6" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.56</v>
+        <v>2.7</v>
       </c>
       <c r="CG6" t="n">
-        <v>3.35</v>
+        <v>3.18</v>
       </c>
       <c r="CH6" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="CI6" t="n">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CL6" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="CN6" t="n">
         <v>2.2</v>
       </c>
       <c r="CO6" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="CP6" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="CQ6" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="CR6" t="inlineStr"/>
-      <c r="CS6" t="inlineStr"/>
-      <c r="CT6" t="inlineStr"/>
-      <c r="CU6" t="inlineStr"/>
+        <v>2.97</v>
+      </c>
+      <c r="CR6" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="CS6" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="CT6" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="CU6" t="n">
+        <v>1.33</v>
+      </c>
       <c r="CV6" t="n">
         <v>1.6</v>
       </c>
       <c r="CW6" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="CX6" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="CY6" t="n">
-        <v>2.17</v>
+        <v>2.24</v>
       </c>
       <c r="CZ6" t="n">
-        <v>3.81</v>
+        <v>3.92</v>
+      </c>
+      <c r="DA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB6" t="n">
+        <v>1</v>
+      </c>
+      <c r="DC6" t="n">
+        <v>3</v>
+      </c>
+      <c r="DD6" t="n">
+        <v>90.5</v>
+      </c>
+      <c r="DE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DG6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="DH6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DI6" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="DJ6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DK6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DL6" t="n">
+        <v>12</v>
+      </c>
+      <c r="DM6" t="n">
+        <v>8</v>
+      </c>
+      <c r="DN6" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="DO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR6" t="n">
+        <v>44.5</v>
+      </c>
+      <c r="DS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT6" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="DU6" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="DV6" t="n">
+        <v>4</v>
+      </c>
+      <c r="DW6" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="DX6" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="DY6" t="n">
+        <v>1.5</v>
       </c>
     </row>
     <row r="7">
@@ -2692,6 +3108,31 @@
       <c r="CZ7" t="n">
         <v>3.5</v>
       </c>
+      <c r="DA7" t="inlineStr"/>
+      <c r="DB7" t="inlineStr"/>
+      <c r="DC7" t="inlineStr"/>
+      <c r="DD7" t="inlineStr"/>
+      <c r="DE7" t="inlineStr"/>
+      <c r="DF7" t="inlineStr"/>
+      <c r="DG7" t="inlineStr"/>
+      <c r="DH7" t="inlineStr"/>
+      <c r="DI7" t="inlineStr"/>
+      <c r="DJ7" t="inlineStr"/>
+      <c r="DK7" t="inlineStr"/>
+      <c r="DL7" t="inlineStr"/>
+      <c r="DM7" t="inlineStr"/>
+      <c r="DN7" t="inlineStr"/>
+      <c r="DO7" t="inlineStr"/>
+      <c r="DP7" t="inlineStr"/>
+      <c r="DQ7" t="inlineStr"/>
+      <c r="DR7" t="inlineStr"/>
+      <c r="DS7" t="inlineStr"/>
+      <c r="DT7" t="inlineStr"/>
+      <c r="DU7" t="inlineStr"/>
+      <c r="DV7" t="inlineStr"/>
+      <c r="DW7" t="inlineStr"/>
+      <c r="DX7" t="inlineStr"/>
+      <c r="DY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2950,6 +3391,31 @@
       <c r="CZ8" t="n">
         <v>3.41</v>
       </c>
+      <c r="DA8" t="inlineStr"/>
+      <c r="DB8" t="inlineStr"/>
+      <c r="DC8" t="inlineStr"/>
+      <c r="DD8" t="inlineStr"/>
+      <c r="DE8" t="inlineStr"/>
+      <c r="DF8" t="inlineStr"/>
+      <c r="DG8" t="inlineStr"/>
+      <c r="DH8" t="inlineStr"/>
+      <c r="DI8" t="inlineStr"/>
+      <c r="DJ8" t="inlineStr"/>
+      <c r="DK8" t="inlineStr"/>
+      <c r="DL8" t="inlineStr"/>
+      <c r="DM8" t="inlineStr"/>
+      <c r="DN8" t="inlineStr"/>
+      <c r="DO8" t="inlineStr"/>
+      <c r="DP8" t="inlineStr"/>
+      <c r="DQ8" t="inlineStr"/>
+      <c r="DR8" t="inlineStr"/>
+      <c r="DS8" t="inlineStr"/>
+      <c r="DT8" t="inlineStr"/>
+      <c r="DU8" t="inlineStr"/>
+      <c r="DV8" t="inlineStr"/>
+      <c r="DW8" t="inlineStr"/>
+      <c r="DX8" t="inlineStr"/>
+      <c r="DY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3200,6 +3666,31 @@
       <c r="CZ9" t="n">
         <v>3.15</v>
       </c>
+      <c r="DA9" t="inlineStr"/>
+      <c r="DB9" t="inlineStr"/>
+      <c r="DC9" t="inlineStr"/>
+      <c r="DD9" t="inlineStr"/>
+      <c r="DE9" t="inlineStr"/>
+      <c r="DF9" t="inlineStr"/>
+      <c r="DG9" t="inlineStr"/>
+      <c r="DH9" t="inlineStr"/>
+      <c r="DI9" t="inlineStr"/>
+      <c r="DJ9" t="inlineStr"/>
+      <c r="DK9" t="inlineStr"/>
+      <c r="DL9" t="inlineStr"/>
+      <c r="DM9" t="inlineStr"/>
+      <c r="DN9" t="inlineStr"/>
+      <c r="DO9" t="inlineStr"/>
+      <c r="DP9" t="inlineStr"/>
+      <c r="DQ9" t="inlineStr"/>
+      <c r="DR9" t="inlineStr"/>
+      <c r="DS9" t="inlineStr"/>
+      <c r="DT9" t="inlineStr"/>
+      <c r="DU9" t="inlineStr"/>
+      <c r="DV9" t="inlineStr"/>
+      <c r="DW9" t="inlineStr"/>
+      <c r="DX9" t="inlineStr"/>
+      <c r="DY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3208,13 +3699,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -3297,41 +3788,95 @@
       <c r="AE10" t="n">
         <v>2</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
-      <c r="AG10" t="inlineStr"/>
-      <c r="AH10" t="inlineStr"/>
-      <c r="AI10" t="inlineStr"/>
-      <c r="AJ10" t="inlineStr"/>
-      <c r="AK10" t="inlineStr"/>
-      <c r="AL10" t="inlineStr"/>
-      <c r="AM10" t="inlineStr"/>
-      <c r="AN10" t="inlineStr"/>
-      <c r="AO10" t="inlineStr"/>
-      <c r="AP10" t="inlineStr"/>
-      <c r="AQ10" t="inlineStr"/>
-      <c r="AR10" t="inlineStr"/>
-      <c r="AS10" t="inlineStr"/>
-      <c r="AT10" t="inlineStr"/>
-      <c r="AU10" t="inlineStr"/>
-      <c r="AV10" t="inlineStr"/>
-      <c r="AW10" t="inlineStr"/>
-      <c r="AX10" t="inlineStr"/>
-      <c r="AY10" t="inlineStr"/>
-      <c r="AZ10" t="inlineStr"/>
-      <c r="BA10" t="inlineStr"/>
-      <c r="BB10" t="inlineStr"/>
-      <c r="BC10" t="inlineStr"/>
-      <c r="BD10" t="inlineStr"/>
-      <c r="BE10" t="inlineStr"/>
-      <c r="BF10" t="inlineStr"/>
+      <c r="AF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>61</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>6</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>26</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>19</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>8</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>12</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>32</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>12</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>16</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>6</v>
+      </c>
       <c r="BG10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BH10" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="BI10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BJ10" t="n">
         <v>0</v>
@@ -3340,13 +3885,13 @@
         <v>1</v>
       </c>
       <c r="BL10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BM10" t="n">
         <v>1</v>
       </c>
       <c r="BN10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BO10" t="n">
         <v>1</v>
@@ -3355,7 +3900,7 @@
         <v>7</v>
       </c>
       <c r="BQ10" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="BR10" t="n">
         <v>100</v>
@@ -3364,10 +3909,10 @@
         <v>100</v>
       </c>
       <c r="BT10" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="BU10" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="BV10" t="n">
         <v>0</v>
@@ -3376,7 +3921,7 @@
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="BY10" t="n">
         <v>1.53</v>
@@ -3385,70 +3930,153 @@
         <v>1.7</v>
       </c>
       <c r="CA10" t="n">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
       <c r="CB10" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="CC10" t="inlineStr"/>
-      <c r="CD10" t="inlineStr"/>
+        <v>3.66</v>
+      </c>
+      <c r="CC10" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="CD10" t="n">
+        <v>2.44</v>
+      </c>
       <c r="CE10" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="CG10" t="n">
-        <v>3.34</v>
+        <v>3.12</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="CI10" t="n">
-        <v>2.15</v>
+        <v>2.22</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="CK10" t="n">
         <v>1.26</v>
       </c>
       <c r="CL10" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CM10" t="n">
-        <v>3.28</v>
+        <v>3.39</v>
       </c>
       <c r="CN10" t="n">
         <v>2.6</v>
       </c>
       <c r="CO10" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="CP10" t="n">
-        <v>1.56</v>
+        <v>1.64</v>
       </c>
       <c r="CQ10" t="n">
-        <v>2.12</v>
+        <v>2.38</v>
       </c>
       <c r="CR10" t="inlineStr"/>
       <c r="CS10" t="n">
-        <v>2.49</v>
+        <v>2.54</v>
       </c>
       <c r="CT10" t="inlineStr"/>
       <c r="CU10" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="CV10" t="inlineStr"/>
-      <c r="CW10" t="inlineStr"/>
+        <v>1.53</v>
+      </c>
+      <c r="CV10" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="CW10" t="n">
+        <v>2.56</v>
+      </c>
       <c r="CX10" t="n">
         <v>1.21</v>
       </c>
       <c r="CY10" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="CZ10" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
+      </c>
+      <c r="DA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="DC10" t="n">
+        <v>1</v>
+      </c>
+      <c r="DD10" t="n">
+        <v>95.5</v>
+      </c>
+      <c r="DE10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DF10" t="n">
+        <v>4</v>
+      </c>
+      <c r="DG10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="DH10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DI10" t="n">
+        <v>44</v>
+      </c>
+      <c r="DJ10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DK10" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="DL10" t="n">
+        <v>16</v>
+      </c>
+      <c r="DM10" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="DN10" t="n">
+        <v>7</v>
+      </c>
+      <c r="DO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR10" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="DS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT10" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="DU10" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="DV10" t="n">
+        <v>5</v>
+      </c>
+      <c r="DW10" t="n">
+        <v>21</v>
+      </c>
+      <c r="DX10" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="DY10" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -3458,41 +4086,95 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D11" t="n">
         <v>1</v>
       </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
-      <c r="W11" t="inlineStr"/>
-      <c r="X11" t="inlineStr"/>
-      <c r="Y11" t="inlineStr"/>
-      <c r="Z11" t="inlineStr"/>
-      <c r="AA11" t="inlineStr"/>
-      <c r="AB11" t="inlineStr"/>
-      <c r="AC11" t="inlineStr"/>
-      <c r="AD11" t="inlineStr"/>
-      <c r="AE11" t="inlineStr"/>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>4</v>
+      </c>
+      <c r="G11" t="n">
+        <v>5</v>
+      </c>
+      <c r="H11" t="n">
+        <v>111</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>5</v>
+      </c>
+      <c r="K11" t="n">
+        <v>9</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>46</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>4</v>
+      </c>
+      <c r="P11" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>18</v>
+      </c>
+      <c r="R11" t="n">
+        <v>4</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>68</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>19</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>12</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>20</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>3</v>
+      </c>
       <c r="AF11" t="n">
         <v>0</v>
       </c>
@@ -3578,7 +4260,7 @@
         <v>2</v>
       </c>
       <c r="BH11" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BI11" t="n">
         <v>2</v>
@@ -3587,25 +4269,25 @@
         <v>0</v>
       </c>
       <c r="BK11" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="BL11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BM11" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="BN11" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="BO11" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="BP11" t="n">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="BQ11" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BR11" t="n">
         <v>100</v>
@@ -3628,13 +4310,17 @@
       <c r="BX11" t="n">
         <v>0</v>
       </c>
-      <c r="BY11" t="inlineStr"/>
-      <c r="BZ11" t="inlineStr"/>
+      <c r="BY11" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="BZ11" t="n">
+        <v>3.09</v>
+      </c>
       <c r="CA11" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.16</v>
+        <v>3.2</v>
       </c>
       <c r="CC11" t="n">
         <v>2.6</v>
@@ -3643,62 +4329,141 @@
         <v>3.51</v>
       </c>
       <c r="CE11" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.56</v>
+        <v>2.48</v>
       </c>
       <c r="CG11" t="n">
-        <v>3.35</v>
+        <v>3.12</v>
       </c>
       <c r="CH11" t="n">
         <v>1.5</v>
       </c>
       <c r="CI11" t="n">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="CJ11" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="CL11" t="n">
-        <v>1.65</v>
+        <v>1.54</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.95</v>
+        <v>3.22</v>
       </c>
       <c r="CN11" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="CO11" t="n">
         <v>1.19</v>
       </c>
       <c r="CP11" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="CQ11" t="n">
-        <v>2.76</v>
+        <v>2.7</v>
       </c>
       <c r="CR11" t="inlineStr"/>
-      <c r="CS11" t="inlineStr"/>
+      <c r="CS11" t="n">
+        <v>2.6</v>
+      </c>
       <c r="CT11" t="inlineStr"/>
-      <c r="CU11" t="inlineStr"/>
+      <c r="CU11" t="n">
+        <v>1.51</v>
+      </c>
       <c r="CV11" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="CW11" t="n">
-        <v>2.27</v>
+        <v>2.42</v>
       </c>
       <c r="CX11" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="CY11" t="n">
-        <v>2.17</v>
+        <v>1.96</v>
       </c>
       <c r="CZ11" t="n">
-        <v>3.81</v>
+        <v>3.29</v>
+      </c>
+      <c r="DA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB11" t="n">
+        <v>3</v>
+      </c>
+      <c r="DC11" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="DD11" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="DE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF11" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="DG11" t="n">
+        <v>8</v>
+      </c>
+      <c r="DH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI11" t="n">
+        <v>44</v>
+      </c>
+      <c r="DJ11" t="n">
+        <v>1</v>
+      </c>
+      <c r="DK11" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="DL11" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="DM11" t="n">
+        <v>15</v>
+      </c>
+      <c r="DN11" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="DO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR11" t="n">
+        <v>64</v>
+      </c>
+      <c r="DS11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DT11" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="DU11" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="DV11" t="n">
+        <v>4</v>
+      </c>
+      <c r="DW11" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="DX11" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="DY11" t="n">
+        <v>3.5</v>
       </c>
     </row>
     <row r="12">
@@ -3954,6 +4719,31 @@
       <c r="CZ12" t="n">
         <v>3.39</v>
       </c>
+      <c r="DA12" t="inlineStr"/>
+      <c r="DB12" t="inlineStr"/>
+      <c r="DC12" t="inlineStr"/>
+      <c r="DD12" t="inlineStr"/>
+      <c r="DE12" t="inlineStr"/>
+      <c r="DF12" t="inlineStr"/>
+      <c r="DG12" t="inlineStr"/>
+      <c r="DH12" t="inlineStr"/>
+      <c r="DI12" t="inlineStr"/>
+      <c r="DJ12" t="inlineStr"/>
+      <c r="DK12" t="inlineStr"/>
+      <c r="DL12" t="inlineStr"/>
+      <c r="DM12" t="inlineStr"/>
+      <c r="DN12" t="inlineStr"/>
+      <c r="DO12" t="inlineStr"/>
+      <c r="DP12" t="inlineStr"/>
+      <c r="DQ12" t="inlineStr"/>
+      <c r="DR12" t="inlineStr"/>
+      <c r="DS12" t="inlineStr"/>
+      <c r="DT12" t="inlineStr"/>
+      <c r="DU12" t="inlineStr"/>
+      <c r="DV12" t="inlineStr"/>
+      <c r="DW12" t="inlineStr"/>
+      <c r="DX12" t="inlineStr"/>
+      <c r="DY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -4198,6 +4988,31 @@
       <c r="CX13" t="inlineStr"/>
       <c r="CY13" t="inlineStr"/>
       <c r="CZ13" t="inlineStr"/>
+      <c r="DA13" t="inlineStr"/>
+      <c r="DB13" t="inlineStr"/>
+      <c r="DC13" t="inlineStr"/>
+      <c r="DD13" t="inlineStr"/>
+      <c r="DE13" t="inlineStr"/>
+      <c r="DF13" t="inlineStr"/>
+      <c r="DG13" t="inlineStr"/>
+      <c r="DH13" t="inlineStr"/>
+      <c r="DI13" t="inlineStr"/>
+      <c r="DJ13" t="inlineStr"/>
+      <c r="DK13" t="inlineStr"/>
+      <c r="DL13" t="inlineStr"/>
+      <c r="DM13" t="inlineStr"/>
+      <c r="DN13" t="inlineStr"/>
+      <c r="DO13" t="inlineStr"/>
+      <c r="DP13" t="inlineStr"/>
+      <c r="DQ13" t="inlineStr"/>
+      <c r="DR13" t="inlineStr"/>
+      <c r="DS13" t="inlineStr"/>
+      <c r="DT13" t="inlineStr"/>
+      <c r="DU13" t="inlineStr"/>
+      <c r="DV13" t="inlineStr"/>
+      <c r="DW13" t="inlineStr"/>
+      <c r="DX13" t="inlineStr"/>
+      <c r="DY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -4206,41 +5021,95 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D14" t="n">
         <v>1</v>
       </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr"/>
-      <c r="W14" t="inlineStr"/>
-      <c r="X14" t="inlineStr"/>
-      <c r="Y14" t="inlineStr"/>
-      <c r="Z14" t="inlineStr"/>
-      <c r="AA14" t="inlineStr"/>
-      <c r="AB14" t="inlineStr"/>
-      <c r="AC14" t="inlineStr"/>
-      <c r="AD14" t="inlineStr"/>
-      <c r="AE14" t="inlineStr"/>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H14" t="n">
+        <v>134</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>12</v>
+      </c>
+      <c r="L14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="M14" t="n">
+        <v>91</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1</v>
+      </c>
+      <c r="O14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="P14" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>18</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>64</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>18</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>22</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1</v>
+      </c>
       <c r="AF14" t="n">
         <v>0</v>
       </c>
@@ -4323,37 +5192,37 @@
         <v>4</v>
       </c>
       <c r="BG14" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="BH14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="BI14" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="BJ14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BK14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BL14" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="BM14" t="n">
         <v>0</v>
       </c>
       <c r="BN14" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="BO14" t="n">
         <v>2</v>
       </c>
       <c r="BP14" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="BQ14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BR14" t="n">
         <v>100</v>
@@ -4362,7 +5231,7 @@
         <v>100</v>
       </c>
       <c r="BT14" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="BU14" t="n">
         <v>0</v>
@@ -4376,13 +5245,17 @@
       <c r="BX14" t="n">
         <v>0</v>
       </c>
-      <c r="BY14" t="inlineStr"/>
-      <c r="BZ14" t="inlineStr"/>
+      <c r="BY14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BZ14" t="n">
+        <v>1.32</v>
+      </c>
       <c r="CA14" t="n">
-        <v>3.48</v>
+        <v>4.19</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.51</v>
+        <v>4.5</v>
       </c>
       <c r="CC14" t="n">
         <v>3.35</v>
@@ -4391,62 +5264,137 @@
         <v>3.69</v>
       </c>
       <c r="CE14" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="CF14" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="CG14" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="CH14" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="CI14" t="n">
+        <v>2</v>
+      </c>
+      <c r="CJ14" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="CK14" t="n">
         <v>1.36</v>
       </c>
-      <c r="CF14" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="CG14" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="CH14" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="CI14" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="CJ14" t="n">
+      <c r="CL14" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="CM14" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="CN14" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="CO14" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="CP14" t="n">
         <v>1.65</v>
       </c>
-      <c r="CK14" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="CL14" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="CM14" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="CN14" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="CO14" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="CP14" t="n">
-        <v>1.8</v>
-      </c>
       <c r="CQ14" t="n">
-        <v>3.1</v>
+        <v>2.74</v>
       </c>
       <c r="CR14" t="inlineStr"/>
       <c r="CS14" t="inlineStr"/>
       <c r="CT14" t="inlineStr"/>
       <c r="CU14" t="inlineStr"/>
       <c r="CV14" t="n">
-        <v>1.7</v>
+        <v>1.59</v>
       </c>
       <c r="CW14" t="n">
-        <v>2.09</v>
+        <v>2.31</v>
       </c>
       <c r="CX14" t="n">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="CY14" t="n">
-        <v>1.89</v>
+        <v>1.74</v>
       </c>
       <c r="CZ14" t="n">
-        <v>3.15</v>
+        <v>2.81</v>
+      </c>
+      <c r="DA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB14" t="n">
+        <v>2</v>
+      </c>
+      <c r="DC14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DD14" t="n">
+        <v>102</v>
+      </c>
+      <c r="DE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="DG14" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="DH14" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="DI14" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="DJ14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL14" t="n">
+        <v>11</v>
+      </c>
+      <c r="DM14" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="DN14" t="n">
+        <v>6</v>
+      </c>
+      <c r="DO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR14" t="n">
+        <v>55.5</v>
+      </c>
+      <c r="DS14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT14" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="DU14" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="DV14" t="n">
+        <v>6</v>
+      </c>
+      <c r="DW14" t="n">
+        <v>17</v>
+      </c>
+      <c r="DX14" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="DY14" t="n">
+        <v>2.5</v>
       </c>
     </row>
     <row r="15">
@@ -4698,6 +5646,31 @@
       <c r="CZ15" t="n">
         <v>3.14</v>
       </c>
+      <c r="DA15" t="inlineStr"/>
+      <c r="DB15" t="inlineStr"/>
+      <c r="DC15" t="inlineStr"/>
+      <c r="DD15" t="inlineStr"/>
+      <c r="DE15" t="inlineStr"/>
+      <c r="DF15" t="inlineStr"/>
+      <c r="DG15" t="inlineStr"/>
+      <c r="DH15" t="inlineStr"/>
+      <c r="DI15" t="inlineStr"/>
+      <c r="DJ15" t="inlineStr"/>
+      <c r="DK15" t="inlineStr"/>
+      <c r="DL15" t="inlineStr"/>
+      <c r="DM15" t="inlineStr"/>
+      <c r="DN15" t="inlineStr"/>
+      <c r="DO15" t="inlineStr"/>
+      <c r="DP15" t="inlineStr"/>
+      <c r="DQ15" t="inlineStr"/>
+      <c r="DR15" t="inlineStr"/>
+      <c r="DS15" t="inlineStr"/>
+      <c r="DT15" t="inlineStr"/>
+      <c r="DU15" t="inlineStr"/>
+      <c r="DV15" t="inlineStr"/>
+      <c r="DW15" t="inlineStr"/>
+      <c r="DX15" t="inlineStr"/>
+      <c r="DY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -4706,41 +5679,95 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D16" t="n">
         <v>1</v>
       </c>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr"/>
-      <c r="S16" t="inlineStr"/>
-      <c r="T16" t="inlineStr"/>
-      <c r="U16" t="inlineStr"/>
-      <c r="V16" t="inlineStr"/>
-      <c r="W16" t="inlineStr"/>
-      <c r="X16" t="inlineStr"/>
-      <c r="Y16" t="inlineStr"/>
-      <c r="Z16" t="inlineStr"/>
-      <c r="AA16" t="inlineStr"/>
-      <c r="AB16" t="inlineStr"/>
-      <c r="AC16" t="inlineStr"/>
-      <c r="AD16" t="inlineStr"/>
-      <c r="AE16" t="inlineStr"/>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>8</v>
+      </c>
+      <c r="H16" t="n">
+        <v>97</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>8</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>59</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>13</v>
+      </c>
+      <c r="R16" t="n">
+        <v>5</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>51</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>18</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>0</v>
+      </c>
       <c r="AF16" t="n">
         <v>0</v>
       </c>
@@ -4823,49 +5850,49 @@
         <v>2</v>
       </c>
       <c r="BG16" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="BH16" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="BI16" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="BJ16" t="n">
         <v>0</v>
       </c>
       <c r="BK16" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="BL16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BM16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BN16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BO16" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="BP16" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="BQ16" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="BR16" t="n">
         <v>100</v>
       </c>
       <c r="BS16" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BT16" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BU16" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BV16" t="n">
         <v>0</v>
@@ -4874,15 +5901,19 @@
         <v>0</v>
       </c>
       <c r="BX16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY16" t="inlineStr"/>
-      <c r="BZ16" t="inlineStr"/>
+        <v>50</v>
+      </c>
+      <c r="BY16" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="BZ16" t="n">
+        <v>3.1</v>
+      </c>
       <c r="CA16" t="n">
-        <v>3.2</v>
+        <v>3.32</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="CC16" t="n">
         <v>3.5</v>
@@ -4891,66 +5922,145 @@
         <v>3.4</v>
       </c>
       <c r="CE16" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="CF16" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="CG16" t="n">
         <v>2.75</v>
       </c>
-      <c r="CG16" t="n">
+      <c r="CH16" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="CI16" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="CJ16" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="CK16" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="CL16" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="CM16" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="CN16" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="CO16" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="CP16" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="CQ16" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="CR16" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="CS16" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="CT16" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="CU16" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="CV16" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="CW16" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="CX16" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="CY16" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="CZ16" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="DA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB16" t="n">
+        <v>1</v>
+      </c>
+      <c r="DC16" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="DD16" t="n">
+        <v>87</v>
+      </c>
+      <c r="DE16" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DF16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DG16" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="DH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI16" t="n">
+        <v>46</v>
+      </c>
+      <c r="DJ16" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL16" t="n">
+        <v>13</v>
+      </c>
+      <c r="DM16" t="n">
+        <v>14</v>
+      </c>
+      <c r="DN16" t="n">
+        <v>8</v>
+      </c>
+      <c r="DO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR16" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="DS16" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DT16" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="DU16" t="n">
+        <v>4</v>
+      </c>
+      <c r="DV16" t="n">
         <v>2.5</v>
       </c>
-      <c r="CH16" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="CI16" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="CJ16" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="CK16" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="CL16" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="CM16" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="CN16" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="CO16" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="CP16" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="CQ16" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="CR16" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="CS16" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="CT16" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="CU16" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="CV16" t="inlineStr"/>
-      <c r="CW16" t="inlineStr"/>
-      <c r="CX16" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="CY16" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="CZ16" t="n">
-        <v>3.39</v>
+      <c r="DW16" t="n">
+        <v>15</v>
+      </c>
+      <c r="DX16" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="DY16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -4960,13 +6070,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C17" t="n">
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -5049,33 +6159,87 @@
       <c r="AE17" t="n">
         <v>1</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
-      <c r="AG17" t="inlineStr"/>
-      <c r="AH17" t="inlineStr"/>
-      <c r="AI17" t="inlineStr"/>
-      <c r="AJ17" t="inlineStr"/>
-      <c r="AK17" t="inlineStr"/>
-      <c r="AL17" t="inlineStr"/>
-      <c r="AM17" t="inlineStr"/>
-      <c r="AN17" t="inlineStr"/>
-      <c r="AO17" t="inlineStr"/>
-      <c r="AP17" t="inlineStr"/>
-      <c r="AQ17" t="inlineStr"/>
-      <c r="AR17" t="inlineStr"/>
-      <c r="AS17" t="inlineStr"/>
-      <c r="AT17" t="inlineStr"/>
-      <c r="AU17" t="inlineStr"/>
-      <c r="AV17" t="inlineStr"/>
-      <c r="AW17" t="inlineStr"/>
-      <c r="AX17" t="inlineStr"/>
-      <c r="AY17" t="inlineStr"/>
-      <c r="AZ17" t="inlineStr"/>
-      <c r="BA17" t="inlineStr"/>
-      <c r="BB17" t="inlineStr"/>
-      <c r="BC17" t="inlineStr"/>
-      <c r="BD17" t="inlineStr"/>
-      <c r="BE17" t="inlineStr"/>
-      <c r="BF17" t="inlineStr"/>
+      <c r="AF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>66</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>24</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>8</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>18</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>36</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>19</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>3</v>
+      </c>
       <c r="BG17" t="n">
         <v>2</v>
       </c>
@@ -5089,25 +6253,25 @@
         <v>0</v>
       </c>
       <c r="BK17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BL17" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="BM17" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="BN17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BO17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP17" t="n">
-        <v>10</v>
+        <v>4.5</v>
       </c>
       <c r="BQ17" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BR17" t="n">
         <v>100</v>
@@ -5128,7 +6292,7 @@
         <v>0</v>
       </c>
       <c r="BX17" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="BY17" t="n">
         <v>5.21</v>
@@ -5137,65 +6301,150 @@
         <v>5.43</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.88</v>
+        <v>4.39</v>
       </c>
       <c r="CB17" t="n">
-        <v>4.09</v>
-      </c>
-      <c r="CC17" t="inlineStr"/>
-      <c r="CD17" t="inlineStr"/>
+        <v>4.8</v>
+      </c>
+      <c r="CC17" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="CD17" t="n">
+        <v>9.34</v>
+      </c>
       <c r="CE17" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="CF17" t="n">
-        <v>2.49</v>
+        <v>2.37</v>
       </c>
       <c r="CG17" t="n">
-        <v>3.04</v>
+        <v>3.24</v>
       </c>
       <c r="CH17" t="n">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="CI17" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="CJ17" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="CK17" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="CL17" t="n">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.83</v>
+        <v>2.92</v>
       </c>
       <c r="CN17" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="CO17" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="CP17" t="n">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="CQ17" t="n">
-        <v>2.64</v>
+        <v>2.52</v>
       </c>
       <c r="CR17" t="inlineStr"/>
       <c r="CS17" t="inlineStr"/>
       <c r="CT17" t="inlineStr"/>
       <c r="CU17" t="inlineStr"/>
       <c r="CV17" t="n">
-        <v>1.68</v>
+        <v>1.58</v>
       </c>
       <c r="CW17" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="CX17" t="inlineStr"/>
-      <c r="CY17" t="inlineStr"/>
-      <c r="CZ17" t="inlineStr"/>
+        <v>2.33</v>
+      </c>
+      <c r="CX17" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="CY17" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="CZ17" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="DA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB17" t="n">
+        <v>1</v>
+      </c>
+      <c r="DC17" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="DD17" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="DE17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DF17" t="n">
+        <v>2</v>
+      </c>
+      <c r="DG17" t="n">
+        <v>4</v>
+      </c>
+      <c r="DH17" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="DI17" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="DJ17" t="n">
+        <v>1</v>
+      </c>
+      <c r="DK17" t="n">
+        <v>2</v>
+      </c>
+      <c r="DL17" t="n">
+        <v>11</v>
+      </c>
+      <c r="DM17" t="n">
+        <v>9</v>
+      </c>
+      <c r="DN17" t="n">
+        <v>17</v>
+      </c>
+      <c r="DO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR17" t="n">
+        <v>39</v>
+      </c>
+      <c r="DS17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT17" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="DU17" t="n">
+        <v>6</v>
+      </c>
+      <c r="DV17" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="DW17" t="n">
+        <v>20</v>
+      </c>
+      <c r="DX17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="DY17" t="n">
+        <v>2</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/teams/leagues/Averages_Sweden_Allsvenskan_2026.xlsx
+++ b/data/teams/leagues/Averages_Sweden_Allsvenskan_2026.xlsx
@@ -1353,13 +1353,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" t="n">
         <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -1443,52 +1443,52 @@
         <v>2.75</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="AH2" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>92.40000000000001</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>46.2</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP2" t="n">
         <v>3</v>
       </c>
-      <c r="AI2" t="n">
-        <v>94.5</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>48.25</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>3.25</v>
-      </c>
       <c r="AQ2" t="n">
-        <v>11.5</v>
+        <v>12.8</v>
       </c>
       <c r="AR2" t="n">
-        <v>12.25</v>
+        <v>12.2</v>
       </c>
       <c r="AS2" t="n">
-        <v>9.25</v>
+        <v>10.6</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AV2" t="n">
         <v>0</v>
@@ -1500,82 +1500,82 @@
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>53.5</v>
+        <v>52.4</v>
       </c>
       <c r="AZ2" t="n">
         <v>0</v>
       </c>
       <c r="BA2" t="n">
-        <v>11.5</v>
+        <v>11.4</v>
       </c>
       <c r="BB2" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BC2" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BD2" t="n">
-        <v>20</v>
+        <v>19.2</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="BF2" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="BH2" t="n">
-        <v>11.88</v>
+        <v>11.56</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.12</v>
+        <v>1.33</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="BP2" t="n">
-        <v>4.88</v>
+        <v>4.89</v>
       </c>
       <c r="BQ2" t="n">
-        <v>7</v>
+        <v>6.56</v>
       </c>
       <c r="BR2" t="n">
         <v>100</v>
       </c>
       <c r="BS2" t="n">
-        <v>75</v>
+        <v>77.78</v>
       </c>
       <c r="BT2" t="n">
-        <v>50</v>
+        <v>55.56</v>
       </c>
       <c r="BU2" t="n">
-        <v>25</v>
+        <v>22.22</v>
       </c>
       <c r="BV2" t="n">
-        <v>12.5</v>
+        <v>11.11</v>
       </c>
       <c r="BW2" t="n">
-        <v>12.5</v>
+        <v>11.11</v>
       </c>
       <c r="BX2" t="n">
-        <v>75</v>
+        <v>77.78</v>
       </c>
       <c r="BY2" t="n">
         <v>2.06</v>
@@ -1584,34 +1584,34 @@
         <v>2.05</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.39</v>
+        <v>3.56</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.58</v>
+        <v>3.69</v>
       </c>
       <c r="CC2" t="n">
-        <v>2.26</v>
+        <v>3.04</v>
       </c>
       <c r="CD2" t="n">
-        <v>2.32</v>
+        <v>3.11</v>
       </c>
       <c r="CE2" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.77</v>
+        <v>2.72</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.79</v>
+        <v>2.85</v>
       </c>
       <c r="CH2" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="CI2" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="CJ2" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CK2" t="n">
         <v>1.37</v>
@@ -1620,31 +1620,31 @@
         <v>1.71</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="CN2" t="n">
         <v>2.16</v>
       </c>
       <c r="CO2" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="CP2" t="n">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="CQ2" t="n">
-        <v>3.18</v>
+        <v>3.09</v>
       </c>
       <c r="CR2" t="n">
         <v>1.38</v>
       </c>
       <c r="CS2" t="n">
-        <v>2.89</v>
+        <v>2.82</v>
       </c>
       <c r="CT2" t="n">
         <v>3.06</v>
       </c>
       <c r="CU2" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="CV2" t="inlineStr"/>
       <c r="CW2" t="n">
@@ -1655,88 +1655,88 @@
         <v>2.15</v>
       </c>
       <c r="CZ2" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="DA2" t="n">
-        <v>1.98</v>
+        <v>1.93</v>
       </c>
       <c r="DB2" t="n">
-        <v>3.44</v>
+        <v>3.33</v>
       </c>
       <c r="DC2" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DD2" t="n">
-        <v>2.25</v>
+        <v>2.44</v>
       </c>
       <c r="DE2" t="n">
-        <v>4.12</v>
+        <v>3.78</v>
       </c>
       <c r="DF2" t="n">
-        <v>92.12</v>
+        <v>91.22</v>
       </c>
       <c r="DG2" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DH2" t="n">
-        <v>3.12</v>
+        <v>3.22</v>
       </c>
       <c r="DI2" t="n">
-        <v>6.75</v>
+        <v>6.44</v>
       </c>
       <c r="DJ2" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="DK2" t="n">
-        <v>52.62</v>
+        <v>51</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="DM2" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="DN2" t="n">
-        <v>11.38</v>
+        <v>12.11</v>
       </c>
       <c r="DO2" t="n">
         <v>12</v>
       </c>
       <c r="DP2" t="n">
-        <v>7.38</v>
+        <v>8.33</v>
       </c>
       <c r="DQ2" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DR2" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DS2" t="n">
         <v>0</v>
       </c>
       <c r="DT2" t="n">
-        <v>53.75</v>
+        <v>53.11</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>14</v>
+        <v>13.67</v>
       </c>
       <c r="DW2" t="n">
-        <v>8.5</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="DX2" t="n">
-        <v>5.5</v>
+        <v>5.44</v>
       </c>
       <c r="DY2" t="n">
-        <v>22.62</v>
+        <v>21.89</v>
       </c>
       <c r="DZ2" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="EA2" t="n">
-        <v>3.12</v>
+        <v>3.22</v>
       </c>
     </row>
     <row r="3">
@@ -1746,13 +1746,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C3" t="n">
         <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E3" t="n">
         <v>0.33</v>
@@ -1836,52 +1836,52 @@
         <v>2</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AH3" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AI3" t="n">
-        <v>76.8</v>
+        <v>75.83</v>
       </c>
       <c r="AJ3" t="n">
         <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AL3" t="n">
-        <v>3.6</v>
+        <v>4.33</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AN3" t="n">
-        <v>37</v>
+        <v>38.5</v>
       </c>
       <c r="AO3" t="n">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="AP3" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="AQ3" t="n">
-        <v>12.2</v>
+        <v>12</v>
       </c>
       <c r="AR3" t="n">
-        <v>10.8</v>
+        <v>10.33</v>
       </c>
       <c r="AS3" t="n">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AV3" t="n">
         <v>0</v>
@@ -1893,73 +1893,73 @@
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>44.6</v>
+        <v>43.67</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="BA3" t="n">
-        <v>11.2</v>
+        <v>10.67</v>
       </c>
       <c r="BB3" t="n">
-        <v>7.4</v>
+        <v>6.83</v>
       </c>
       <c r="BC3" t="n">
-        <v>3.8</v>
+        <v>3.83</v>
       </c>
       <c r="BD3" t="n">
-        <v>18.4</v>
+        <v>19.33</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="BG3" t="n">
         <v>3</v>
       </c>
       <c r="BH3" t="n">
-        <v>9</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="BI3" t="n">
         <v>3</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="BL3" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="BM3" t="n">
         <v>1</v>
       </c>
       <c r="BN3" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="BO3" t="n">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.75</v>
+        <v>4.89</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4.25</v>
+        <v>4.33</v>
       </c>
       <c r="BR3" t="n">
         <v>100</v>
       </c>
       <c r="BS3" t="n">
-        <v>87.5</v>
+        <v>88.89</v>
       </c>
       <c r="BT3" t="n">
-        <v>75</v>
+        <v>77.78</v>
       </c>
       <c r="BU3" t="n">
-        <v>37.5</v>
+        <v>33.33</v>
       </c>
       <c r="BV3" t="n">
         <v>0</v>
@@ -1968,7 +1968,7 @@
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>62.5</v>
+        <v>66.67</v>
       </c>
       <c r="BY3" t="n">
         <v>2.83</v>
@@ -1977,55 +1977,55 @@
         <v>2.98</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.59</v>
+        <v>3.7</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.7</v>
+        <v>3.81</v>
       </c>
       <c r="CC3" t="n">
-        <v>3.85</v>
+        <v>4.23</v>
       </c>
       <c r="CD3" t="n">
-        <v>3.91</v>
+        <v>4.3</v>
       </c>
       <c r="CE3" t="n">
         <v>1.34</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.99</v>
+        <v>3.05</v>
       </c>
       <c r="CH3" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="CI3" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CK3" t="n">
         <v>1.35</v>
       </c>
       <c r="CL3" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.98</v>
+        <v>2.97</v>
       </c>
       <c r="CN3" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="CO3" t="n">
         <v>1.22</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="CQ3" t="n">
-        <v>2.87</v>
+        <v>2.82</v>
       </c>
       <c r="CR3" t="n">
         <v>1.38</v>
@@ -2048,88 +2048,88 @@
         <v>2.33</v>
       </c>
       <c r="CZ3" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="DB3" t="n">
-        <v>3.07</v>
+        <v>3</v>
       </c>
       <c r="DC3" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="DD3" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="DE3" t="n">
-        <v>1.5</v>
+        <v>1.66</v>
       </c>
       <c r="DF3" t="n">
-        <v>70.88</v>
+        <v>70.89</v>
       </c>
       <c r="DG3" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DH3" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="DI3" t="n">
-        <v>4</v>
+        <v>4.44</v>
       </c>
       <c r="DJ3" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="DK3" t="n">
-        <v>35.12</v>
+        <v>36.33</v>
       </c>
       <c r="DL3" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="DM3" t="n">
-        <v>2.5</v>
+        <v>2.78</v>
       </c>
       <c r="DN3" t="n">
-        <v>10.62</v>
+        <v>10.67</v>
       </c>
       <c r="DO3" t="n">
+        <v>10.66</v>
+      </c>
+      <c r="DP3" t="n">
+        <v>9.109999999999999</v>
+      </c>
+      <c r="DQ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR3" t="n">
+        <v>0</v>
+      </c>
+      <c r="DS3" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT3" t="n">
+        <v>45</v>
+      </c>
+      <c r="DU3" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="DV3" t="n">
         <v>11</v>
       </c>
-      <c r="DP3" t="n">
-        <v>9</v>
-      </c>
-      <c r="DQ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="DR3" t="n">
-        <v>0</v>
-      </c>
-      <c r="DS3" t="n">
-        <v>0</v>
-      </c>
-      <c r="DT3" t="n">
-        <v>45.75</v>
-      </c>
-      <c r="DU3" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="DV3" t="n">
-        <v>11.38</v>
-      </c>
       <c r="DW3" t="n">
-        <v>7.5</v>
+        <v>7.11</v>
       </c>
       <c r="DX3" t="n">
-        <v>3.88</v>
+        <v>3.89</v>
       </c>
       <c r="DY3" t="n">
-        <v>19</v>
+        <v>19.55</v>
       </c>
       <c r="DZ3" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="EA3" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
     </row>
     <row r="4">
@@ -2139,13 +2139,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C4" t="n">
         <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -2232,13 +2232,13 @@
         <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AH4" t="n">
-        <v>1</v>
+        <v>1.75</v>
       </c>
       <c r="AI4" t="n">
-        <v>100</v>
+        <v>101.5</v>
       </c>
       <c r="AJ4" t="n">
         <v>0</v>
@@ -2247,34 +2247,34 @@
         <v>2</v>
       </c>
       <c r="AL4" t="n">
-        <v>3</v>
+        <v>4.25</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AN4" t="n">
-        <v>45.33</v>
+        <v>46.5</v>
       </c>
       <c r="AO4" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AP4" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>9.67</v>
+        <v>10.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>13</v>
+        <v>12.25</v>
       </c>
       <c r="AS4" t="n">
-        <v>9.33</v>
+        <v>9.5</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AV4" t="n">
         <v>0</v>
@@ -2286,82 +2286,82 @@
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>49</v>
+        <v>50.5</v>
       </c>
       <c r="AZ4" t="n">
         <v>0</v>
       </c>
       <c r="BA4" t="n">
-        <v>9.33</v>
+        <v>12.25</v>
       </c>
       <c r="BB4" t="n">
-        <v>5.33</v>
+        <v>6.75</v>
       </c>
       <c r="BC4" t="n">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>16.67</v>
+        <v>18.75</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.21</v>
+        <v>1.5</v>
       </c>
       <c r="BF4" t="n">
         <v>2</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.62</v>
+        <v>2.67</v>
       </c>
       <c r="BH4" t="n">
-        <v>8.119999999999999</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.62</v>
+        <v>2.67</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="BO4" t="n">
         <v>1</v>
       </c>
       <c r="BP4" t="n">
-        <v>4.12</v>
+        <v>4.56</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4</v>
+        <v>4.22</v>
       </c>
       <c r="BR4" t="n">
         <v>100</v>
       </c>
       <c r="BS4" t="n">
-        <v>87.5</v>
+        <v>88.89</v>
       </c>
       <c r="BT4" t="n">
-        <v>50</v>
+        <v>55.56</v>
       </c>
       <c r="BU4" t="n">
-        <v>12.5</v>
+        <v>11.11</v>
       </c>
       <c r="BV4" t="n">
-        <v>12.5</v>
+        <v>11.11</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>62.5</v>
+        <v>66.67</v>
       </c>
       <c r="BY4" t="n">
         <v>3.01</v>
@@ -2373,19 +2373,19 @@
         <v>3.25</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.37</v>
+        <v>3.38</v>
       </c>
       <c r="CC4" t="n">
-        <v>3.13</v>
+        <v>3.35</v>
       </c>
       <c r="CD4" t="n">
-        <v>3.33</v>
+        <v>3.56</v>
       </c>
       <c r="CE4" t="n">
         <v>1.43</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.98</v>
+        <v>3.01</v>
       </c>
       <c r="CG4" t="n">
         <v>2.77</v>
@@ -2394,31 +2394,31 @@
         <v>1.35</v>
       </c>
       <c r="CI4" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="CJ4" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CL4" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="CM4" t="n">
-        <v>3.02</v>
+        <v>2.99</v>
       </c>
       <c r="CN4" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="CO4" t="n">
         <v>1.33</v>
       </c>
       <c r="CP4" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="CQ4" t="n">
-        <v>3.61</v>
+        <v>3.64</v>
       </c>
       <c r="CR4" t="n">
         <v>1.43</v>
@@ -2442,7 +2442,7 @@
         <v>2.56</v>
       </c>
       <c r="CY4" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="CZ4" t="n">
         <v>1.36</v>
@@ -2451,49 +2451,49 @@
         <v>2.17</v>
       </c>
       <c r="DB4" t="n">
-        <v>3.86</v>
+        <v>3.87</v>
       </c>
       <c r="DC4" t="n">
         <v>0</v>
       </c>
       <c r="DD4" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="DE4" t="n">
-        <v>2</v>
+        <v>2.22</v>
       </c>
       <c r="DF4" t="n">
-        <v>91.88</v>
+        <v>93.44</v>
       </c>
       <c r="DG4" t="n">
         <v>0</v>
       </c>
       <c r="DH4" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="DI4" t="n">
-        <v>4</v>
+        <v>4.44</v>
       </c>
       <c r="DJ4" t="n">
-        <v>0</v>
+        <v>0.22</v>
       </c>
       <c r="DK4" t="n">
-        <v>45.12</v>
+        <v>45.67</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DM4" t="n">
-        <v>2</v>
+        <v>2.22</v>
       </c>
       <c r="DN4" t="n">
-        <v>14.75</v>
+        <v>14.56</v>
       </c>
       <c r="DO4" t="n">
-        <v>12.5</v>
+        <v>12.22</v>
       </c>
       <c r="DP4" t="n">
-        <v>8.25</v>
+        <v>8.44</v>
       </c>
       <c r="DQ4" t="n">
         <v>0</v>
@@ -2505,28 +2505,28 @@
         <v>0</v>
       </c>
       <c r="DT4" t="n">
-        <v>48.75</v>
+        <v>49.44</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>10.62</v>
+        <v>11.78</v>
       </c>
       <c r="DW4" t="n">
-        <v>7.75</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="DX4" t="n">
-        <v>2.88</v>
+        <v>3.67</v>
       </c>
       <c r="DY4" t="n">
-        <v>19.88</v>
+        <v>20.44</v>
       </c>
       <c r="DZ4" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="EA4" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
     </row>
     <row r="5">
@@ -2536,61 +2536,61 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D5" t="n">
         <v>3</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="F5" t="n">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="G5" t="n">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="H5" t="n">
-        <v>109.8</v>
+        <v>111.17</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="K5" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="L5" t="n">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="M5" t="n">
-        <v>60.8</v>
+        <v>61</v>
       </c>
       <c r="N5" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="O5" t="n">
-        <v>3</v>
+        <v>2.67</v>
       </c>
       <c r="P5" t="n">
-        <v>15</v>
+        <v>13.83</v>
       </c>
       <c r="Q5" t="n">
-        <v>11.6</v>
+        <v>11.5</v>
       </c>
       <c r="R5" t="n">
-        <v>5.8</v>
+        <v>5.83</v>
       </c>
       <c r="S5" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="T5" t="n">
-        <v>2.4</v>
+        <v>2.17</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -2602,28 +2602,28 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>58</v>
+        <v>58.5</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>16.4</v>
+        <v>16.67</v>
       </c>
       <c r="AA5" t="n">
-        <v>10.8</v>
+        <v>10.83</v>
       </c>
       <c r="AB5" t="n">
-        <v>5.6</v>
+        <v>5.83</v>
       </c>
       <c r="AC5" t="n">
-        <v>20.6</v>
+        <v>18.83</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AF5" t="n">
         <v>0.33</v>
@@ -2707,70 +2707,70 @@
         <v>1.67</v>
       </c>
       <c r="BG5" t="n">
-        <v>3.62</v>
+        <v>3.56</v>
       </c>
       <c r="BH5" t="n">
-        <v>10.62</v>
+        <v>10.67</v>
       </c>
       <c r="BI5" t="n">
-        <v>3.62</v>
+        <v>3.56</v>
       </c>
       <c r="BJ5" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="BK5" t="n">
         <v>1</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="BO5" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="BP5" t="n">
-        <v>4.75</v>
+        <v>4.89</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.88</v>
+        <v>5.78</v>
       </c>
       <c r="BR5" t="n">
         <v>100</v>
       </c>
       <c r="BS5" t="n">
-        <v>75</v>
+        <v>77.78</v>
       </c>
       <c r="BT5" t="n">
-        <v>62.5</v>
+        <v>66.67</v>
       </c>
       <c r="BU5" t="n">
-        <v>50</v>
+        <v>44.44</v>
       </c>
       <c r="BV5" t="n">
-        <v>50</v>
+        <v>44.44</v>
       </c>
       <c r="BW5" t="n">
-        <v>25</v>
+        <v>22.22</v>
       </c>
       <c r="BX5" t="n">
-        <v>62.5</v>
+        <v>66.67</v>
       </c>
       <c r="BY5" t="n">
-        <v>2.11</v>
+        <v>1.98</v>
       </c>
       <c r="BZ5" t="n">
-        <v>2.24</v>
+        <v>2.12</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.42</v>
+        <v>3.55</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.62</v>
+        <v>3.74</v>
       </c>
       <c r="CC5" t="n">
         <v>2.62</v>
@@ -2779,28 +2779,28 @@
         <v>2.89</v>
       </c>
       <c r="CE5" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.63</v>
+        <v>2.59</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.99</v>
+        <v>3.06</v>
       </c>
       <c r="CH5" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CI5" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CK5" t="n">
         <v>1.36</v>
       </c>
       <c r="CL5" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="CM5" t="n">
         <v>2.85</v>
@@ -2812,10 +2812,10 @@
         <v>1.23</v>
       </c>
       <c r="CP5" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="CQ5" t="n">
-        <v>2.96</v>
+        <v>2.89</v>
       </c>
       <c r="CR5" t="n">
         <v>1.38</v>
@@ -2838,52 +2838,52 @@
         <v>2.22</v>
       </c>
       <c r="CZ5" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="DA5" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="DB5" t="n">
-        <v>3.07</v>
+        <v>2.99</v>
       </c>
       <c r="DC5" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="DD5" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="DE5" t="n">
-        <v>3.87</v>
+        <v>3.66</v>
       </c>
       <c r="DF5" t="n">
-        <v>108.12</v>
+        <v>109.22</v>
       </c>
       <c r="DG5" t="n">
         <v>0</v>
       </c>
       <c r="DH5" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="DI5" t="n">
-        <v>7</v>
+        <v>6.56</v>
       </c>
       <c r="DJ5" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="DK5" t="n">
-        <v>54.88</v>
+        <v>55.67</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.75</v>
+        <v>0.66</v>
       </c>
       <c r="DM5" t="n">
-        <v>3.12</v>
+        <v>2.89</v>
       </c>
       <c r="DN5" t="n">
-        <v>12.75</v>
+        <v>12.22</v>
       </c>
       <c r="DO5" t="n">
-        <v>12.5</v>
+        <v>12.33</v>
       </c>
       <c r="DP5" t="n">
         <v>6</v>
@@ -2898,28 +2898,28 @@
         <v>0</v>
       </c>
       <c r="DT5" t="n">
-        <v>57.13</v>
+        <v>57.56</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>16.5</v>
+        <v>16.67</v>
       </c>
       <c r="DW5" t="n">
-        <v>10.5</v>
+        <v>10.55</v>
       </c>
       <c r="DX5" t="n">
-        <v>6</v>
+        <v>6.11</v>
       </c>
       <c r="DY5" t="n">
-        <v>21</v>
+        <v>19.78</v>
       </c>
       <c r="DZ5" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="EA5" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="6">
@@ -2929,94 +2929,94 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D6" t="n">
         <v>4</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="G6" t="n">
-        <v>3</v>
+        <v>2.67</v>
       </c>
       <c r="H6" t="n">
-        <v>82.8</v>
+        <v>87.83</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="K6" t="n">
-        <v>4.2</v>
+        <v>3.67</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>36.2</v>
+        <v>37.17</v>
       </c>
       <c r="N6" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="O6" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="P6" t="n">
-        <v>11.4</v>
+        <v>11.67</v>
       </c>
       <c r="Q6" t="n">
-        <v>7.8</v>
+        <v>7.67</v>
       </c>
       <c r="R6" t="n">
-        <v>9.4</v>
+        <v>9.83</v>
       </c>
       <c r="S6" t="n">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="T6" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="V6" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>40.8</v>
+        <v>40.17</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>12.2</v>
+        <v>11.67</v>
       </c>
       <c r="AA6" t="n">
-        <v>8</v>
+        <v>7.33</v>
       </c>
       <c r="AB6" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="AC6" t="n">
-        <v>17.2</v>
+        <v>17.33</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="AF6" t="n">
         <v>0.25</v>
@@ -3100,49 +3100,49 @@
         <v>2.5</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.33</v>
+        <v>9.1</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="BP6" t="n">
-        <v>3.22</v>
+        <v>3.3</v>
       </c>
       <c r="BQ6" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="BR6" t="n">
         <v>100</v>
       </c>
       <c r="BS6" t="n">
-        <v>88.89</v>
+        <v>90</v>
       </c>
       <c r="BT6" t="n">
-        <v>33.33</v>
+        <v>30</v>
       </c>
       <c r="BU6" t="n">
-        <v>11.11</v>
+        <v>10</v>
       </c>
       <c r="BV6" t="n">
         <v>0</v>
@@ -3151,19 +3151,19 @@
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>66.67</v>
+        <v>70</v>
       </c>
       <c r="BY6" t="n">
-        <v>2.48</v>
+        <v>2.51</v>
       </c>
       <c r="BZ6" t="n">
-        <v>2.4</v>
+        <v>2.47</v>
       </c>
       <c r="CA6" t="n">
         <v>3.22</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.3</v>
+        <v>3.32</v>
       </c>
       <c r="CC6" t="n">
         <v>2.47</v>
@@ -3175,40 +3175,40 @@
         <v>1.4</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="CG6" t="n">
-        <v>2.85</v>
+        <v>2.87</v>
       </c>
       <c r="CH6" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CI6" t="n">
-        <v>2.01</v>
+        <v>2.03</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CL6" t="n">
         <v>1.71</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="CN6" t="n">
-        <v>2.11</v>
+        <v>2.14</v>
       </c>
       <c r="CO6" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="CP6" t="n">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="CQ6" t="n">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="CR6" t="n">
         <v>1.44</v>
@@ -3226,13 +3226,13 @@
         <v>1.49</v>
       </c>
       <c r="CW6" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="CX6" t="n">
         <v>2.5</v>
       </c>
       <c r="CY6" t="n">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="CZ6" t="n">
         <v>1.36</v>
@@ -3244,79 +3244,79 @@
         <v>3.84</v>
       </c>
       <c r="DC6" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="DD6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="DE6" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="DF6" t="n">
+        <v>92.8</v>
+      </c>
+      <c r="DG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH6" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="DI6" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="DJ6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="DK6" t="n">
+        <v>41.6</v>
+      </c>
+      <c r="DL6" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="DM6" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="DN6" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="DO6" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="DP6" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="DQ6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="DR6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="DS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT6" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="DU6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV6" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="DW6" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="DX6" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="DY6" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="DZ6" t="n">
         <v>1.22</v>
       </c>
-      <c r="DE6" t="n">
-        <v>3</v>
-      </c>
-      <c r="DF6" t="n">
-        <v>90.56</v>
-      </c>
-      <c r="DG6" t="n">
-        <v>0</v>
-      </c>
-      <c r="DH6" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="DI6" t="n">
-        <v>4</v>
-      </c>
-      <c r="DJ6" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="DK6" t="n">
-        <v>41.56</v>
-      </c>
-      <c r="DL6" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="DM6" t="n">
-        <v>1</v>
-      </c>
-      <c r="DN6" t="n">
-        <v>11.44</v>
-      </c>
-      <c r="DO6" t="n">
-        <v>10.22</v>
-      </c>
-      <c r="DP6" t="n">
-        <v>8.33</v>
-      </c>
-      <c r="DQ6" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="DR6" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="DS6" t="n">
-        <v>0</v>
-      </c>
-      <c r="DT6" t="n">
-        <v>45.22</v>
-      </c>
-      <c r="DU6" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV6" t="n">
-        <v>10.44</v>
-      </c>
-      <c r="DW6" t="n">
-        <v>7</v>
-      </c>
-      <c r="DX6" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="DY6" t="n">
-        <v>21.11</v>
-      </c>
-      <c r="DZ6" t="n">
-        <v>1.21</v>
-      </c>
       <c r="EA6" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="7">
@@ -3326,13 +3326,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C7" t="n">
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -3419,49 +3419,49 @@
         <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AI7" t="n">
-        <v>106.5</v>
+        <v>107.6</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AK7" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AL7" t="n">
         <v>4</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="AN7" t="n">
-        <v>56.25</v>
+        <v>59.4</v>
       </c>
       <c r="AO7" t="n">
         <v>2</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AQ7" t="n">
-        <v>20.5</v>
+        <v>18.6</v>
       </c>
       <c r="AR7" t="n">
-        <v>10.25</v>
+        <v>10.4</v>
       </c>
       <c r="AS7" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AV7" t="n">
         <v>0</v>
@@ -3473,73 +3473,73 @@
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>54.25</v>
+        <v>54.6</v>
       </c>
       <c r="AZ7" t="n">
         <v>0</v>
       </c>
       <c r="BA7" t="n">
-        <v>11</v>
+        <v>10.6</v>
       </c>
       <c r="BB7" t="n">
-        <v>6.75</v>
+        <v>6.4</v>
       </c>
       <c r="BC7" t="n">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
       <c r="BD7" t="n">
-        <v>21.5</v>
+        <v>22.4</v>
       </c>
       <c r="BE7" t="n">
         <v>1.4</v>
       </c>
       <c r="BF7" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="BH7" t="n">
-        <v>8.56</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.78</v>
+        <v>0.9</v>
       </c>
       <c r="BK7" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="BP7" t="n">
-        <v>4.22</v>
+        <v>4.5</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.33</v>
+        <v>4.3</v>
       </c>
       <c r="BR7" t="n">
-        <v>88.89</v>
+        <v>90</v>
       </c>
       <c r="BS7" t="n">
-        <v>66.67</v>
+        <v>70</v>
       </c>
       <c r="BT7" t="n">
-        <v>44.44</v>
+        <v>50</v>
       </c>
       <c r="BU7" t="n">
-        <v>33.33</v>
+        <v>30</v>
       </c>
       <c r="BV7" t="n">
         <v>0</v>
@@ -3548,7 +3548,7 @@
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>44.44</v>
+        <v>50</v>
       </c>
       <c r="BY7" t="n">
         <v>2.28</v>
@@ -3557,55 +3557,55 @@
         <v>2.24</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.46</v>
+        <v>3.49</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.66</v>
+        <v>3.68</v>
       </c>
       <c r="CC7" t="n">
-        <v>2.87</v>
+        <v>3.15</v>
       </c>
       <c r="CD7" t="n">
-        <v>3.17</v>
+        <v>3.49</v>
       </c>
       <c r="CE7" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CI7" t="n">
         <v>2.07</v>
       </c>
       <c r="CJ7" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="CK7" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="CL7" t="n">
         <v>1.69</v>
       </c>
-      <c r="CK7" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="CL7" t="n">
-        <v>1.68</v>
-      </c>
       <c r="CM7" t="n">
-        <v>3.09</v>
+        <v>3.04</v>
       </c>
       <c r="CN7" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="CO7" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="CP7" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="CQ7" t="n">
-        <v>3.04</v>
+        <v>2.98</v>
       </c>
       <c r="CR7" t="n">
         <v>1.41</v>
@@ -3623,97 +3623,97 @@
         <v>1.47</v>
       </c>
       <c r="CW7" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CX7" t="n">
-        <v>2.55</v>
+        <v>2.57</v>
       </c>
       <c r="CY7" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="CZ7" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="DA7" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="DB7" t="n">
-        <v>3.24</v>
+        <v>3.17</v>
       </c>
       <c r="DC7" t="n">
         <v>0</v>
       </c>
       <c r="DD7" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="DE7" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="DF7" t="n">
-        <v>105.44</v>
+        <v>106.1</v>
       </c>
       <c r="DG7" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DH7" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="DI7" t="n">
-        <v>4.56</v>
+        <v>4.5</v>
       </c>
       <c r="DJ7" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="DK7" t="n">
-        <v>52.78</v>
+        <v>54.7</v>
       </c>
       <c r="DL7" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="DM7" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="DN7" t="n">
-        <v>16.56</v>
+        <v>16</v>
       </c>
       <c r="DO7" t="n">
-        <v>9.890000000000001</v>
+        <v>10</v>
       </c>
       <c r="DP7" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="DQ7" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DR7" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DS7" t="n">
         <v>0</v>
       </c>
       <c r="DT7" t="n">
-        <v>49.33</v>
+        <v>50</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>14.56</v>
+        <v>14</v>
       </c>
       <c r="DW7" t="n">
-        <v>9.56</v>
+        <v>9.1</v>
       </c>
       <c r="DX7" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="DY7" t="n">
-        <v>19.44</v>
+        <v>20.1</v>
       </c>
       <c r="DZ7" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="EA7" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="8">
@@ -3723,10 +3723,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D8" t="n">
         <v>4</v>
@@ -3735,49 +3735,49 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="H8" t="n">
-        <v>89.25</v>
+        <v>89</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="K8" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="M8" t="n">
-        <v>40.25</v>
+        <v>42.8</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="O8" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="P8" t="n">
-        <v>13</v>
+        <v>14.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>12.25</v>
+        <v>12</v>
       </c>
       <c r="R8" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="S8" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="T8" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
@@ -3789,28 +3789,28 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>44</v>
+        <v>45.8</v>
       </c>
       <c r="Y8" t="n">
         <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>10.5</v>
+        <v>12.6</v>
       </c>
       <c r="AA8" t="n">
-        <v>8.5</v>
+        <v>10.2</v>
       </c>
       <c r="AB8" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="AC8" t="n">
-        <v>22.75</v>
+        <v>20.8</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AF8" t="n">
         <v>0.25</v>
@@ -3894,37 +3894,37 @@
         <v>1.5</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="BH8" t="n">
-        <v>9</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="BL8" t="n">
         <v>1</v>
       </c>
       <c r="BM8" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="BN8" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.62</v>
+        <v>4.44</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.25</v>
+        <v>4.33</v>
       </c>
       <c r="BR8" t="n">
         <v>100</v>
@@ -3933,10 +3933,10 @@
         <v>100</v>
       </c>
       <c r="BT8" t="n">
-        <v>37.5</v>
+        <v>33.33</v>
       </c>
       <c r="BU8" t="n">
-        <v>12.5</v>
+        <v>11.11</v>
       </c>
       <c r="BV8" t="n">
         <v>0</v>
@@ -3945,19 +3945,19 @@
         <v>0</v>
       </c>
       <c r="BX8" t="n">
-        <v>62.5</v>
+        <v>55.56</v>
       </c>
       <c r="BY8" t="n">
-        <v>3.14</v>
+        <v>2.91</v>
       </c>
       <c r="BZ8" t="n">
-        <v>3.44</v>
+        <v>3.16</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.81</v>
+        <v>3.77</v>
       </c>
       <c r="CB8" t="n">
-        <v>4.09</v>
+        <v>4.03</v>
       </c>
       <c r="CC8" t="n">
         <v>7.05</v>
@@ -3969,31 +3969,31 @@
         <v>1.38</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.76</v>
+        <v>2.73</v>
       </c>
       <c r="CG8" t="n">
-        <v>2.88</v>
+        <v>2.87</v>
       </c>
       <c r="CH8" t="n">
         <v>1.41</v>
       </c>
       <c r="CI8" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="CK8" t="n">
         <v>1.42</v>
       </c>
       <c r="CL8" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="CN8" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CO8" t="n">
         <v>1.29</v>
@@ -4002,16 +4002,16 @@
         <v>1.93</v>
       </c>
       <c r="CQ8" t="n">
-        <v>3.25</v>
+        <v>3.27</v>
       </c>
       <c r="CR8" t="n">
         <v>1.4</v>
       </c>
       <c r="CS8" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="CT8" t="n">
-        <v>2.98</v>
+        <v>3.01</v>
       </c>
       <c r="CU8" t="n">
         <v>1.44</v>
@@ -4020,64 +4020,64 @@
         <v>1.48</v>
       </c>
       <c r="CW8" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CX8" t="n">
         <v>2.54</v>
       </c>
       <c r="CY8" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="CZ8" t="n">
         <v>1.3</v>
       </c>
       <c r="DA8" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="DB8" t="n">
-        <v>3.42</v>
+        <v>3.38</v>
       </c>
       <c r="DC8" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DD8" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="DE8" t="n">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="DF8" t="n">
-        <v>80.62</v>
+        <v>81.44</v>
       </c>
       <c r="DG8" t="n">
         <v>0</v>
       </c>
       <c r="DH8" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="DI8" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="DJ8" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="DK8" t="n">
-        <v>33.88</v>
+        <v>36</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="DM8" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="DN8" t="n">
-        <v>12.62</v>
+        <v>13.33</v>
       </c>
       <c r="DO8" t="n">
-        <v>11.38</v>
+        <v>11.33</v>
       </c>
       <c r="DP8" t="n">
-        <v>9.880000000000001</v>
+        <v>10</v>
       </c>
       <c r="DQ8" t="n">
         <v>0</v>
@@ -4089,28 +4089,28 @@
         <v>0</v>
       </c>
       <c r="DT8" t="n">
-        <v>39.88</v>
+        <v>41.33</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>11</v>
+        <v>12.11</v>
       </c>
       <c r="DW8" t="n">
-        <v>8.25</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="DX8" t="n">
-        <v>2.75</v>
+        <v>2.89</v>
       </c>
       <c r="DY8" t="n">
-        <v>20.12</v>
+        <v>19.33</v>
       </c>
       <c r="DZ8" t="n">
-        <v>1.14</v>
+        <v>1.23</v>
       </c>
       <c r="EA8" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="9">
@@ -4120,10 +4120,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D9" t="n">
         <v>4</v>
@@ -4132,13 +4132,13 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="G9" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="H9" t="n">
-        <v>117.8</v>
+        <v>111</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -4147,16 +4147,16 @@
         <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>6.8</v>
+        <v>6.5</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6</v>
+        <v>0.83</v>
       </c>
       <c r="M9" t="n">
-        <v>70</v>
+        <v>65.83</v>
       </c>
       <c r="N9" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="O9" t="n">
         <v>3</v>
@@ -4165,46 +4165,46 @@
         <v>12</v>
       </c>
       <c r="Q9" t="n">
-        <v>13.4</v>
+        <v>14.17</v>
       </c>
       <c r="R9" t="n">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="S9" t="n">
-        <v>0.6</v>
+        <v>0.83</v>
       </c>
       <c r="T9" t="n">
-        <v>3.8</v>
+        <v>3.33</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="V9" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>60.8</v>
+        <v>59.33</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>26</v>
+        <v>24.83</v>
       </c>
       <c r="AA9" t="n">
-        <v>16.6</v>
+        <v>16.17</v>
       </c>
       <c r="AB9" t="n">
-        <v>9.4</v>
+        <v>8.67</v>
       </c>
       <c r="AC9" t="n">
-        <v>17.2</v>
+        <v>17.33</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.8</v>
+        <v>2.64</v>
       </c>
       <c r="AE9" t="n">
         <v>1</v>
@@ -4291,70 +4291,70 @@
         <v>1</v>
       </c>
       <c r="BG9" t="n">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="BH9" t="n">
-        <v>7.56</v>
+        <v>7.7</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="BJ9" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="BL9" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.22</v>
+        <v>0.4</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="BP9" t="n">
-        <v>3.67</v>
+        <v>3.8</v>
       </c>
       <c r="BQ9" t="n">
-        <v>3.89</v>
+        <v>3.8</v>
       </c>
       <c r="BR9" t="n">
         <v>100</v>
       </c>
       <c r="BS9" t="n">
-        <v>88.89</v>
+        <v>90</v>
       </c>
       <c r="BT9" t="n">
-        <v>44.44</v>
+        <v>50</v>
       </c>
       <c r="BU9" t="n">
-        <v>22.22</v>
+        <v>20</v>
       </c>
       <c r="BV9" t="n">
-        <v>22.22</v>
+        <v>20</v>
       </c>
       <c r="BW9" t="n">
-        <v>11.11</v>
+        <v>10</v>
       </c>
       <c r="BX9" t="n">
-        <v>44.44</v>
+        <v>50</v>
       </c>
       <c r="BY9" t="n">
         <v>1.47</v>
       </c>
       <c r="BZ9" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="CA9" t="n">
-        <v>4.36</v>
+        <v>4.41</v>
       </c>
       <c r="CB9" t="n">
-        <v>4.76</v>
+        <v>4.74</v>
       </c>
       <c r="CC9" t="n">
         <v>2.12</v>
@@ -4363,13 +4363,13 @@
         <v>2.19</v>
       </c>
       <c r="CE9" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="CG9" t="n">
-        <v>3.27</v>
+        <v>3.28</v>
       </c>
       <c r="CH9" t="n">
         <v>1.54</v>
@@ -4384,28 +4384,28 @@
         <v>1.34</v>
       </c>
       <c r="CL9" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CM9" t="n">
         <v>3</v>
       </c>
       <c r="CN9" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="CO9" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="CP9" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CQ9" t="n">
-        <v>2.57</v>
+        <v>2.55</v>
       </c>
       <c r="CR9" t="n">
         <v>1.34</v>
       </c>
       <c r="CS9" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="CT9" t="n">
         <v>3.35</v>
@@ -4426,85 +4426,85 @@
         <v>2.22</v>
       </c>
       <c r="CZ9" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="DA9" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="DB9" t="n">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="DC9" t="n">
         <v>0</v>
       </c>
       <c r="DD9" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="DE9" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="DF9" t="n">
-        <v>114.56</v>
+        <v>110.8</v>
       </c>
       <c r="DG9" t="n">
         <v>0</v>
       </c>
       <c r="DH9" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="DI9" t="n">
-        <v>5.11</v>
+        <v>5.1</v>
       </c>
       <c r="DJ9" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="DK9" t="n">
-        <v>63.22</v>
+        <v>61.4</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="DM9" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="DN9" t="n">
-        <v>11.22</v>
+        <v>11.3</v>
       </c>
       <c r="DO9" t="n">
-        <v>15.22</v>
+        <v>15.5</v>
       </c>
       <c r="DP9" t="n">
-        <v>5.56</v>
+        <v>5.2</v>
       </c>
       <c r="DQ9" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DR9" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DS9" t="n">
         <v>0</v>
       </c>
       <c r="DT9" t="n">
-        <v>61.67</v>
+        <v>60.7</v>
       </c>
       <c r="DU9" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DV9" t="n">
-        <v>21.33</v>
+        <v>21.1</v>
       </c>
       <c r="DW9" t="n">
-        <v>14.44</v>
+        <v>14.4</v>
       </c>
       <c r="DX9" t="n">
-        <v>6.89</v>
+        <v>6.7</v>
       </c>
       <c r="DY9" t="n">
-        <v>18.78</v>
+        <v>18.7</v>
       </c>
       <c r="DZ9" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="EA9" t="n">
         <v>1</v>
@@ -4517,13 +4517,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E10" t="n">
         <v>0.25</v>
@@ -4613,133 +4613,133 @@
         <v>2</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="AI10" t="n">
-        <v>98.25</v>
+        <v>101.6</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AK10" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AL10" t="n">
         <v>6</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="AN10" t="n">
-        <v>45.25</v>
+        <v>47</v>
       </c>
       <c r="AO10" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AP10" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="AQ10" t="n">
-        <v>13.25</v>
+        <v>12</v>
       </c>
       <c r="AR10" t="n">
-        <v>14.25</v>
+        <v>14</v>
       </c>
       <c r="AS10" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="AT10" t="n">
         <v>1</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AX10" t="n">
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>51.75</v>
+        <v>54</v>
       </c>
       <c r="AZ10" t="n">
         <v>0</v>
       </c>
       <c r="BA10" t="n">
-        <v>15</v>
+        <v>15.6</v>
       </c>
       <c r="BB10" t="n">
-        <v>10.25</v>
+        <v>11</v>
       </c>
       <c r="BC10" t="n">
-        <v>4.75</v>
+        <v>4.6</v>
       </c>
       <c r="BD10" t="n">
-        <v>24</v>
+        <v>24.4</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="BF10" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="BG10" t="n">
-        <v>3.38</v>
+        <v>3.22</v>
       </c>
       <c r="BH10" t="n">
-        <v>10.75</v>
+        <v>10.33</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.38</v>
+        <v>3.22</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="BP10" t="n">
-        <v>6</v>
+        <v>5.78</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.75</v>
+        <v>4.56</v>
       </c>
       <c r="BR10" t="n">
         <v>100</v>
       </c>
       <c r="BS10" t="n">
-        <v>87.5</v>
+        <v>88.89</v>
       </c>
       <c r="BT10" t="n">
-        <v>62.5</v>
+        <v>55.56</v>
       </c>
       <c r="BU10" t="n">
-        <v>50</v>
+        <v>44.44</v>
       </c>
       <c r="BV10" t="n">
-        <v>25</v>
+        <v>22.22</v>
       </c>
       <c r="BW10" t="n">
-        <v>12.5</v>
+        <v>11.11</v>
       </c>
       <c r="BX10" t="n">
-        <v>75</v>
+        <v>77.78</v>
       </c>
       <c r="BY10" t="n">
         <v>2.14</v>
@@ -4748,22 +4748,22 @@
         <v>2.24</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.53</v>
+        <v>3.5</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.66</v>
+        <v>3.65</v>
       </c>
       <c r="CC10" t="n">
-        <v>2.7</v>
+        <v>2.61</v>
       </c>
       <c r="CD10" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="CE10" t="n">
         <v>1.32</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.48</v>
+        <v>2.49</v>
       </c>
       <c r="CG10" t="n">
         <v>3.1</v>
@@ -4772,22 +4772,22 @@
         <v>1.48</v>
       </c>
       <c r="CI10" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="CJ10" t="n">
         <v>1.59</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="CL10" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CM10" t="n">
-        <v>3.29</v>
+        <v>3.3</v>
       </c>
       <c r="CN10" t="n">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="CO10" t="n">
         <v>1.2</v>
@@ -4828,79 +4828,79 @@
         <v>2.73</v>
       </c>
       <c r="DC10" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DD10" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="DE10" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="DF10" t="n">
-        <v>90.75</v>
+        <v>93.44</v>
       </c>
       <c r="DG10" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="DH10" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="DI10" t="n">
-        <v>5.25</v>
+        <v>5.33</v>
       </c>
       <c r="DJ10" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="DK10" t="n">
-        <v>41.88</v>
+        <v>43.22</v>
       </c>
       <c r="DL10" t="n">
         <v>1</v>
       </c>
       <c r="DM10" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="DN10" t="n">
-        <v>12.62</v>
+        <v>12</v>
       </c>
       <c r="DO10" t="n">
-        <v>16.25</v>
+        <v>15.89</v>
       </c>
       <c r="DP10" t="n">
-        <v>7.75</v>
+        <v>7.67</v>
       </c>
       <c r="DQ10" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DR10" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DS10" t="n">
         <v>0</v>
       </c>
       <c r="DT10" t="n">
-        <v>49.75</v>
+        <v>51.22</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>14.25</v>
+        <v>14.67</v>
       </c>
       <c r="DW10" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="DX10" t="n">
-        <v>4.75</v>
+        <v>4.67</v>
       </c>
       <c r="DY10" t="n">
-        <v>20.5</v>
+        <v>21.11</v>
       </c>
       <c r="DZ10" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="EA10" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="11">
@@ -4910,10 +4910,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D11" t="n">
         <v>4</v>
@@ -4922,82 +4922,82 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>2.33</v>
+        <v>3</v>
       </c>
       <c r="G11" t="n">
-        <v>2.67</v>
+        <v>2</v>
       </c>
       <c r="H11" t="n">
-        <v>89.33</v>
+        <v>94.5</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>3</v>
+        <v>3.75</v>
       </c>
       <c r="K11" t="n">
-        <v>5.67</v>
+        <v>4.75</v>
       </c>
       <c r="L11" t="n">
         <v>1</v>
       </c>
       <c r="M11" t="n">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="N11" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="O11" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="P11" t="n">
-        <v>12.67</v>
+        <v>13</v>
       </c>
       <c r="Q11" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R11" t="n">
-        <v>8.33</v>
+        <v>9</v>
       </c>
       <c r="S11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>49.75</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>25.25</v>
+      </c>
+      <c r="AD11" t="n">
         <v>1.67</v>
       </c>
-      <c r="T11" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" t="n">
-        <v>0</v>
-      </c>
-      <c r="W11" t="n">
-        <v>0</v>
-      </c>
-      <c r="X11" t="n">
-        <v>50.33</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>13.67</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>9</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>4.67</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>25.67</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.47</v>
-      </c>
       <c r="AE11" t="n">
-        <v>2.33</v>
+        <v>3.25</v>
       </c>
       <c r="AF11" t="n">
         <v>0</v>
@@ -5081,70 +5081,70 @@
         <v>2.5</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.71</v>
+        <v>2.62</v>
       </c>
       <c r="BH11" t="n">
-        <v>10.43</v>
+        <v>9.75</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.71</v>
+        <v>2.62</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="BL11" t="n">
         <v>1</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="BO11" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="BP11" t="n">
-        <v>5</v>
+        <v>4.88</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.43</v>
+        <v>4.88</v>
       </c>
       <c r="BR11" t="n">
         <v>100</v>
       </c>
       <c r="BS11" t="n">
-        <v>85.70999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="BT11" t="n">
-        <v>28.57</v>
+        <v>25</v>
       </c>
       <c r="BU11" t="n">
-        <v>28.57</v>
+        <v>25</v>
       </c>
       <c r="BV11" t="n">
-        <v>14.29</v>
+        <v>12.5</v>
       </c>
       <c r="BW11" t="n">
-        <v>14.29</v>
+        <v>12.5</v>
       </c>
       <c r="BX11" t="n">
-        <v>42.86</v>
+        <v>50</v>
       </c>
       <c r="BY11" t="n">
-        <v>3.39</v>
+        <v>3.18</v>
       </c>
       <c r="BZ11" t="n">
-        <v>3.78</v>
+        <v>3.46</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.38</v>
+        <v>3.36</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.57</v>
+        <v>3.55</v>
       </c>
       <c r="CC11" t="n">
         <v>2.98</v>
@@ -5153,13 +5153,13 @@
         <v>3.45</v>
       </c>
       <c r="CE11" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="CG11" t="n">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="CH11" t="n">
         <v>1.44</v>
@@ -5168,19 +5168,19 @@
         <v>2.1</v>
       </c>
       <c r="CJ11" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="CL11" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="CM11" t="n">
-        <v>3.1</v>
+        <v>3.06</v>
       </c>
       <c r="CN11" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="CO11" t="n">
         <v>1.23</v>
@@ -5189,7 +5189,7 @@
         <v>1.82</v>
       </c>
       <c r="CQ11" t="n">
-        <v>2.98</v>
+        <v>3.04</v>
       </c>
       <c r="CR11" t="n">
         <v>1.37</v>
@@ -5205,62 +5205,62 @@
       </c>
       <c r="CV11" t="inlineStr"/>
       <c r="CW11" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="CX11" t="inlineStr"/>
       <c r="CY11" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="CZ11" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="DA11" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="DB11" t="n">
-        <v>3.14</v>
+        <v>3.17</v>
       </c>
       <c r="DC11" t="n">
         <v>0</v>
       </c>
       <c r="DD11" t="n">
-        <v>1.86</v>
+        <v>2.25</v>
       </c>
       <c r="DE11" t="n">
-        <v>3</v>
+        <v>2.62</v>
       </c>
       <c r="DF11" t="n">
-        <v>92.86</v>
+        <v>95</v>
       </c>
       <c r="DG11" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DH11" t="n">
-        <v>2.71</v>
+        <v>3.12</v>
       </c>
       <c r="DI11" t="n">
-        <v>5.43</v>
+        <v>5</v>
       </c>
       <c r="DJ11" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="DK11" t="n">
-        <v>41.43</v>
+        <v>45.12</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="DM11" t="n">
-        <v>2.43</v>
+        <v>2.38</v>
       </c>
       <c r="DN11" t="n">
-        <v>11.86</v>
+        <v>12.12</v>
       </c>
       <c r="DO11" t="n">
-        <v>13.71</v>
+        <v>13.5</v>
       </c>
       <c r="DP11" t="n">
-        <v>9.279999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="DQ11" t="n">
         <v>0</v>
@@ -5272,28 +5272,28 @@
         <v>0</v>
       </c>
       <c r="DT11" t="n">
-        <v>53</v>
+        <v>52.38</v>
       </c>
       <c r="DU11" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DV11" t="n">
-        <v>14.14</v>
+        <v>14.75</v>
       </c>
       <c r="DW11" t="n">
-        <v>10.29</v>
+        <v>10.38</v>
       </c>
       <c r="DX11" t="n">
-        <v>3.86</v>
+        <v>4.38</v>
       </c>
       <c r="DY11" t="n">
-        <v>24.72</v>
+        <v>24.62</v>
       </c>
       <c r="DZ11" t="n">
-        <v>1.46</v>
+        <v>1.56</v>
       </c>
       <c r="EA11" t="n">
-        <v>2.43</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="12">
@@ -5303,10 +5303,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D12" t="n">
         <v>4</v>
@@ -5318,46 +5318,46 @@
         <v>1</v>
       </c>
       <c r="G12" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="H12" t="n">
-        <v>101.5</v>
+        <v>96.8</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="K12" t="n">
-        <v>8.75</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="M12" t="n">
-        <v>54.75</v>
+        <v>52.2</v>
       </c>
       <c r="N12" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="O12" t="n">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
       <c r="P12" t="n">
-        <v>11.75</v>
+        <v>11.4</v>
       </c>
       <c r="Q12" t="n">
-        <v>12.75</v>
+        <v>12.8</v>
       </c>
       <c r="R12" t="n">
-        <v>7.75</v>
+        <v>7.6</v>
       </c>
       <c r="S12" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="T12" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
@@ -5369,28 +5369,28 @@
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>52.75</v>
+        <v>51.2</v>
       </c>
       <c r="Y12" t="n">
         <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>14.25</v>
+        <v>14.2</v>
       </c>
       <c r="AA12" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AB12" t="n">
-        <v>5.25</v>
+        <v>5.6</v>
       </c>
       <c r="AC12" t="n">
-        <v>17.75</v>
+        <v>18</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>
@@ -5474,70 +5474,70 @@
         <v>1.25</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="BH12" t="n">
-        <v>11</v>
+        <v>11.33</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="BM12" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="BN12" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.88</v>
+        <v>5.22</v>
       </c>
       <c r="BQ12" t="n">
-        <v>6.12</v>
+        <v>6.11</v>
       </c>
       <c r="BR12" t="n">
         <v>100</v>
       </c>
       <c r="BS12" t="n">
-        <v>62.5</v>
+        <v>66.67</v>
       </c>
       <c r="BT12" t="n">
-        <v>37.5</v>
+        <v>44.44</v>
       </c>
       <c r="BU12" t="n">
-        <v>25</v>
+        <v>22.22</v>
       </c>
       <c r="BV12" t="n">
-        <v>25</v>
+        <v>22.22</v>
       </c>
       <c r="BW12" t="n">
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>50</v>
+        <v>55.56</v>
       </c>
       <c r="BY12" t="n">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="BZ12" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.5</v>
+        <v>3.47</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.69</v>
+        <v>3.66</v>
       </c>
       <c r="CC12" t="n">
         <v>4.59</v>
@@ -5549,40 +5549,40 @@
         <v>1.39</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.76</v>
+        <v>2.81</v>
       </c>
       <c r="CG12" t="n">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
       <c r="CH12" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CI12" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CJ12" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="CL12" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="CM12" t="n">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="CN12" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="CO12" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="CP12" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="CQ12" t="n">
-        <v>3.25</v>
+        <v>3.33</v>
       </c>
       <c r="CR12" t="n">
         <v>1.4</v>
@@ -5600,64 +5600,64 @@
         <v>1.46</v>
       </c>
       <c r="CW12" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CX12" t="n">
         <v>2.59</v>
       </c>
       <c r="CY12" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="CZ12" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="DA12" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="DB12" t="n">
-        <v>3.34</v>
+        <v>3.41</v>
       </c>
       <c r="DC12" t="n">
         <v>0</v>
       </c>
       <c r="DD12" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="DE12" t="n">
-        <v>3.5</v>
+        <v>3.33</v>
       </c>
       <c r="DF12" t="n">
-        <v>95.62</v>
+        <v>93.67</v>
       </c>
       <c r="DG12" t="n">
         <v>0</v>
       </c>
       <c r="DH12" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="DI12" t="n">
-        <v>6.62</v>
+        <v>6.56</v>
       </c>
       <c r="DJ12" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DK12" t="n">
-        <v>52.25</v>
+        <v>51.11</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DM12" t="n">
-        <v>3.12</v>
+        <v>3.22</v>
       </c>
       <c r="DN12" t="n">
-        <v>13</v>
+        <v>12.67</v>
       </c>
       <c r="DO12" t="n">
-        <v>11.12</v>
+        <v>11.33</v>
       </c>
       <c r="DP12" t="n">
-        <v>8.380000000000001</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="DQ12" t="n">
         <v>0</v>
@@ -5669,28 +5669,28 @@
         <v>0</v>
       </c>
       <c r="DT12" t="n">
-        <v>48.62</v>
+        <v>48.22</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>15.75</v>
+        <v>15.56</v>
       </c>
       <c r="DW12" t="n">
-        <v>10.25</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="DX12" t="n">
-        <v>5.5</v>
+        <v>5.67</v>
       </c>
       <c r="DY12" t="n">
-        <v>18.88</v>
+        <v>18.89</v>
       </c>
       <c r="DZ12" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="EA12" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="13">
@@ -5700,10 +5700,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D13" t="n">
         <v>5</v>
@@ -5712,49 +5712,49 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="G13" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="H13" t="n">
-        <v>100.67</v>
+        <v>109</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="K13" t="n">
-        <v>5</v>
+        <v>4.25</v>
       </c>
       <c r="L13" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="M13" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="N13" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="O13" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="P13" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q13" t="n">
-        <v>15.67</v>
+        <v>15</v>
       </c>
       <c r="R13" t="n">
-        <v>7.33</v>
+        <v>7</v>
       </c>
       <c r="S13" t="n">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="T13" t="n">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -5766,28 +5766,28 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>51.67</v>
+        <v>54</v>
       </c>
       <c r="Y13" t="n">
         <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>16</v>
+        <v>14.25</v>
       </c>
       <c r="AA13" t="n">
-        <v>11</v>
+        <v>9.5</v>
       </c>
       <c r="AB13" t="n">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="AC13" t="n">
-        <v>25</v>
+        <v>23.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.74</v>
+        <v>1.64</v>
       </c>
       <c r="AE13" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -5871,70 +5871,70 @@
         <v>2.4</v>
       </c>
       <c r="BG13" t="n">
-        <v>3.5</v>
+        <v>3.67</v>
       </c>
       <c r="BH13" t="n">
-        <v>12</v>
+        <v>11.22</v>
       </c>
       <c r="BI13" t="n">
-        <v>3.5</v>
+        <v>3.67</v>
       </c>
       <c r="BJ13" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.75</v>
+        <v>0.89</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="BP13" t="n">
-        <v>5.62</v>
+        <v>5.11</v>
       </c>
       <c r="BQ13" t="n">
-        <v>6.38</v>
+        <v>6.11</v>
       </c>
       <c r="BR13" t="n">
         <v>100</v>
       </c>
       <c r="BS13" t="n">
-        <v>75</v>
+        <v>77.78</v>
       </c>
       <c r="BT13" t="n">
-        <v>62.5</v>
+        <v>66.67</v>
       </c>
       <c r="BU13" t="n">
-        <v>62.5</v>
+        <v>66.67</v>
       </c>
       <c r="BV13" t="n">
-        <v>50</v>
+        <v>55.56</v>
       </c>
       <c r="BW13" t="n">
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>75</v>
+        <v>77.78</v>
       </c>
       <c r="BY13" t="n">
-        <v>2.23</v>
+        <v>2.1</v>
       </c>
       <c r="BZ13" t="n">
-        <v>2.28</v>
+        <v>2.15</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.55</v>
+        <v>3.56</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.86</v>
+        <v>3.87</v>
       </c>
       <c r="CC13" t="n">
         <v>3.02</v>
@@ -5943,16 +5943,16 @@
         <v>3.6</v>
       </c>
       <c r="CE13" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="CF13" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="CG13" t="n">
-        <v>3.01</v>
+        <v>3.03</v>
       </c>
       <c r="CH13" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="CI13" t="n">
         <v>2.09</v>
@@ -5964,42 +5964,42 @@
         <v>1.32</v>
       </c>
       <c r="CL13" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CM13" t="n">
-        <v>3.03</v>
+        <v>3.04</v>
       </c>
       <c r="CN13" t="n">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="CO13" t="n">
         <v>1.22</v>
       </c>
       <c r="CP13" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CQ13" t="n">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="CR13" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CS13" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="CT13" t="n">
-        <v>3.23</v>
+        <v>3.22</v>
       </c>
       <c r="CU13" t="n">
         <v>1.48</v>
       </c>
       <c r="CV13" t="inlineStr"/>
       <c r="CW13" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CX13" t="inlineStr"/>
       <c r="CY13" t="n">
-        <v>2.19</v>
+        <v>2.22</v>
       </c>
       <c r="CZ13" t="n">
         <v>1.24</v>
@@ -6008,49 +6008,49 @@
         <v>1.78</v>
       </c>
       <c r="DB13" t="n">
-        <v>2.93</v>
+        <v>2.91</v>
       </c>
       <c r="DC13" t="n">
         <v>0</v>
       </c>
       <c r="DD13" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="DE13" t="n">
-        <v>2.62</v>
+        <v>2.44</v>
       </c>
       <c r="DF13" t="n">
-        <v>87.88</v>
+        <v>93</v>
       </c>
       <c r="DG13" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DH13" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="DI13" t="n">
-        <v>5.12</v>
+        <v>4.78</v>
       </c>
       <c r="DJ13" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="DK13" t="n">
-        <v>43.38</v>
+        <v>45.78</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DM13" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="DN13" t="n">
-        <v>12.5</v>
+        <v>13.11</v>
       </c>
       <c r="DO13" t="n">
-        <v>14.25</v>
+        <v>14.11</v>
       </c>
       <c r="DP13" t="n">
-        <v>8.869999999999999</v>
+        <v>8.56</v>
       </c>
       <c r="DQ13" t="n">
         <v>0</v>
@@ -6062,28 +6062,28 @@
         <v>0</v>
       </c>
       <c r="DT13" t="n">
-        <v>50.38</v>
+        <v>51.56</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="DW13" t="n">
-        <v>9.119999999999999</v>
+        <v>8.67</v>
       </c>
       <c r="DX13" t="n">
-        <v>4.38</v>
+        <v>4.33</v>
       </c>
       <c r="DY13" t="n">
-        <v>21.25</v>
+        <v>21</v>
       </c>
       <c r="DZ13" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="EA13" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -6093,13 +6093,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C14" t="n">
         <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E14" t="n">
         <v>0.25</v>
@@ -6183,139 +6183,139 @@
         <v>0.75</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="AG14" t="n">
         <v>2</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AI14" t="n">
-        <v>88.40000000000001</v>
+        <v>86.67</v>
       </c>
       <c r="AJ14" t="n">
         <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AL14" t="n">
         <v>3</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AN14" t="n">
-        <v>38.4</v>
+        <v>37.83</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AQ14" t="n">
-        <v>12.6</v>
+        <v>12.5</v>
       </c>
       <c r="AR14" t="n">
         <v>13</v>
       </c>
       <c r="AS14" t="n">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AV14" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="AW14" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="AX14" t="n">
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>53</v>
+        <v>52.83</v>
       </c>
       <c r="AZ14" t="n">
         <v>0</v>
       </c>
       <c r="BA14" t="n">
-        <v>11.6</v>
+        <v>12</v>
       </c>
       <c r="BB14" t="n">
-        <v>6.2</v>
+        <v>6.67</v>
       </c>
       <c r="BC14" t="n">
-        <v>5.4</v>
+        <v>5.33</v>
       </c>
       <c r="BD14" t="n">
-        <v>17.4</v>
+        <v>17.33</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="BF14" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="BH14" t="n">
-        <v>9.109999999999999</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.44</v>
+        <v>4.4</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4.67</v>
+        <v>4.3</v>
       </c>
       <c r="BR14" t="n">
-        <v>88.89</v>
+        <v>90</v>
       </c>
       <c r="BS14" t="n">
-        <v>77.78</v>
+        <v>80</v>
       </c>
       <c r="BT14" t="n">
-        <v>44.44</v>
+        <v>40</v>
       </c>
       <c r="BU14" t="n">
-        <v>22.22</v>
+        <v>20</v>
       </c>
       <c r="BV14" t="n">
-        <v>22.22</v>
+        <v>20</v>
       </c>
       <c r="BW14" t="n">
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>33.33</v>
+        <v>40</v>
       </c>
       <c r="BY14" t="n">
         <v>1.51</v>
@@ -6324,46 +6324,46 @@
         <v>1.66</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.69</v>
+        <v>3.64</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="CC14" t="n">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="CD14" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="CE14" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.66</v>
+        <v>2.67</v>
       </c>
       <c r="CG14" t="n">
-        <v>3.02</v>
+        <v>2.98</v>
       </c>
       <c r="CH14" t="n">
         <v>1.43</v>
       </c>
       <c r="CI14" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="CJ14" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CK14" t="n">
         <v>1.35</v>
       </c>
       <c r="CL14" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="CN14" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="CO14" t="n">
         <v>1.25</v>
@@ -6372,7 +6372,7 @@
         <v>1.84</v>
       </c>
       <c r="CQ14" t="n">
-        <v>3.11</v>
+        <v>3.14</v>
       </c>
       <c r="CR14" t="n">
         <v>1.4</v>
@@ -6388,11 +6388,11 @@
       </c>
       <c r="CV14" t="inlineStr"/>
       <c r="CW14" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CX14" t="inlineStr"/>
       <c r="CY14" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="CZ14" t="n">
         <v>1.29</v>
@@ -6401,82 +6401,82 @@
         <v>1.93</v>
       </c>
       <c r="DB14" t="n">
-        <v>3.29</v>
+        <v>3.3</v>
       </c>
       <c r="DC14" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="DD14" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="DE14" t="n">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="DF14" t="n">
-        <v>91.56</v>
+        <v>90.2</v>
       </c>
       <c r="DG14" t="n">
         <v>0</v>
       </c>
       <c r="DH14" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="DI14" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="DJ14" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="DK14" t="n">
-        <v>45.22</v>
+        <v>44.2</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="DM14" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="DN14" t="n">
-        <v>12.22</v>
+        <v>12.2</v>
       </c>
       <c r="DO14" t="n">
-        <v>14.33</v>
+        <v>14.2</v>
       </c>
       <c r="DP14" t="n">
-        <v>8.33</v>
+        <v>8.5</v>
       </c>
       <c r="DQ14" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="DR14" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="DS14" t="n">
         <v>0</v>
       </c>
       <c r="DT14" t="n">
-        <v>54</v>
+        <v>53.8</v>
       </c>
       <c r="DU14" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DV14" t="n">
-        <v>12.22</v>
+        <v>12.4</v>
       </c>
       <c r="DW14" t="n">
-        <v>6.89</v>
+        <v>7.1</v>
       </c>
       <c r="DX14" t="n">
-        <v>5.33</v>
+        <v>5.3</v>
       </c>
       <c r="DY14" t="n">
-        <v>18.44</v>
+        <v>18.3</v>
       </c>
       <c r="DZ14" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="EA14" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="15">
@@ -6486,94 +6486,94 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D15" t="n">
         <v>4</v>
       </c>
       <c r="E15" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="G15" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="H15" t="n">
-        <v>101.75</v>
+        <v>100.6</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="K15" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="L15" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="M15" t="n">
-        <v>52.25</v>
+        <v>55.2</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="P15" t="n">
-        <v>10.25</v>
+        <v>10.4</v>
       </c>
       <c r="Q15" t="n">
-        <v>15</v>
+        <v>14.2</v>
       </c>
       <c r="R15" t="n">
-        <v>10.25</v>
+        <v>9</v>
       </c>
       <c r="S15" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="T15" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="U15" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="V15" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>49.25</v>
+        <v>48.2</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="Z15" t="n">
-        <v>16</v>
+        <v>15.8</v>
       </c>
       <c r="AA15" t="n">
-        <v>10.5</v>
+        <v>10.2</v>
       </c>
       <c r="AB15" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AC15" t="n">
         <v>18</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AF15" t="n">
         <v>0</v>
@@ -6657,37 +6657,37 @@
         <v>1.75</v>
       </c>
       <c r="BG15" t="n">
-        <v>3.88</v>
+        <v>3.78</v>
       </c>
       <c r="BH15" t="n">
-        <v>9.880000000000001</v>
+        <v>10</v>
       </c>
       <c r="BI15" t="n">
-        <v>3.88</v>
+        <v>3.78</v>
       </c>
       <c r="BJ15" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="BL15" t="n">
         <v>1</v>
       </c>
-      <c r="BK15" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="BL15" t="n">
-        <v>1.12</v>
-      </c>
       <c r="BM15" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="BN15" t="n">
-        <v>2.12</v>
+        <v>1.89</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="BP15" t="n">
-        <v>5.75</v>
+        <v>5.89</v>
       </c>
       <c r="BQ15" t="n">
-        <v>4.12</v>
+        <v>4.11</v>
       </c>
       <c r="BR15" t="n">
         <v>100</v>
@@ -6696,31 +6696,31 @@
         <v>100</v>
       </c>
       <c r="BT15" t="n">
-        <v>75</v>
+        <v>77.78</v>
       </c>
       <c r="BU15" t="n">
-        <v>62.5</v>
+        <v>55.56</v>
       </c>
       <c r="BV15" t="n">
-        <v>50</v>
+        <v>44.44</v>
       </c>
       <c r="BW15" t="n">
         <v>0</v>
       </c>
       <c r="BX15" t="n">
-        <v>62.5</v>
+        <v>66.67</v>
       </c>
       <c r="BY15" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="BZ15" t="n">
         <v>1.74</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.93</v>
+        <v>3.91</v>
       </c>
       <c r="CB15" t="n">
-        <v>4.33</v>
+        <v>4.28</v>
       </c>
       <c r="CC15" t="n">
         <v>2.43</v>
@@ -6732,10 +6732,10 @@
         <v>1.29</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="CG15" t="n">
-        <v>3.36</v>
+        <v>3.34</v>
       </c>
       <c r="CH15" t="n">
         <v>1.54</v>
@@ -6747,16 +6747,16 @@
         <v>1.61</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="CL15" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="CM15" t="n">
-        <v>3.2</v>
+        <v>3.13</v>
       </c>
       <c r="CN15" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="CO15" t="n">
         <v>1.17</v>
@@ -6765,7 +6765,7 @@
         <v>1.65</v>
       </c>
       <c r="CQ15" t="n">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="CR15" t="n">
         <v>1.34</v>
@@ -6779,13 +6779,17 @@
       <c r="CU15" t="n">
         <v>1.49</v>
       </c>
-      <c r="CV15" t="inlineStr"/>
+      <c r="CV15" t="n">
+        <v>1.46</v>
+      </c>
       <c r="CW15" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="CX15" t="inlineStr"/>
+        <v>1.6</v>
+      </c>
+      <c r="CX15" t="n">
+        <v>2.59</v>
+      </c>
       <c r="CY15" t="n">
-        <v>2.32</v>
+        <v>2.29</v>
       </c>
       <c r="CZ15" t="n">
         <v>1.21</v>
@@ -6797,79 +6801,79 @@
         <v>2.65</v>
       </c>
       <c r="DC15" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="DD15" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="DE15" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="DF15" t="n">
-        <v>87.25</v>
+        <v>88.22</v>
       </c>
       <c r="DG15" t="n">
         <v>0</v>
       </c>
       <c r="DH15" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="DI15" t="n">
-        <v>4.88</v>
+        <v>5.11</v>
       </c>
       <c r="DJ15" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="DK15" t="n">
-        <v>44.12</v>
+        <v>46.67</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="DM15" t="n">
-        <v>3</v>
+        <v>3.22</v>
       </c>
       <c r="DN15" t="n">
-        <v>12.38</v>
+        <v>12.22</v>
       </c>
       <c r="DO15" t="n">
-        <v>15.12</v>
+        <v>14.67</v>
       </c>
       <c r="DP15" t="n">
-        <v>8.380000000000001</v>
+        <v>7.89</v>
       </c>
       <c r="DQ15" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="DR15" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="DS15" t="n">
         <v>0</v>
       </c>
       <c r="DT15" t="n">
-        <v>48.5</v>
+        <v>48</v>
       </c>
       <c r="DU15" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="DV15" t="n">
-        <v>15.12</v>
+        <v>15.11</v>
       </c>
       <c r="DW15" t="n">
-        <v>9.619999999999999</v>
+        <v>9.56</v>
       </c>
       <c r="DX15" t="n">
-        <v>5.5</v>
+        <v>5.56</v>
       </c>
       <c r="DY15" t="n">
-        <v>19.12</v>
+        <v>19</v>
       </c>
       <c r="DZ15" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="EA15" t="n">
-        <v>1.12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -6879,13 +6883,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C16" t="n">
         <v>4</v>
       </c>
       <c r="D16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E16" t="n">
         <v>0.25</v>
@@ -6969,52 +6973,52 @@
         <v>1</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AG16" t="n">
         <v>1</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AI16" t="n">
-        <v>79.25</v>
+        <v>81.8</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AL16" t="n">
-        <v>4.75</v>
+        <v>4.4</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AN16" t="n">
-        <v>34</v>
+        <v>31.8</v>
       </c>
       <c r="AO16" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AP16" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="AQ16" t="n">
-        <v>15.25</v>
+        <v>14.8</v>
       </c>
       <c r="AR16" t="n">
-        <v>11.5</v>
+        <v>12.8</v>
       </c>
       <c r="AS16" t="n">
-        <v>9.75</v>
+        <v>10.2</v>
       </c>
       <c r="AT16" t="n">
         <v>2</v>
       </c>
       <c r="AU16" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="AV16" t="n">
         <v>0</v>
@@ -7026,82 +7030,82 @@
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>44.5</v>
+        <v>43.4</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="BA16" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB16" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BC16" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="BD16" t="n">
-        <v>18.75</v>
+        <v>18</v>
       </c>
       <c r="BE16" t="n">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="BG16" t="n">
-        <v>3.12</v>
+        <v>3.33</v>
       </c>
       <c r="BH16" t="n">
-        <v>11.38</v>
+        <v>10.67</v>
       </c>
       <c r="BI16" t="n">
-        <v>3.12</v>
+        <v>3.33</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="BP16" t="n">
-        <v>5</v>
+        <v>4.56</v>
       </c>
       <c r="BQ16" t="n">
-        <v>6.38</v>
+        <v>6.11</v>
       </c>
       <c r="BR16" t="n">
         <v>100</v>
       </c>
       <c r="BS16" t="n">
-        <v>75</v>
+        <v>77.78</v>
       </c>
       <c r="BT16" t="n">
-        <v>62.5</v>
+        <v>66.67</v>
       </c>
       <c r="BU16" t="n">
-        <v>37.5</v>
+        <v>44.44</v>
       </c>
       <c r="BV16" t="n">
-        <v>25</v>
+        <v>33.33</v>
       </c>
       <c r="BW16" t="n">
-        <v>12.5</v>
+        <v>11.11</v>
       </c>
       <c r="BX16" t="n">
-        <v>62.5</v>
+        <v>66.67</v>
       </c>
       <c r="BY16" t="n">
         <v>2.97</v>
@@ -7113,31 +7117,31 @@
         <v>3.6</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.8</v>
+        <v>3.81</v>
       </c>
       <c r="CC16" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="CD16" t="n">
-        <v>5.19</v>
+        <v>5.06</v>
       </c>
       <c r="CE16" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="CG16" t="n">
-        <v>2.93</v>
+        <v>2.96</v>
       </c>
       <c r="CH16" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CI16" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="CJ16" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CK16" t="n">
         <v>1.32</v>
@@ -7149,87 +7153,87 @@
         <v>3.1</v>
       </c>
       <c r="CN16" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="CO16" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="CP16" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="CQ16" t="n">
-        <v>2.97</v>
+        <v>2.93</v>
       </c>
       <c r="CR16" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="CS16" t="n">
-        <v>2.83</v>
+        <v>2.79</v>
       </c>
       <c r="CT16" t="n">
-        <v>2.99</v>
+        <v>3.03</v>
       </c>
       <c r="CU16" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="CV16" t="inlineStr"/>
       <c r="CW16" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CX16" t="inlineStr"/>
       <c r="CY16" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="CZ16" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="DA16" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="DB16" t="n">
-        <v>3.19</v>
+        <v>3.15</v>
       </c>
       <c r="DC16" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="DD16" t="n">
         <v>1</v>
       </c>
       <c r="DE16" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="DF16" t="n">
-        <v>86.62</v>
+        <v>87.22</v>
       </c>
       <c r="DG16" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DH16" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="DI16" t="n">
-        <v>4.88</v>
+        <v>4.67</v>
       </c>
       <c r="DJ16" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="DK16" t="n">
-        <v>40.88</v>
+        <v>38.89</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="DM16" t="n">
-        <v>2.12</v>
+        <v>1.89</v>
       </c>
       <c r="DN16" t="n">
-        <v>13.5</v>
+        <v>13.44</v>
       </c>
       <c r="DO16" t="n">
-        <v>12.12</v>
+        <v>12.78</v>
       </c>
       <c r="DP16" t="n">
-        <v>8.380000000000001</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="DQ16" t="n">
         <v>0</v>
@@ -7241,28 +7245,28 @@
         <v>0</v>
       </c>
       <c r="DT16" t="n">
-        <v>47.75</v>
+        <v>46.78</v>
       </c>
       <c r="DU16" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DV16" t="n">
-        <v>9.619999999999999</v>
+        <v>9.56</v>
       </c>
       <c r="DW16" t="n">
-        <v>6.5</v>
+        <v>6.44</v>
       </c>
       <c r="DX16" t="n">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
       <c r="DY16" t="n">
-        <v>19</v>
+        <v>18.56</v>
       </c>
       <c r="DZ16" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="EA16" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
     </row>
     <row r="17">
@@ -7272,13 +7276,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C17" t="n">
         <v>3</v>
       </c>
       <c r="D17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -7365,49 +7369,49 @@
         <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AI17" t="n">
-        <v>77.5</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AL17" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="AN17" t="n">
-        <v>31.75</v>
+        <v>32</v>
       </c>
       <c r="AO17" t="n">
         <v>1</v>
       </c>
       <c r="AP17" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AQ17" t="n">
-        <v>14.25</v>
+        <v>13.6</v>
       </c>
       <c r="AR17" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AS17" t="n">
-        <v>14.5</v>
+        <v>13.6</v>
       </c>
       <c r="AT17" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="AU17" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="AV17" t="n">
         <v>0</v>
@@ -7419,61 +7423,61 @@
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>41.25</v>
+        <v>42.4</v>
       </c>
       <c r="AZ17" t="n">
         <v>0</v>
       </c>
       <c r="BA17" t="n">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="BB17" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BC17" t="n">
-        <v>2.5</v>
+        <v>3.4</v>
       </c>
       <c r="BD17" t="n">
-        <v>19.75</v>
+        <v>20.6</v>
       </c>
       <c r="BE17" t="n">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="BF17" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>9.619999999999999</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BL17" t="n">
         <v>1.5</v>
       </c>
-      <c r="BG17" t="n">
-        <v>3.43</v>
-      </c>
-      <c r="BH17" t="n">
-        <v>9.859999999999999</v>
-      </c>
-      <c r="BI17" t="n">
-        <v>3.43</v>
-      </c>
-      <c r="BJ17" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="BK17" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="BL17" t="n">
-        <v>1.57</v>
-      </c>
       <c r="BM17" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="BN17" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="BP17" t="n">
-        <v>5.43</v>
+        <v>5.12</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4.43</v>
+        <v>4.5</v>
       </c>
       <c r="BR17" t="n">
         <v>100</v>
@@ -7482,19 +7486,19 @@
         <v>100</v>
       </c>
       <c r="BT17" t="n">
-        <v>42.86</v>
+        <v>37.5</v>
       </c>
       <c r="BU17" t="n">
-        <v>28.57</v>
+        <v>25</v>
       </c>
       <c r="BV17" t="n">
-        <v>14.29</v>
+        <v>12.5</v>
       </c>
       <c r="BW17" t="n">
-        <v>14.29</v>
+        <v>12.5</v>
       </c>
       <c r="BX17" t="n">
-        <v>57.14</v>
+        <v>50</v>
       </c>
       <c r="BY17" t="n">
         <v>3.89</v>
@@ -7503,61 +7507,61 @@
         <v>4.03</v>
       </c>
       <c r="CA17" t="n">
-        <v>4.66</v>
+        <v>4.5</v>
       </c>
       <c r="CB17" t="n">
-        <v>5.25</v>
+        <v>5.04</v>
       </c>
       <c r="CC17" t="n">
-        <v>8.949999999999999</v>
+        <v>7.82</v>
       </c>
       <c r="CD17" t="n">
-        <v>9.949999999999999</v>
+        <v>8.69</v>
       </c>
       <c r="CE17" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="CF17" t="n">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="CG17" t="n">
-        <v>3.47</v>
+        <v>3.39</v>
       </c>
       <c r="CH17" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="CI17" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CJ17" t="n">
         <v>1.7</v>
       </c>
       <c r="CK17" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="CL17" t="n">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="CM17" t="n">
-        <v>3.17</v>
+        <v>3.1</v>
       </c>
       <c r="CN17" t="n">
-        <v>2.41</v>
+        <v>2.37</v>
       </c>
       <c r="CO17" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="CP17" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="CQ17" t="n">
-        <v>2.43</v>
+        <v>2.55</v>
       </c>
       <c r="CR17" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CS17" t="n">
-        <v>2.81</v>
+        <v>2.78</v>
       </c>
       <c r="CT17" t="n">
         <v>3.15</v>
@@ -7567,95 +7571,95 @@
       </c>
       <c r="CV17" t="inlineStr"/>
       <c r="CW17" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="CX17" t="inlineStr"/>
       <c r="CY17" t="n">
-        <v>2.37</v>
+        <v>2.32</v>
       </c>
       <c r="CZ17" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="DA17" t="n">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="DB17" t="n">
-        <v>2.42</v>
+        <v>2.52</v>
       </c>
       <c r="DC17" t="n">
         <v>0</v>
       </c>
       <c r="DD17" t="n">
-        <v>0.43</v>
+        <v>0.62</v>
       </c>
       <c r="DE17" t="n">
-        <v>1.43</v>
+        <v>1.62</v>
       </c>
       <c r="DF17" t="n">
-        <v>81.70999999999999</v>
+        <v>82.5</v>
       </c>
       <c r="DG17" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DH17" t="n">
-        <v>1.43</v>
+        <v>1.62</v>
       </c>
       <c r="DI17" t="n">
-        <v>3.86</v>
+        <v>4</v>
       </c>
       <c r="DJ17" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="DK17" t="n">
-        <v>37.86</v>
+        <v>37.25</v>
       </c>
       <c r="DL17" t="n">
         <v>1</v>
       </c>
       <c r="DM17" t="n">
-        <v>2.43</v>
+        <v>2.38</v>
       </c>
       <c r="DN17" t="n">
-        <v>12.57</v>
+        <v>12.37</v>
       </c>
       <c r="DO17" t="n">
-        <v>8.710000000000001</v>
+        <v>10</v>
       </c>
       <c r="DP17" t="n">
-        <v>12</v>
+        <v>11.75</v>
       </c>
       <c r="DQ17" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DR17" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DS17" t="n">
         <v>0</v>
       </c>
       <c r="DT17" t="n">
-        <v>45</v>
+        <v>45.25</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>10.14</v>
+        <v>10.75</v>
       </c>
       <c r="DW17" t="n">
-        <v>6.28</v>
+        <v>6.5</v>
       </c>
       <c r="DX17" t="n">
-        <v>3.86</v>
+        <v>4.25</v>
       </c>
       <c r="DY17" t="n">
-        <v>20.43</v>
+        <v>20.87</v>
       </c>
       <c r="DZ17" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="EA17" t="n">
-        <v>1.43</v>
+        <v>1.62</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Sweden_Allsvenskan_2026.xlsx
+++ b/data/teams/leagues/Averages_Sweden_Allsvenskan_2026.xlsx
@@ -1353,10 +1353,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D2" t="n">
         <v>5</v>
@@ -1365,82 +1365,82 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="G2" t="n">
-        <v>5.25</v>
+        <v>5.2</v>
       </c>
       <c r="H2" t="n">
-        <v>89.75</v>
+        <v>93</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="K2" t="n">
-        <v>7.25</v>
+        <v>7.6</v>
       </c>
       <c r="L2" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="M2" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="N2" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="O2" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="P2" t="n">
-        <v>11.25</v>
+        <v>11.4</v>
       </c>
       <c r="Q2" t="n">
-        <v>11.75</v>
+        <v>12</v>
       </c>
       <c r="R2" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="S2" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="T2" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="V2" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>54</v>
+        <v>54.6</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AA2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AB2" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="AC2" t="n">
-        <v>25.25</v>
+        <v>25.8</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="AF2" t="n">
         <v>0.2</v>
@@ -1524,70 +1524,70 @@
         <v>3.6</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="BH2" t="n">
-        <v>11.56</v>
+        <v>11.6</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.78</v>
+        <v>0.9</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="BP2" t="n">
-        <v>4.89</v>
+        <v>5.1</v>
       </c>
       <c r="BQ2" t="n">
-        <v>6.56</v>
+        <v>6.4</v>
       </c>
       <c r="BR2" t="n">
         <v>100</v>
       </c>
       <c r="BS2" t="n">
-        <v>77.78</v>
+        <v>80</v>
       </c>
       <c r="BT2" t="n">
-        <v>55.56</v>
+        <v>60</v>
       </c>
       <c r="BU2" t="n">
-        <v>22.22</v>
+        <v>20</v>
       </c>
       <c r="BV2" t="n">
-        <v>11.11</v>
+        <v>10</v>
       </c>
       <c r="BW2" t="n">
-        <v>11.11</v>
+        <v>10</v>
       </c>
       <c r="BX2" t="n">
-        <v>77.78</v>
+        <v>70</v>
       </c>
       <c r="BY2" t="n">
-        <v>2.06</v>
+        <v>2.26</v>
       </c>
       <c r="BZ2" t="n">
-        <v>2.05</v>
+        <v>2.31</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.56</v>
+        <v>3.54</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.69</v>
+        <v>3.71</v>
       </c>
       <c r="CC2" t="n">
         <v>3.04</v>
@@ -1596,43 +1596,43 @@
         <v>3.11</v>
       </c>
       <c r="CE2" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.72</v>
+        <v>2.67</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="CH2" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CI2" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="CJ2" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CL2" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.85</v>
+        <v>2.89</v>
       </c>
       <c r="CN2" t="n">
-        <v>2.16</v>
+        <v>2.19</v>
       </c>
       <c r="CO2" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="CP2" t="n">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="CQ2" t="n">
-        <v>3.09</v>
+        <v>3.01</v>
       </c>
       <c r="CR2" t="n">
         <v>1.38</v>
@@ -1648,95 +1648,95 @@
       </c>
       <c r="CV2" t="inlineStr"/>
       <c r="CW2" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CX2" t="inlineStr"/>
       <c r="CY2" t="n">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
       <c r="CZ2" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="DA2" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="DB2" t="n">
-        <v>3.33</v>
+        <v>3.26</v>
       </c>
       <c r="DC2" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DD2" t="n">
-        <v>2.44</v>
+        <v>2.6</v>
       </c>
       <c r="DE2" t="n">
-        <v>3.78</v>
+        <v>3.9</v>
       </c>
       <c r="DF2" t="n">
-        <v>91.22</v>
+        <v>92.7</v>
       </c>
       <c r="DG2" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DH2" t="n">
-        <v>3.22</v>
+        <v>3.3</v>
       </c>
       <c r="DI2" t="n">
-        <v>6.44</v>
+        <v>6.7</v>
       </c>
       <c r="DJ2" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="DK2" t="n">
-        <v>51</v>
+        <v>52.6</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="DM2" t="n">
-        <v>2.56</v>
+        <v>2.7</v>
       </c>
       <c r="DN2" t="n">
-        <v>12.11</v>
+        <v>12.1</v>
       </c>
       <c r="DO2" t="n">
-        <v>12</v>
+        <v>12.1</v>
       </c>
       <c r="DP2" t="n">
-        <v>8.33</v>
+        <v>7.9</v>
       </c>
       <c r="DQ2" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DR2" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DS2" t="n">
         <v>0</v>
       </c>
       <c r="DT2" t="n">
-        <v>53.11</v>
+        <v>53.5</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>13.67</v>
+        <v>14.2</v>
       </c>
       <c r="DW2" t="n">
-        <v>8.220000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="DX2" t="n">
-        <v>5.44</v>
+        <v>5.3</v>
       </c>
       <c r="DY2" t="n">
-        <v>21.89</v>
+        <v>22.5</v>
       </c>
       <c r="DZ2" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="EA2" t="n">
-        <v>3.22</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="3">
@@ -1746,13 +1746,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C3" t="n">
         <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E3" t="n">
         <v>0.33</v>
@@ -1836,52 +1836,52 @@
         <v>2</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="AG3" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AI3" t="n">
-        <v>75.83</v>
+        <v>78.86</v>
       </c>
       <c r="AJ3" t="n">
         <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="AL3" t="n">
-        <v>4.33</v>
+        <v>4.43</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AN3" t="n">
-        <v>38.5</v>
+        <v>40.43</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="AP3" t="n">
         <v>3</v>
       </c>
       <c r="AQ3" t="n">
-        <v>12</v>
+        <v>11.43</v>
       </c>
       <c r="AR3" t="n">
-        <v>10.33</v>
+        <v>10.71</v>
       </c>
       <c r="AS3" t="n">
-        <v>9.5</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AV3" t="n">
         <v>0</v>
@@ -1893,73 +1893,73 @@
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>43.67</v>
+        <v>45.71</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="BA3" t="n">
-        <v>10.67</v>
+        <v>11.43</v>
       </c>
       <c r="BB3" t="n">
-        <v>6.83</v>
+        <v>6.86</v>
       </c>
       <c r="BC3" t="n">
-        <v>3.83</v>
+        <v>4.57</v>
       </c>
       <c r="BD3" t="n">
-        <v>19.33</v>
+        <v>20</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.22</v>
+        <v>1.34</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="BG3" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="BH3" t="n">
-        <v>9.220000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="BI3" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="BM3" t="n">
         <v>1</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.89</v>
+        <v>4.9</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="BR3" t="n">
         <v>100</v>
       </c>
       <c r="BS3" t="n">
-        <v>88.89</v>
+        <v>90</v>
       </c>
       <c r="BT3" t="n">
-        <v>77.78</v>
+        <v>80</v>
       </c>
       <c r="BU3" t="n">
-        <v>33.33</v>
+        <v>40</v>
       </c>
       <c r="BV3" t="n">
         <v>0</v>
@@ -1968,7 +1968,7 @@
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>66.67</v>
+        <v>70</v>
       </c>
       <c r="BY3" t="n">
         <v>2.83</v>
@@ -1977,34 +1977,34 @@
         <v>2.98</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.81</v>
+        <v>3.76</v>
       </c>
       <c r="CC3" t="n">
-        <v>4.23</v>
+        <v>4.05</v>
       </c>
       <c r="CD3" t="n">
-        <v>4.3</v>
+        <v>4.17</v>
       </c>
       <c r="CE3" t="n">
         <v>1.34</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.58</v>
+        <v>2.63</v>
       </c>
       <c r="CG3" t="n">
-        <v>3.05</v>
+        <v>3.04</v>
       </c>
       <c r="CH3" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CI3" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CK3" t="n">
         <v>1.35</v>
@@ -2013,90 +2013,90 @@
         <v>1.7</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.97</v>
+        <v>2.94</v>
       </c>
       <c r="CN3" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="CO3" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="CQ3" t="n">
-        <v>2.82</v>
+        <v>2.87</v>
       </c>
       <c r="CR3" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CS3" t="n">
-        <v>2.75</v>
+        <v>2.83</v>
       </c>
       <c r="CT3" t="n">
-        <v>3.08</v>
+        <v>3.01</v>
       </c>
       <c r="CU3" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="CV3" t="inlineStr"/>
       <c r="CW3" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="CX3" t="inlineStr"/>
       <c r="CY3" t="n">
-        <v>2.33</v>
+        <v>2.27</v>
       </c>
       <c r="CZ3" t="n">
         <v>1.26</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="DB3" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="DC3" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="DD3" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="DE3" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="DF3" t="n">
-        <v>70.89</v>
+        <v>73.5</v>
       </c>
       <c r="DG3" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DH3" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="DI3" t="n">
-        <v>4.44</v>
+        <v>4.5</v>
       </c>
       <c r="DJ3" t="n">
-        <v>0.45</v>
+        <v>0.4</v>
       </c>
       <c r="DK3" t="n">
-        <v>36.33</v>
+        <v>37.9</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="DM3" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="DN3" t="n">
-        <v>10.67</v>
+        <v>10.4</v>
       </c>
       <c r="DO3" t="n">
-        <v>10.66</v>
+        <v>10.9</v>
       </c>
       <c r="DP3" t="n">
-        <v>9.109999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="DQ3" t="n">
         <v>0</v>
@@ -2108,28 +2108,28 @@
         <v>0</v>
       </c>
       <c r="DT3" t="n">
-        <v>45</v>
+        <v>46.3</v>
       </c>
       <c r="DU3" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DV3" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="DW3" t="n">
-        <v>7.11</v>
+        <v>7.1</v>
       </c>
       <c r="DX3" t="n">
-        <v>3.89</v>
+        <v>4.4</v>
       </c>
       <c r="DY3" t="n">
-        <v>19.55</v>
+        <v>20</v>
       </c>
       <c r="DZ3" t="n">
-        <v>1.23</v>
+        <v>1.31</v>
       </c>
       <c r="EA3" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="4">
@@ -2139,10 +2139,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D4" t="n">
         <v>4</v>
@@ -2151,49 +2151,49 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="G4" t="n">
-        <v>2.6</v>
+        <v>2.33</v>
       </c>
       <c r="H4" t="n">
-        <v>87</v>
+        <v>86.17</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="K4" t="n">
-        <v>4.6</v>
+        <v>4.33</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>45</v>
+        <v>46.5</v>
       </c>
       <c r="N4" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="O4" t="n">
         <v>2</v>
       </c>
       <c r="P4" t="n">
-        <v>17.8</v>
+        <v>17</v>
       </c>
       <c r="Q4" t="n">
-        <v>12.2</v>
+        <v>11.5</v>
       </c>
       <c r="R4" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="S4" t="n">
         <v>2</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -2205,28 +2205,28 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>48.6</v>
+        <v>47.5</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>11.4</v>
+        <v>11.33</v>
       </c>
       <c r="AA4" t="n">
-        <v>9.199999999999999</v>
+        <v>9.17</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="AC4" t="n">
-        <v>21.8</v>
+        <v>21.67</v>
       </c>
       <c r="AD4" t="n">
         <v>1.2</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="AF4" t="n">
         <v>0</v>
@@ -2310,70 +2310,70 @@
         <v>2</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.67</v>
+        <v>2.8</v>
       </c>
       <c r="BH4" t="n">
-        <v>8.779999999999999</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.67</v>
+        <v>2.8</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="BO4" t="n">
         <v>1</v>
       </c>
       <c r="BP4" t="n">
-        <v>4.56</v>
+        <v>4.6</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.22</v>
+        <v>4.1</v>
       </c>
       <c r="BR4" t="n">
         <v>100</v>
       </c>
       <c r="BS4" t="n">
-        <v>88.89</v>
+        <v>90</v>
       </c>
       <c r="BT4" t="n">
-        <v>55.56</v>
+        <v>60</v>
       </c>
       <c r="BU4" t="n">
-        <v>11.11</v>
+        <v>20</v>
       </c>
       <c r="BV4" t="n">
-        <v>11.11</v>
+        <v>10</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>66.67</v>
+        <v>70</v>
       </c>
       <c r="BY4" t="n">
-        <v>3.01</v>
+        <v>2.89</v>
       </c>
       <c r="BZ4" t="n">
-        <v>3.2</v>
+        <v>3.04</v>
       </c>
       <c r="CA4" t="n">
         <v>3.25</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.38</v>
+        <v>3.37</v>
       </c>
       <c r="CC4" t="n">
         <v>3.35</v>
@@ -2382,22 +2382,22 @@
         <v>3.56</v>
       </c>
       <c r="CE4" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CF4" t="n">
         <v>3.01</v>
       </c>
       <c r="CG4" t="n">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="CH4" t="n">
         <v>1.35</v>
       </c>
       <c r="CI4" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CJ4" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CK4" t="n">
         <v>1.35</v>
@@ -2406,25 +2406,25 @@
         <v>1.69</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.99</v>
+        <v>2.95</v>
       </c>
       <c r="CN4" t="n">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="CO4" t="n">
         <v>1.33</v>
       </c>
       <c r="CP4" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CQ4" t="n">
-        <v>3.64</v>
+        <v>3.61</v>
       </c>
       <c r="CR4" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CS4" t="n">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
       <c r="CT4" t="n">
         <v>2.87</v>
@@ -2436,64 +2436,64 @@
         <v>1.47</v>
       </c>
       <c r="CW4" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CX4" t="n">
         <v>2.56</v>
       </c>
       <c r="CY4" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="CZ4" t="n">
         <v>1.36</v>
       </c>
       <c r="DA4" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="DB4" t="n">
-        <v>3.87</v>
+        <v>3.83</v>
       </c>
       <c r="DC4" t="n">
         <v>0</v>
       </c>
       <c r="DD4" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="DE4" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="DF4" t="n">
-        <v>93.44</v>
+        <v>92.3</v>
       </c>
       <c r="DG4" t="n">
         <v>0</v>
       </c>
       <c r="DH4" t="n">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="DI4" t="n">
-        <v>4.44</v>
+        <v>4.3</v>
       </c>
       <c r="DJ4" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DK4" t="n">
-        <v>45.67</v>
+        <v>46.5</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="DM4" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="DN4" t="n">
-        <v>14.56</v>
+        <v>14.4</v>
       </c>
       <c r="DO4" t="n">
-        <v>12.22</v>
+        <v>11.8</v>
       </c>
       <c r="DP4" t="n">
-        <v>8.44</v>
+        <v>8.6</v>
       </c>
       <c r="DQ4" t="n">
         <v>0</v>
@@ -2505,28 +2505,28 @@
         <v>0</v>
       </c>
       <c r="DT4" t="n">
-        <v>49.44</v>
+        <v>48.7</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>11.78</v>
+        <v>11.7</v>
       </c>
       <c r="DW4" t="n">
-        <v>8.109999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="DX4" t="n">
-        <v>3.67</v>
+        <v>3.5</v>
       </c>
       <c r="DY4" t="n">
-        <v>20.44</v>
+        <v>20.5</v>
       </c>
       <c r="DZ4" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="EA4" t="n">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="5">
@@ -2929,19 +2929,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C6" t="n">
         <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E6" t="n">
         <v>0.33</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="G6" t="n">
         <v>2.67</v>
@@ -2953,7 +2953,7 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="K6" t="n">
         <v>3.67</v>
@@ -3016,133 +3016,133 @@
         <v>1.32</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AG6" t="n">
         <v>2</v>
       </c>
       <c r="AH6" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="AI6" t="n">
-        <v>100.25</v>
+        <v>106.4</v>
       </c>
       <c r="AJ6" t="n">
         <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AL6" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AN6" t="n">
-        <v>48.25</v>
+        <v>46</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AP6" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="AQ6" t="n">
-        <v>11.5</v>
+        <v>11.4</v>
       </c>
       <c r="AR6" t="n">
-        <v>13.25</v>
+        <v>12.6</v>
       </c>
       <c r="AS6" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AW6" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AX6" t="n">
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>50.75</v>
+        <v>50.4</v>
       </c>
       <c r="AZ6" t="n">
         <v>0</v>
       </c>
       <c r="BA6" t="n">
-        <v>8.25</v>
+        <v>8.6</v>
       </c>
       <c r="BB6" t="n">
-        <v>5.75</v>
+        <v>5.8</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="BD6" t="n">
-        <v>26</v>
+        <v>27.2</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="BF6" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.1</v>
+        <v>8.82</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="BP6" t="n">
-        <v>3.3</v>
+        <v>3.18</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.7</v>
+        <v>5.55</v>
       </c>
       <c r="BR6" t="n">
         <v>100</v>
       </c>
       <c r="BS6" t="n">
-        <v>90</v>
+        <v>90.91</v>
       </c>
       <c r="BT6" t="n">
-        <v>30</v>
+        <v>36.36</v>
       </c>
       <c r="BU6" t="n">
-        <v>10</v>
+        <v>18.18</v>
       </c>
       <c r="BV6" t="n">
         <v>0</v>
@@ -3151,7 +3151,7 @@
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>70</v>
+        <v>72.73</v>
       </c>
       <c r="BY6" t="n">
         <v>2.51</v>
@@ -3160,28 +3160,28 @@
         <v>2.47</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.22</v>
+        <v>3.25</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.32</v>
+        <v>3.38</v>
       </c>
       <c r="CC6" t="n">
-        <v>2.47</v>
+        <v>2.32</v>
       </c>
       <c r="CD6" t="n">
-        <v>2.61</v>
+        <v>2.43</v>
       </c>
       <c r="CE6" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.85</v>
+        <v>2.82</v>
       </c>
       <c r="CG6" t="n">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="CH6" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CI6" t="n">
         <v>2.03</v>
@@ -3193,22 +3193,22 @@
         <v>1.38</v>
       </c>
       <c r="CL6" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="CN6" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="CO6" t="n">
         <v>1.28</v>
       </c>
       <c r="CP6" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CQ6" t="n">
-        <v>3.42</v>
+        <v>3.38</v>
       </c>
       <c r="CR6" t="n">
         <v>1.44</v>
@@ -3235,88 +3235,88 @@
         <v>2.23</v>
       </c>
       <c r="CZ6" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="DA6" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="DB6" t="n">
-        <v>3.84</v>
+        <v>3.74</v>
       </c>
       <c r="DC6" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="DD6" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="DE6" t="n">
-        <v>2.8</v>
+        <v>2.73</v>
       </c>
       <c r="DF6" t="n">
-        <v>92.8</v>
+        <v>96.27</v>
       </c>
       <c r="DG6" t="n">
         <v>0</v>
       </c>
       <c r="DH6" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="DI6" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="DJ6" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DK6" t="n">
-        <v>41.6</v>
+        <v>41.18</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="DM6" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="DN6" t="n">
-        <v>11.6</v>
+        <v>11.55</v>
       </c>
       <c r="DO6" t="n">
-        <v>9.9</v>
+        <v>9.91</v>
       </c>
       <c r="DP6" t="n">
-        <v>8.699999999999999</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="DQ6" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="DR6" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="DS6" t="n">
         <v>0</v>
       </c>
       <c r="DT6" t="n">
-        <v>44.4</v>
+        <v>44.82</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>10.3</v>
+        <v>10.27</v>
       </c>
       <c r="DW6" t="n">
-        <v>6.7</v>
+        <v>6.63</v>
       </c>
       <c r="DX6" t="n">
-        <v>3.6</v>
+        <v>3.63</v>
       </c>
       <c r="DY6" t="n">
-        <v>20.8</v>
+        <v>21.82</v>
       </c>
       <c r="DZ6" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="EA6" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
     </row>
     <row r="7">
@@ -3326,94 +3326,94 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D7" t="n">
         <v>5</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="G7" t="n">
-        <v>2.4</v>
+        <v>2.83</v>
       </c>
       <c r="H7" t="n">
-        <v>104.6</v>
+        <v>102.67</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="K7" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="L7" t="n">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="M7" t="n">
-        <v>50</v>
+        <v>46.67</v>
       </c>
       <c r="N7" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="O7" t="n">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="P7" t="n">
-        <v>13.4</v>
+        <v>12.83</v>
       </c>
       <c r="Q7" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="R7" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="T7" t="n">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="V7" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>45.4</v>
+        <v>46.5</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>17.4</v>
+        <v>17.17</v>
       </c>
       <c r="AA7" t="n">
-        <v>11.8</v>
+        <v>11.67</v>
       </c>
       <c r="AB7" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>17.8</v>
+        <v>17.83</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AE7" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AF7" t="n">
         <v>0</v>
@@ -3497,49 +3497,49 @@
         <v>3.2</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="BH7" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.7</v>
+        <v>0.82</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="BO7" t="n">
         <v>1</v>
       </c>
       <c r="BP7" t="n">
-        <v>4.5</v>
+        <v>4.55</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.3</v>
+        <v>4.45</v>
       </c>
       <c r="BR7" t="n">
-        <v>90</v>
+        <v>90.91</v>
       </c>
       <c r="BS7" t="n">
-        <v>70</v>
+        <v>72.73</v>
       </c>
       <c r="BT7" t="n">
-        <v>50</v>
+        <v>54.55</v>
       </c>
       <c r="BU7" t="n">
-        <v>30</v>
+        <v>27.27</v>
       </c>
       <c r="BV7" t="n">
         <v>0</v>
@@ -3548,19 +3548,19 @@
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>50</v>
+        <v>45.45</v>
       </c>
       <c r="BY7" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="BZ7" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="CA7" t="n">
         <v>3.49</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.68</v>
+        <v>3.67</v>
       </c>
       <c r="CC7" t="n">
         <v>3.15</v>
@@ -3572,10 +3572,10 @@
         <v>1.35</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.59</v>
+        <v>2.61</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.98</v>
+        <v>2.97</v>
       </c>
       <c r="CH7" t="n">
         <v>1.44</v>
@@ -3602,10 +3602,10 @@
         <v>1.23</v>
       </c>
       <c r="CP7" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CQ7" t="n">
-        <v>2.98</v>
+        <v>2.99</v>
       </c>
       <c r="CR7" t="n">
         <v>1.41</v>
@@ -3623,13 +3623,13 @@
         <v>1.47</v>
       </c>
       <c r="CW7" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CX7" t="n">
         <v>2.57</v>
       </c>
       <c r="CY7" t="n">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="CZ7" t="n">
         <v>1.28</v>
@@ -3641,79 +3641,79 @@
         <v>3.17</v>
       </c>
       <c r="DC7" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="DD7" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="DE7" t="n">
-        <v>2.3</v>
+        <v>2.54</v>
       </c>
       <c r="DF7" t="n">
-        <v>106.1</v>
+        <v>104.91</v>
       </c>
       <c r="DG7" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DH7" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="DI7" t="n">
-        <v>4.5</v>
+        <v>4.82</v>
       </c>
       <c r="DJ7" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="DK7" t="n">
-        <v>54.7</v>
+        <v>52.46</v>
       </c>
       <c r="DL7" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="DM7" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="DN7" t="n">
-        <v>16</v>
+        <v>15.45</v>
       </c>
       <c r="DO7" t="n">
-        <v>10</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="DP7" t="n">
-        <v>6.9</v>
+        <v>7.18</v>
       </c>
       <c r="DQ7" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DR7" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DS7" t="n">
         <v>0</v>
       </c>
       <c r="DT7" t="n">
-        <v>50</v>
+        <v>50.18</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>14</v>
+        <v>14.18</v>
       </c>
       <c r="DW7" t="n">
-        <v>9.1</v>
+        <v>9.27</v>
       </c>
       <c r="DX7" t="n">
-        <v>4.9</v>
+        <v>4.91</v>
       </c>
       <c r="DY7" t="n">
-        <v>20.1</v>
+        <v>19.91</v>
       </c>
       <c r="DZ7" t="n">
         <v>1.62</v>
       </c>
       <c r="EA7" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
     </row>
     <row r="8">
@@ -3723,13 +3723,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C8" t="n">
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -3795,10 +3795,10 @@
         <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>12.6</v>
+        <v>12.4</v>
       </c>
       <c r="AA8" t="n">
-        <v>10.2</v>
+        <v>10</v>
       </c>
       <c r="AB8" t="n">
         <v>2.4</v>
@@ -3807,58 +3807,58 @@
         <v>20.8</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AE8" t="n">
         <v>1.6</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="AG8" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AI8" t="n">
-        <v>72</v>
+        <v>71.2</v>
       </c>
       <c r="AJ8" t="n">
         <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="AL8" t="n">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.25</v>
+        <v>0.6</v>
       </c>
       <c r="AN8" t="n">
-        <v>27.5</v>
+        <v>31.2</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.25</v>
+        <v>1.8</v>
       </c>
       <c r="AQ8" t="n">
-        <v>12.25</v>
+        <v>12</v>
       </c>
       <c r="AR8" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AS8" t="n">
-        <v>11.75</v>
+        <v>11</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.75</v>
+        <v>2.4</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="AV8" t="n">
         <v>0</v>
@@ -3870,61 +3870,61 @@
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>35.75</v>
+        <v>35.4</v>
       </c>
       <c r="AZ8" t="n">
         <v>0</v>
       </c>
       <c r="BA8" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BB8" t="n">
         <v>8</v>
       </c>
       <c r="BC8" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="BD8" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.44</v>
+        <v>2.9</v>
       </c>
       <c r="BH8" t="n">
-        <v>8.890000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.44</v>
+        <v>2.9</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.22</v>
+        <v>0.4</v>
       </c>
       <c r="BL8" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.44</v>
+        <v>4.6</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="BR8" t="n">
         <v>100</v>
@@ -3933,19 +3933,19 @@
         <v>100</v>
       </c>
       <c r="BT8" t="n">
-        <v>33.33</v>
+        <v>40</v>
       </c>
       <c r="BU8" t="n">
-        <v>11.11</v>
+        <v>20</v>
       </c>
       <c r="BV8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BW8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BX8" t="n">
-        <v>55.56</v>
+        <v>60</v>
       </c>
       <c r="BY8" t="n">
         <v>2.91</v>
@@ -3954,64 +3954,64 @@
         <v>3.16</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.77</v>
+        <v>3.83</v>
       </c>
       <c r="CB8" t="n">
-        <v>4.03</v>
+        <v>4.07</v>
       </c>
       <c r="CC8" t="n">
-        <v>7.05</v>
+        <v>6.8</v>
       </c>
       <c r="CD8" t="n">
-        <v>7.88</v>
+        <v>7.53</v>
       </c>
       <c r="CE8" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.73</v>
+        <v>2.71</v>
       </c>
       <c r="CG8" t="n">
-        <v>2.87</v>
+        <v>2.89</v>
       </c>
       <c r="CH8" t="n">
         <v>1.41</v>
       </c>
       <c r="CI8" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CJ8" t="n">
         <v>1.84</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CL8" t="n">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.61</v>
+        <v>2.65</v>
       </c>
       <c r="CN8" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="CO8" t="n">
         <v>1.29</v>
       </c>
       <c r="CP8" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="CQ8" t="n">
-        <v>3.27</v>
+        <v>3.21</v>
       </c>
       <c r="CR8" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CS8" t="n">
-        <v>2.86</v>
+        <v>2.83</v>
       </c>
       <c r="CT8" t="n">
-        <v>3.01</v>
+        <v>3.05</v>
       </c>
       <c r="CU8" t="n">
         <v>1.44</v>
@@ -4020,64 +4020,64 @@
         <v>1.48</v>
       </c>
       <c r="CW8" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="CX8" t="n">
         <v>2.54</v>
       </c>
       <c r="CY8" t="n">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="CZ8" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="DA8" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="DB8" t="n">
-        <v>3.38</v>
+        <v>3.33</v>
       </c>
       <c r="DC8" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="DD8" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="DE8" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="DF8" t="n">
-        <v>81.44</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="DG8" t="n">
         <v>0</v>
       </c>
       <c r="DH8" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="DI8" t="n">
-        <v>2.56</v>
+        <v>2.8</v>
       </c>
       <c r="DJ8" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="DK8" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="DM8" t="n">
-        <v>1.33</v>
+        <v>1.6</v>
       </c>
       <c r="DN8" t="n">
-        <v>13.33</v>
+        <v>13.1</v>
       </c>
       <c r="DO8" t="n">
-        <v>11.33</v>
+        <v>11.5</v>
       </c>
       <c r="DP8" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="DQ8" t="n">
         <v>0</v>
@@ -4089,28 +4089,28 @@
         <v>0</v>
       </c>
       <c r="DT8" t="n">
-        <v>41.33</v>
+        <v>40.6</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>12.11</v>
+        <v>12.2</v>
       </c>
       <c r="DW8" t="n">
-        <v>9.220000000000001</v>
+        <v>9</v>
       </c>
       <c r="DX8" t="n">
-        <v>2.89</v>
+        <v>3.2</v>
       </c>
       <c r="DY8" t="n">
-        <v>19.33</v>
+        <v>19.4</v>
       </c>
       <c r="DZ8" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="EA8" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="9">
@@ -4120,13 +4120,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C9" t="n">
         <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -4210,52 +4210,52 @@
         <v>1</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AG9" t="n">
         <v>1</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="AI9" t="n">
-        <v>110.5</v>
+        <v>109</v>
       </c>
       <c r="AJ9" t="n">
         <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AL9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AM9" t="n">
         <v>0</v>
       </c>
       <c r="AN9" t="n">
-        <v>54.75</v>
+        <v>58.4</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AQ9" t="n">
-        <v>10.25</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR9" t="n">
-        <v>17.5</v>
+        <v>16.2</v>
       </c>
       <c r="AS9" t="n">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="AV9" t="n">
         <v>0</v>
@@ -4267,82 +4267,82 @@
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>62.75</v>
+        <v>61.4</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="BA9" t="n">
-        <v>15.5</v>
+        <v>15.6</v>
       </c>
       <c r="BB9" t="n">
-        <v>11.75</v>
+        <v>11.2</v>
       </c>
       <c r="BC9" t="n">
-        <v>3.75</v>
+        <v>4.4</v>
       </c>
       <c r="BD9" t="n">
-        <v>20.75</v>
+        <v>19.8</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.64</v>
+        <v>1.72</v>
       </c>
       <c r="BF9" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="BG9" t="n">
-        <v>3.2</v>
+        <v>3.36</v>
       </c>
       <c r="BH9" t="n">
-        <v>7.7</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.2</v>
+        <v>3.36</v>
       </c>
       <c r="BJ9" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.3</v>
+        <v>0.45</v>
       </c>
       <c r="BL9" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="BP9" t="n">
-        <v>3.8</v>
+        <v>3.82</v>
       </c>
       <c r="BQ9" t="n">
-        <v>3.8</v>
+        <v>4.45</v>
       </c>
       <c r="BR9" t="n">
         <v>100</v>
       </c>
       <c r="BS9" t="n">
-        <v>90</v>
+        <v>90.91</v>
       </c>
       <c r="BT9" t="n">
-        <v>50</v>
+        <v>54.55</v>
       </c>
       <c r="BU9" t="n">
-        <v>20</v>
+        <v>27.27</v>
       </c>
       <c r="BV9" t="n">
-        <v>20</v>
+        <v>27.27</v>
       </c>
       <c r="BW9" t="n">
-        <v>10</v>
+        <v>9.09</v>
       </c>
       <c r="BX9" t="n">
-        <v>50</v>
+        <v>54.55</v>
       </c>
       <c r="BY9" t="n">
         <v>1.47</v>
@@ -4351,13 +4351,13 @@
         <v>1.45</v>
       </c>
       <c r="CA9" t="n">
-        <v>4.41</v>
+        <v>4.34</v>
       </c>
       <c r="CB9" t="n">
-        <v>4.74</v>
+        <v>4.65</v>
       </c>
       <c r="CC9" t="n">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="CD9" t="n">
         <v>2.19</v>
@@ -4366,7 +4366,7 @@
         <v>1.29</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="CG9" t="n">
         <v>3.28</v>
@@ -4375,10 +4375,10 @@
         <v>1.54</v>
       </c>
       <c r="CI9" t="n">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="CK9" t="n">
         <v>1.34</v>
@@ -4387,7 +4387,7 @@
         <v>1.68</v>
       </c>
       <c r="CM9" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="CN9" t="n">
         <v>2.24</v>
@@ -4399,31 +4399,31 @@
         <v>1.62</v>
       </c>
       <c r="CQ9" t="n">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="CR9" t="n">
         <v>1.34</v>
       </c>
       <c r="CS9" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="CT9" t="n">
         <v>3.35</v>
       </c>
       <c r="CU9" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CV9" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CW9" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="CX9" t="n">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="CY9" t="n">
-        <v>2.22</v>
+        <v>2.19</v>
       </c>
       <c r="CZ9" t="n">
         <v>1.2</v>
@@ -4435,79 +4435,79 @@
         <v>2.63</v>
       </c>
       <c r="DC9" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="DD9" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="DE9" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="DF9" t="n">
-        <v>110.8</v>
+        <v>110.09</v>
       </c>
       <c r="DG9" t="n">
         <v>0</v>
       </c>
       <c r="DH9" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="DI9" t="n">
-        <v>5.1</v>
+        <v>5.36</v>
       </c>
       <c r="DJ9" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="DK9" t="n">
-        <v>61.4</v>
+        <v>62.45</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="DM9" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="DN9" t="n">
-        <v>11.3</v>
+        <v>11</v>
       </c>
       <c r="DO9" t="n">
-        <v>15.5</v>
+        <v>15.09</v>
       </c>
       <c r="DP9" t="n">
-        <v>5.2</v>
+        <v>5.91</v>
       </c>
       <c r="DQ9" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DR9" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DS9" t="n">
         <v>0</v>
       </c>
       <c r="DT9" t="n">
-        <v>60.7</v>
+        <v>60.27</v>
       </c>
       <c r="DU9" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DV9" t="n">
-        <v>21.1</v>
+        <v>20.63</v>
       </c>
       <c r="DW9" t="n">
-        <v>14.4</v>
+        <v>13.91</v>
       </c>
       <c r="DX9" t="n">
-        <v>6.7</v>
+        <v>6.73</v>
       </c>
       <c r="DY9" t="n">
-        <v>18.7</v>
+        <v>18.45</v>
       </c>
       <c r="DZ9" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="EA9" t="n">
-        <v>1</v>
+        <v>1.09</v>
       </c>
     </row>
     <row r="10">
@@ -4517,94 +4517,94 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D10" t="n">
         <v>5</v>
       </c>
       <c r="E10" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="F10" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="G10" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="H10" t="n">
-        <v>83.25</v>
+        <v>81.2</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="K10" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="L10" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="M10" t="n">
-        <v>38.5</v>
+        <v>37.4</v>
       </c>
       <c r="N10" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="O10" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="P10" t="n">
-        <v>12</v>
+        <v>11.8</v>
       </c>
       <c r="Q10" t="n">
-        <v>18.25</v>
+        <v>16</v>
       </c>
       <c r="R10" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="S10" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="T10" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>47.75</v>
+        <v>47</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>13.5</v>
+        <v>14.8</v>
       </c>
       <c r="AA10" t="n">
-        <v>8.75</v>
+        <v>9.6</v>
       </c>
       <c r="AB10" t="n">
-        <v>4.75</v>
+        <v>5.2</v>
       </c>
       <c r="AC10" t="n">
-        <v>17</v>
+        <v>15.4</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AF10" t="n">
         <v>0</v>
@@ -4688,70 +4688,70 @@
         <v>3.2</v>
       </c>
       <c r="BG10" t="n">
-        <v>3.22</v>
+        <v>3.4</v>
       </c>
       <c r="BH10" t="n">
-        <v>10.33</v>
+        <v>10.8</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.22</v>
+        <v>3.4</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="BP10" t="n">
-        <v>5.78</v>
+        <v>5.6</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.56</v>
+        <v>5.2</v>
       </c>
       <c r="BR10" t="n">
         <v>100</v>
       </c>
       <c r="BS10" t="n">
-        <v>88.89</v>
+        <v>90</v>
       </c>
       <c r="BT10" t="n">
-        <v>55.56</v>
+        <v>60</v>
       </c>
       <c r="BU10" t="n">
-        <v>44.44</v>
+        <v>50</v>
       </c>
       <c r="BV10" t="n">
-        <v>22.22</v>
+        <v>30</v>
       </c>
       <c r="BW10" t="n">
-        <v>11.11</v>
+        <v>10</v>
       </c>
       <c r="BX10" t="n">
-        <v>77.78</v>
+        <v>80</v>
       </c>
       <c r="BY10" t="n">
-        <v>2.14</v>
+        <v>2.28</v>
       </c>
       <c r="BZ10" t="n">
-        <v>2.24</v>
+        <v>2.4</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.5</v>
+        <v>3.51</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.65</v>
+        <v>3.66</v>
       </c>
       <c r="CC10" t="n">
         <v>2.61</v>
@@ -4763,60 +4763,64 @@
         <v>1.32</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.49</v>
+        <v>2.47</v>
       </c>
       <c r="CG10" t="n">
-        <v>3.1</v>
+        <v>3.12</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="CI10" t="n">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="CL10" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="CM10" t="n">
-        <v>3.3</v>
+        <v>3.23</v>
       </c>
       <c r="CN10" t="n">
-        <v>2.48</v>
+        <v>2.45</v>
       </c>
       <c r="CO10" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="CP10" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="CQ10" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="CR10" t="n">
         <v>1.37</v>
       </c>
       <c r="CS10" t="n">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="CT10" t="n">
         <v>3.14</v>
       </c>
       <c r="CU10" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="CV10" t="inlineStr"/>
+        <v>1.51</v>
+      </c>
+      <c r="CV10" t="n">
+        <v>1.45</v>
+      </c>
       <c r="CW10" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="CX10" t="inlineStr"/>
+        <v>1.53</v>
+      </c>
+      <c r="CX10" t="n">
+        <v>2.6</v>
+      </c>
       <c r="CY10" t="n">
-        <v>2.49</v>
+        <v>2.41</v>
       </c>
       <c r="CZ10" t="n">
         <v>1.22</v>
@@ -4828,79 +4832,79 @@
         <v>2.73</v>
       </c>
       <c r="DC10" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DD10" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="DE10" t="n">
-        <v>2.33</v>
+        <v>2.6</v>
       </c>
       <c r="DF10" t="n">
-        <v>93.44</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="DG10" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DH10" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="DI10" t="n">
-        <v>5.33</v>
+        <v>5.5</v>
       </c>
       <c r="DJ10" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="DK10" t="n">
-        <v>43.22</v>
+        <v>42.2</v>
       </c>
       <c r="DL10" t="n">
         <v>1</v>
       </c>
       <c r="DM10" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="DN10" t="n">
-        <v>12</v>
+        <v>11.9</v>
       </c>
       <c r="DO10" t="n">
-        <v>15.89</v>
+        <v>15</v>
       </c>
       <c r="DP10" t="n">
-        <v>7.67</v>
+        <v>7.8</v>
       </c>
       <c r="DQ10" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="DR10" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="DS10" t="n">
         <v>0</v>
       </c>
       <c r="DT10" t="n">
-        <v>51.22</v>
+        <v>50.5</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>14.67</v>
+        <v>15.2</v>
       </c>
       <c r="DW10" t="n">
-        <v>10</v>
+        <v>10.3</v>
       </c>
       <c r="DX10" t="n">
-        <v>4.67</v>
+        <v>4.9</v>
       </c>
       <c r="DY10" t="n">
-        <v>21.11</v>
+        <v>19.9</v>
       </c>
       <c r="DZ10" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="EA10" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="11">
@@ -4910,13 +4914,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C11" t="n">
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -5000,139 +5004,139 @@
         <v>3.25</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AH11" t="n">
-        <v>3.25</v>
+        <v>2.33</v>
       </c>
       <c r="AI11" t="n">
-        <v>95.5</v>
+        <v>93.83</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.25</v>
+        <v>0.17</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.5</v>
+        <v>2.17</v>
       </c>
       <c r="AL11" t="n">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="AM11" t="n">
         <v>0</v>
       </c>
       <c r="AN11" t="n">
-        <v>43.25</v>
+        <v>42.5</v>
       </c>
       <c r="AO11" t="n">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="AP11" t="n">
         <v>2</v>
       </c>
       <c r="AQ11" t="n">
-        <v>11.25</v>
+        <v>12.17</v>
       </c>
       <c r="AR11" t="n">
-        <v>12</v>
+        <v>11.33</v>
       </c>
       <c r="AS11" t="n">
+        <v>8.67</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>52.33</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>15.67</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>11.17</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>21.67</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BH11" t="n">
         <v>10</v>
       </c>
-      <c r="AT11" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>55</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>11.25</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>24</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="BH11" t="n">
-        <v>9.75</v>
-      </c>
       <c r="BI11" t="n">
-        <v>2.62</v>
+        <v>3.5</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.62</v>
+        <v>0.8</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.25</v>
+        <v>0.8</v>
       </c>
       <c r="BL11" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="BO11" t="n">
-        <v>0.88</v>
+        <v>1.6</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.88</v>
+        <v>4.8</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.88</v>
+        <v>4.5</v>
       </c>
       <c r="BR11" t="n">
         <v>100</v>
       </c>
       <c r="BS11" t="n">
-        <v>87.5</v>
+        <v>90</v>
       </c>
       <c r="BT11" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="BU11" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="BV11" t="n">
-        <v>12.5</v>
+        <v>30</v>
       </c>
       <c r="BW11" t="n">
-        <v>12.5</v>
+        <v>20</v>
       </c>
       <c r="BX11" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="BY11" t="n">
         <v>3.18</v>
@@ -5144,22 +5148,22 @@
         <v>3.36</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.55</v>
+        <v>3.58</v>
       </c>
       <c r="CC11" t="n">
-        <v>2.98</v>
+        <v>2.72</v>
       </c>
       <c r="CD11" t="n">
-        <v>3.45</v>
+        <v>3.04</v>
       </c>
       <c r="CE11" t="n">
         <v>1.37</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="CG11" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="CH11" t="n">
         <v>1.44</v>
@@ -5171,34 +5175,34 @@
         <v>1.66</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="CL11" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CM11" t="n">
-        <v>3.06</v>
+        <v>3.15</v>
       </c>
       <c r="CN11" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="CO11" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="CP11" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CQ11" t="n">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="CR11" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CS11" t="n">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
       <c r="CT11" t="n">
-        <v>3.14</v>
+        <v>3.17</v>
       </c>
       <c r="CU11" t="n">
         <v>1.46</v>
@@ -5212,55 +5216,55 @@
         <v>2.32</v>
       </c>
       <c r="CZ11" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="DA11" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="DB11" t="n">
-        <v>3.17</v>
+        <v>3.13</v>
       </c>
       <c r="DC11" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="DD11" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="DE11" t="n">
-        <v>2.62</v>
+        <v>2.2</v>
       </c>
       <c r="DF11" t="n">
-        <v>95</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="DG11" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="DH11" t="n">
-        <v>3.12</v>
+        <v>2.8</v>
       </c>
       <c r="DI11" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="DJ11" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="DK11" t="n">
-        <v>45.12</v>
+        <v>44.3</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.75</v>
+        <v>0.7</v>
       </c>
       <c r="DM11" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="DN11" t="n">
-        <v>12.12</v>
+        <v>12.5</v>
       </c>
       <c r="DO11" t="n">
-        <v>13.5</v>
+        <v>12.8</v>
       </c>
       <c r="DP11" t="n">
-        <v>9.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="DQ11" t="n">
         <v>0</v>
@@ -5272,28 +5276,28 @@
         <v>0</v>
       </c>
       <c r="DT11" t="n">
-        <v>52.38</v>
+        <v>51.3</v>
       </c>
       <c r="DU11" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="DV11" t="n">
-        <v>14.75</v>
+        <v>15.4</v>
       </c>
       <c r="DW11" t="n">
-        <v>10.38</v>
+        <v>10.5</v>
       </c>
       <c r="DX11" t="n">
-        <v>4.38</v>
+        <v>4.9</v>
       </c>
       <c r="DY11" t="n">
-        <v>24.62</v>
+        <v>23.1</v>
       </c>
       <c r="DZ11" t="n">
-        <v>1.56</v>
+        <v>1.63</v>
       </c>
       <c r="EA11" t="n">
-        <v>2.88</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="12">
@@ -5303,13 +5307,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -5396,136 +5400,136 @@
         <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AI12" t="n">
-        <v>89.75</v>
+        <v>90.2</v>
       </c>
       <c r="AJ12" t="n">
         <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AL12" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="AM12" t="n">
         <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>49.75</v>
+        <v>47.4</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="AP12" t="n">
         <v>2</v>
       </c>
       <c r="AQ12" t="n">
-        <v>14.25</v>
+        <v>12.6</v>
       </c>
       <c r="AR12" t="n">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
       <c r="AS12" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT12" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AU12" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>45.2</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="BL12" t="n">
         <v>1</v>
       </c>
-      <c r="AV12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>44.5</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>17.25</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>20</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="BH12" t="n">
-        <v>11.33</v>
-      </c>
-      <c r="BI12" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="BJ12" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="BK12" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="BL12" t="n">
-        <v>0.89</v>
-      </c>
       <c r="BM12" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="BN12" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="BP12" t="n">
-        <v>5.22</v>
+        <v>5.2</v>
       </c>
       <c r="BQ12" t="n">
-        <v>6.11</v>
+        <v>6.1</v>
       </c>
       <c r="BR12" t="n">
         <v>100</v>
       </c>
       <c r="BS12" t="n">
-        <v>66.67</v>
+        <v>70</v>
       </c>
       <c r="BT12" t="n">
-        <v>44.44</v>
+        <v>50</v>
       </c>
       <c r="BU12" t="n">
-        <v>22.22</v>
+        <v>20</v>
       </c>
       <c r="BV12" t="n">
-        <v>22.22</v>
+        <v>20</v>
       </c>
       <c r="BW12" t="n">
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>55.56</v>
+        <v>50</v>
       </c>
       <c r="BY12" t="n">
         <v>2.12</v>
@@ -5537,13 +5541,13 @@
         <v>3.47</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.66</v>
+        <v>3.65</v>
       </c>
       <c r="CC12" t="n">
-        <v>4.59</v>
+        <v>4.34</v>
       </c>
       <c r="CD12" t="n">
-        <v>4.73</v>
+        <v>4.48</v>
       </c>
       <c r="CE12" t="n">
         <v>1.39</v>
@@ -5552,25 +5556,25 @@
         <v>2.81</v>
       </c>
       <c r="CG12" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="CH12" t="n">
         <v>1.39</v>
       </c>
       <c r="CI12" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CJ12" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="CL12" t="n">
         <v>1.68</v>
       </c>
       <c r="CM12" t="n">
-        <v>3</v>
+        <v>3.01</v>
       </c>
       <c r="CN12" t="n">
         <v>2.28</v>
@@ -5579,10 +5583,10 @@
         <v>1.28</v>
       </c>
       <c r="CP12" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CQ12" t="n">
-        <v>3.33</v>
+        <v>3.3</v>
       </c>
       <c r="CR12" t="n">
         <v>1.4</v>
@@ -5600,7 +5604,7 @@
         <v>1.46</v>
       </c>
       <c r="CW12" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CX12" t="n">
         <v>2.59</v>
@@ -5609,55 +5613,55 @@
         <v>2.28</v>
       </c>
       <c r="CZ12" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="DA12" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="DB12" t="n">
-        <v>3.41</v>
+        <v>3.38</v>
       </c>
       <c r="DC12" t="n">
         <v>0</v>
       </c>
       <c r="DD12" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="DE12" t="n">
-        <v>3.33</v>
+        <v>3.1</v>
       </c>
       <c r="DF12" t="n">
-        <v>93.67</v>
+        <v>93.5</v>
       </c>
       <c r="DG12" t="n">
         <v>0</v>
       </c>
       <c r="DH12" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="DI12" t="n">
-        <v>6.56</v>
+        <v>6.2</v>
       </c>
       <c r="DJ12" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="DK12" t="n">
-        <v>51.11</v>
+        <v>49.8</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="DM12" t="n">
-        <v>3.22</v>
+        <v>3.1</v>
       </c>
       <c r="DN12" t="n">
-        <v>12.67</v>
+        <v>12</v>
       </c>
       <c r="DO12" t="n">
-        <v>11.33</v>
+        <v>11.2</v>
       </c>
       <c r="DP12" t="n">
-        <v>8.220000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="DQ12" t="n">
         <v>0</v>
@@ -5669,28 +5673,28 @@
         <v>0</v>
       </c>
       <c r="DT12" t="n">
-        <v>48.22</v>
+        <v>48.2</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>15.56</v>
+        <v>15.2</v>
       </c>
       <c r="DW12" t="n">
-        <v>9.890000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="DX12" t="n">
-        <v>5.67</v>
+        <v>5.3</v>
       </c>
       <c r="DY12" t="n">
-        <v>18.89</v>
+        <v>19.1</v>
       </c>
       <c r="DZ12" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="EA12" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="13">
@@ -5700,94 +5704,94 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D13" t="n">
         <v>5</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="F13" t="n">
         <v>1</v>
       </c>
       <c r="G13" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="H13" t="n">
-        <v>109</v>
+        <v>107.6</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="K13" t="n">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
       <c r="L13" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="M13" t="n">
-        <v>56</v>
+        <v>53.4</v>
       </c>
       <c r="N13" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="O13" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="P13" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>56.4</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="AD13" t="n">
         <v>1.75</v>
       </c>
-      <c r="P13" t="n">
-        <v>15</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>15</v>
-      </c>
-      <c r="R13" t="n">
-        <v>7</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X13" t="n">
-        <v>54</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>14.25</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.64</v>
-      </c>
       <c r="AE13" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -5871,70 +5875,70 @@
         <v>2.4</v>
       </c>
       <c r="BG13" t="n">
-        <v>3.67</v>
+        <v>4</v>
       </c>
       <c r="BH13" t="n">
-        <v>11.22</v>
+        <v>11</v>
       </c>
       <c r="BI13" t="n">
-        <v>3.67</v>
+        <v>4</v>
       </c>
       <c r="BJ13" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="BO13" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="BP13" t="n">
-        <v>5.11</v>
+        <v>5.2</v>
       </c>
       <c r="BQ13" t="n">
-        <v>6.11</v>
+        <v>5.8</v>
       </c>
       <c r="BR13" t="n">
         <v>100</v>
       </c>
       <c r="BS13" t="n">
-        <v>77.78</v>
+        <v>80</v>
       </c>
       <c r="BT13" t="n">
-        <v>66.67</v>
+        <v>70</v>
       </c>
       <c r="BU13" t="n">
-        <v>66.67</v>
+        <v>70</v>
       </c>
       <c r="BV13" t="n">
-        <v>55.56</v>
+        <v>60</v>
       </c>
       <c r="BW13" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BX13" t="n">
-        <v>77.78</v>
+        <v>80</v>
       </c>
       <c r="BY13" t="n">
-        <v>2.1</v>
+        <v>1.99</v>
       </c>
       <c r="BZ13" t="n">
-        <v>2.15</v>
+        <v>2.03</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.56</v>
+        <v>3.64</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.87</v>
+        <v>3.93</v>
       </c>
       <c r="CC13" t="n">
         <v>3.02</v>
@@ -5946,19 +5950,19 @@
         <v>1.34</v>
       </c>
       <c r="CF13" t="n">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="CG13" t="n">
-        <v>3.03</v>
+        <v>3.04</v>
       </c>
       <c r="CH13" t="n">
         <v>1.45</v>
       </c>
       <c r="CI13" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CJ13" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="CK13" t="n">
         <v>1.32</v>
@@ -5967,28 +5971,28 @@
         <v>1.61</v>
       </c>
       <c r="CM13" t="n">
-        <v>3.04</v>
+        <v>3.03</v>
       </c>
       <c r="CN13" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="CO13" t="n">
         <v>1.22</v>
       </c>
       <c r="CP13" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CQ13" t="n">
-        <v>2.85</v>
+        <v>2.84</v>
       </c>
       <c r="CR13" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="CS13" t="n">
-        <v>2.66</v>
+        <v>2.65</v>
       </c>
       <c r="CT13" t="n">
-        <v>3.22</v>
+        <v>3.24</v>
       </c>
       <c r="CU13" t="n">
         <v>1.48</v>
@@ -6005,52 +6009,52 @@
         <v>1.24</v>
       </c>
       <c r="DA13" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="DB13" t="n">
         <v>2.91</v>
       </c>
       <c r="DC13" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="DD13" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="DE13" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="DF13" t="n">
-        <v>93</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="DG13" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DH13" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="DI13" t="n">
-        <v>4.78</v>
+        <v>4.7</v>
       </c>
       <c r="DJ13" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="DK13" t="n">
-        <v>45.78</v>
+        <v>45.5</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="DM13" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="DN13" t="n">
-        <v>13.11</v>
+        <v>13.1</v>
       </c>
       <c r="DO13" t="n">
-        <v>14.11</v>
+        <v>13.8</v>
       </c>
       <c r="DP13" t="n">
-        <v>8.56</v>
+        <v>7.9</v>
       </c>
       <c r="DQ13" t="n">
         <v>0</v>
@@ -6062,28 +6066,28 @@
         <v>0</v>
       </c>
       <c r="DT13" t="n">
-        <v>51.56</v>
+        <v>53</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>13</v>
+        <v>13.6</v>
       </c>
       <c r="DW13" t="n">
-        <v>8.67</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="DX13" t="n">
-        <v>4.33</v>
+        <v>4.9</v>
       </c>
       <c r="DY13" t="n">
-        <v>21</v>
+        <v>20.6</v>
       </c>
       <c r="DZ13" t="n">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="EA13" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="14">
@@ -6246,10 +6250,10 @@
         <v>0</v>
       </c>
       <c r="BA14" t="n">
-        <v>12</v>
+        <v>11.83</v>
       </c>
       <c r="BB14" t="n">
-        <v>6.67</v>
+        <v>6.5</v>
       </c>
       <c r="BC14" t="n">
         <v>5.33</v>
@@ -6258,7 +6262,7 @@
         <v>17.33</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="BF14" t="n">
         <v>2.5</v>
@@ -6461,10 +6465,10 @@
         <v>0.1</v>
       </c>
       <c r="DV14" t="n">
-        <v>12.4</v>
+        <v>12.3</v>
       </c>
       <c r="DW14" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="DX14" t="n">
         <v>5.3</v>
@@ -6473,7 +6477,7 @@
         <v>18.3</v>
       </c>
       <c r="DZ14" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="EA14" t="n">
         <v>1.8</v>
@@ -6486,13 +6490,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E15" t="n">
         <v>0.6</v>
@@ -6579,115 +6583,115 @@
         <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="AI15" t="n">
-        <v>72.75</v>
+        <v>74.2</v>
       </c>
       <c r="AJ15" t="n">
         <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AL15" t="n">
-        <v>5.25</v>
+        <v>4.8</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="AN15" t="n">
-        <v>36</v>
+        <v>36.4</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="AP15" t="n">
         <v>3</v>
       </c>
       <c r="AQ15" t="n">
-        <v>14.5</v>
+        <v>14.2</v>
       </c>
       <c r="AR15" t="n">
-        <v>15.25</v>
+        <v>14.6</v>
       </c>
       <c r="AS15" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="AU15" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AX15" t="n">
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>47.75</v>
+        <v>46.8</v>
       </c>
       <c r="AZ15" t="n">
         <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>14.25</v>
+        <v>13.6</v>
       </c>
       <c r="BB15" t="n">
-        <v>8.75</v>
+        <v>8</v>
       </c>
       <c r="BC15" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BD15" t="n">
-        <v>20.25</v>
+        <v>19.8</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="BG15" t="n">
-        <v>3.78</v>
+        <v>3.7</v>
       </c>
       <c r="BH15" t="n">
-        <v>10</v>
+        <v>10.2</v>
       </c>
       <c r="BI15" t="n">
-        <v>3.78</v>
+        <v>3.7</v>
       </c>
       <c r="BJ15" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.78</v>
+        <v>0.9</v>
       </c>
       <c r="BL15" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="BP15" t="n">
-        <v>5.89</v>
+        <v>6</v>
       </c>
       <c r="BQ15" t="n">
-        <v>4.11</v>
+        <v>4.2</v>
       </c>
       <c r="BR15" t="n">
         <v>100</v>
@@ -6696,19 +6700,19 @@
         <v>100</v>
       </c>
       <c r="BT15" t="n">
-        <v>77.78</v>
+        <v>80</v>
       </c>
       <c r="BU15" t="n">
-        <v>55.56</v>
+        <v>50</v>
       </c>
       <c r="BV15" t="n">
-        <v>44.44</v>
+        <v>40</v>
       </c>
       <c r="BW15" t="n">
         <v>0</v>
       </c>
       <c r="BX15" t="n">
-        <v>66.67</v>
+        <v>60</v>
       </c>
       <c r="BY15" t="n">
         <v>1.72</v>
@@ -6717,22 +6721,22 @@
         <v>1.74</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.91</v>
+        <v>3.86</v>
       </c>
       <c r="CB15" t="n">
-        <v>4.28</v>
+        <v>4.24</v>
       </c>
       <c r="CC15" t="n">
-        <v>2.43</v>
+        <v>2.37</v>
       </c>
       <c r="CD15" t="n">
-        <v>2.54</v>
+        <v>2.44</v>
       </c>
       <c r="CE15" t="n">
         <v>1.29</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="CG15" t="n">
         <v>3.34</v>
@@ -6741,31 +6745,31 @@
         <v>1.54</v>
       </c>
       <c r="CI15" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="CJ15" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CK15" t="n">
         <v>1.31</v>
       </c>
       <c r="CL15" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CM15" t="n">
-        <v>3.13</v>
+        <v>3.14</v>
       </c>
       <c r="CN15" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="CO15" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="CP15" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CQ15" t="n">
-        <v>2.53</v>
+        <v>2.51</v>
       </c>
       <c r="CR15" t="n">
         <v>1.34</v>
@@ -6783,13 +6787,13 @@
         <v>1.46</v>
       </c>
       <c r="CW15" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="CX15" t="n">
         <v>2.59</v>
       </c>
       <c r="CY15" t="n">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="CZ15" t="n">
         <v>1.21</v>
@@ -6798,82 +6802,82 @@
         <v>1.67</v>
       </c>
       <c r="DB15" t="n">
-        <v>2.65</v>
+        <v>2.64</v>
       </c>
       <c r="DC15" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="DD15" t="n">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="DE15" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="DF15" t="n">
-        <v>88.22</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="DG15" t="n">
         <v>0</v>
       </c>
       <c r="DH15" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="DI15" t="n">
-        <v>5.11</v>
+        <v>4.9</v>
       </c>
       <c r="DJ15" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="DK15" t="n">
-        <v>46.67</v>
+        <v>45.8</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="DM15" t="n">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="DN15" t="n">
-        <v>12.22</v>
+        <v>12.3</v>
       </c>
       <c r="DO15" t="n">
-        <v>14.67</v>
+        <v>14.4</v>
       </c>
       <c r="DP15" t="n">
-        <v>7.89</v>
+        <v>8</v>
       </c>
       <c r="DQ15" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="DR15" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="DS15" t="n">
         <v>0</v>
       </c>
       <c r="DT15" t="n">
-        <v>48</v>
+        <v>47.5</v>
       </c>
       <c r="DU15" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DV15" t="n">
-        <v>15.11</v>
+        <v>14.7</v>
       </c>
       <c r="DW15" t="n">
-        <v>9.56</v>
+        <v>9.1</v>
       </c>
       <c r="DX15" t="n">
-        <v>5.56</v>
+        <v>5.6</v>
       </c>
       <c r="DY15" t="n">
-        <v>19</v>
+        <v>18.9</v>
       </c>
       <c r="DZ15" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="EA15" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="16">
@@ -6883,61 +6887,61 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D16" t="n">
         <v>5</v>
       </c>
       <c r="E16" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="F16" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="G16" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="H16" t="n">
-        <v>94</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="K16" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="L16" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="M16" t="n">
-        <v>47.75</v>
+        <v>46.2</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="P16" t="n">
-        <v>11.75</v>
+        <v>10.6</v>
       </c>
       <c r="Q16" t="n">
-        <v>12.75</v>
+        <v>13.4</v>
       </c>
       <c r="R16" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="S16" t="n">
-        <v>1.75</v>
+        <v>2.4</v>
       </c>
       <c r="T16" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
@@ -6949,28 +6953,28 @@
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>51</v>
+        <v>52.8</v>
       </c>
       <c r="Y16" t="n">
         <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>11.25</v>
+        <v>13</v>
       </c>
       <c r="AA16" t="n">
-        <v>7.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AB16" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="AC16" t="n">
-        <v>19.25</v>
+        <v>19.4</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.32</v>
+        <v>1.45</v>
       </c>
       <c r="AE16" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AF16" t="n">
         <v>0.2</v>
@@ -7012,7 +7016,7 @@
         <v>12.8</v>
       </c>
       <c r="AS16" t="n">
-        <v>10.2</v>
+        <v>10.4</v>
       </c>
       <c r="AT16" t="n">
         <v>2</v>
@@ -7054,70 +7058,70 @@
         <v>1.2</v>
       </c>
       <c r="BG16" t="n">
-        <v>3.33</v>
+        <v>3.9</v>
       </c>
       <c r="BH16" t="n">
-        <v>10.67</v>
+        <v>10.6</v>
       </c>
       <c r="BI16" t="n">
-        <v>3.33</v>
+        <v>3.9</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.56</v>
+        <v>2</v>
       </c>
       <c r="BP16" t="n">
-        <v>4.56</v>
+        <v>4.5</v>
       </c>
       <c r="BQ16" t="n">
-        <v>6.11</v>
+        <v>6.1</v>
       </c>
       <c r="BR16" t="n">
         <v>100</v>
       </c>
       <c r="BS16" t="n">
-        <v>77.78</v>
+        <v>80</v>
       </c>
       <c r="BT16" t="n">
-        <v>66.67</v>
+        <v>70</v>
       </c>
       <c r="BU16" t="n">
-        <v>44.44</v>
+        <v>50</v>
       </c>
       <c r="BV16" t="n">
-        <v>33.33</v>
+        <v>40</v>
       </c>
       <c r="BW16" t="n">
-        <v>11.11</v>
+        <v>20</v>
       </c>
       <c r="BX16" t="n">
-        <v>66.67</v>
+        <v>70</v>
       </c>
       <c r="BY16" t="n">
-        <v>2.97</v>
+        <v>2.88</v>
       </c>
       <c r="BZ16" t="n">
-        <v>3.17</v>
+        <v>3.06</v>
       </c>
       <c r="CA16" t="n">
-        <v>3.6</v>
+        <v>3.58</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.81</v>
+        <v>3.78</v>
       </c>
       <c r="CC16" t="n">
         <v>4.76</v>
@@ -7129,52 +7133,52 @@
         <v>1.35</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="CG16" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="CH16" t="n">
         <v>1.44</v>
       </c>
       <c r="CI16" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="CJ16" t="n">
         <v>1.71</v>
       </c>
       <c r="CK16" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="CL16" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CM16" t="n">
-        <v>3.1</v>
+        <v>3.16</v>
       </c>
       <c r="CN16" t="n">
-        <v>2.31</v>
+        <v>2.35</v>
       </c>
       <c r="CO16" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="CP16" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CQ16" t="n">
-        <v>2.93</v>
+        <v>2.97</v>
       </c>
       <c r="CR16" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CS16" t="n">
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="CT16" t="n">
-        <v>3.03</v>
+        <v>3.05</v>
       </c>
       <c r="CU16" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CV16" t="inlineStr"/>
       <c r="CW16" t="n">
@@ -7191,82 +7195,82 @@
         <v>1.88</v>
       </c>
       <c r="DB16" t="n">
-        <v>3.15</v>
+        <v>3.14</v>
       </c>
       <c r="DC16" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DD16" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="DE16" t="n">
+        <v>3</v>
+      </c>
+      <c r="DF16" t="n">
+        <v>87.59999999999999</v>
+      </c>
+      <c r="DG16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="DH16" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="DI16" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="DJ16" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="DK16" t="n">
+        <v>39</v>
+      </c>
+      <c r="DL16" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="DM16" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="DN16" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="DO16" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="DP16" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="DQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT16" t="n">
+        <v>48.1</v>
+      </c>
+      <c r="DU16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="DV16" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="DW16" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="DX16" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="DY16" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="DZ16" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="EA16" t="n">
         <v>1</v>
-      </c>
-      <c r="DE16" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="DF16" t="n">
-        <v>87.22</v>
-      </c>
-      <c r="DG16" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="DH16" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="DI16" t="n">
-        <v>4.67</v>
-      </c>
-      <c r="DJ16" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="DK16" t="n">
-        <v>38.89</v>
-      </c>
-      <c r="DL16" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="DM16" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="DN16" t="n">
-        <v>13.44</v>
-      </c>
-      <c r="DO16" t="n">
-        <v>12.78</v>
-      </c>
-      <c r="DP16" t="n">
-        <v>8.779999999999999</v>
-      </c>
-      <c r="DQ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="DR16" t="n">
-        <v>0</v>
-      </c>
-      <c r="DS16" t="n">
-        <v>0</v>
-      </c>
-      <c r="DT16" t="n">
-        <v>46.78</v>
-      </c>
-      <c r="DU16" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="DV16" t="n">
-        <v>9.56</v>
-      </c>
-      <c r="DW16" t="n">
-        <v>6.44</v>
-      </c>
-      <c r="DX16" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="DY16" t="n">
-        <v>18.56</v>
-      </c>
-      <c r="DZ16" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="EA16" t="n">
-        <v>1.11</v>
       </c>
     </row>
     <row r="17">
@@ -7276,10 +7280,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D17" t="n">
         <v>5</v>
@@ -7288,82 +7292,82 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>0.33</v>
+        <v>0.2</v>
       </c>
       <c r="G17" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="H17" t="n">
-        <v>87.33</v>
+        <v>87</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="M17" t="n">
-        <v>46</v>
+        <v>42.4</v>
       </c>
       <c r="N17" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="O17" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="P17" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="R17" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AE17" t="n">
         <v>1</v>
-      </c>
-      <c r="O17" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="P17" t="n">
-        <v>10.33</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>8.33</v>
-      </c>
-      <c r="R17" t="n">
-        <v>8.67</v>
-      </c>
-      <c r="S17" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="V17" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0</v>
-      </c>
-      <c r="X17" t="n">
-        <v>50</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>13</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>7.33</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>5.67</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>21.33</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.33</v>
       </c>
       <c r="AF17" t="n">
         <v>0</v>
@@ -7429,55 +7433,55 @@
         <v>0</v>
       </c>
       <c r="BA17" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB17" t="n">
         <v>6</v>
       </c>
       <c r="BC17" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="BD17" t="n">
         <v>20.6</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="BF17" t="n">
         <v>1.8</v>
       </c>
       <c r="BG17" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="BH17" t="n">
-        <v>9.619999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="BI17" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.88</v>
+        <v>0.8</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="BL17" t="n">
         <v>1.5</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.38</v>
+        <v>0.5</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="BP17" t="n">
-        <v>5.12</v>
+        <v>4.8</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="BR17" t="n">
         <v>100</v>
@@ -7486,31 +7490,31 @@
         <v>100</v>
       </c>
       <c r="BT17" t="n">
-        <v>37.5</v>
+        <v>50</v>
       </c>
       <c r="BU17" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="BV17" t="n">
-        <v>12.5</v>
+        <v>20</v>
       </c>
       <c r="BW17" t="n">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="BX17" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="BY17" t="n">
-        <v>3.89</v>
+        <v>3.79</v>
       </c>
       <c r="BZ17" t="n">
-        <v>4.03</v>
+        <v>4.2</v>
       </c>
       <c r="CA17" t="n">
-        <v>4.5</v>
+        <v>4.29</v>
       </c>
       <c r="CB17" t="n">
-        <v>5.04</v>
+        <v>4.81</v>
       </c>
       <c r="CC17" t="n">
         <v>7.82</v>
@@ -7519,55 +7523,55 @@
         <v>8.69</v>
       </c>
       <c r="CE17" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="CF17" t="n">
-        <v>2.33</v>
+        <v>2.36</v>
       </c>
       <c r="CG17" t="n">
-        <v>3.39</v>
+        <v>3.33</v>
       </c>
       <c r="CH17" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="CI17" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="CJ17" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="CK17" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="CL17" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="CM17" t="n">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="CN17" t="n">
-        <v>2.37</v>
+        <v>2.34</v>
       </c>
       <c r="CO17" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="CP17" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="CQ17" t="n">
-        <v>2.55</v>
+        <v>2.64</v>
       </c>
       <c r="CR17" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CS17" t="n">
-        <v>2.78</v>
+        <v>2.73</v>
       </c>
       <c r="CT17" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="CU17" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="CV17" t="inlineStr"/>
       <c r="CW17" t="n">
@@ -7578,88 +7582,88 @@
         <v>2.32</v>
       </c>
       <c r="CZ17" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="DA17" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="DB17" t="n">
-        <v>2.52</v>
+        <v>2.61</v>
       </c>
       <c r="DC17" t="n">
         <v>0</v>
       </c>
       <c r="DD17" t="n">
-        <v>0.62</v>
+        <v>0.5</v>
       </c>
       <c r="DE17" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="DF17" t="n">
-        <v>82.5</v>
+        <v>83.3</v>
       </c>
       <c r="DG17" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="DH17" t="n">
-        <v>1.62</v>
+        <v>1.4</v>
       </c>
       <c r="DI17" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="DJ17" t="n">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="DK17" t="n">
-        <v>37.25</v>
+        <v>37.2</v>
       </c>
       <c r="DL17" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="DM17" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="DN17" t="n">
-        <v>12.37</v>
+        <v>12.4</v>
       </c>
       <c r="DO17" t="n">
-        <v>10</v>
+        <v>10.3</v>
       </c>
       <c r="DP17" t="n">
-        <v>11.75</v>
+        <v>11</v>
       </c>
       <c r="DQ17" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="DR17" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="DS17" t="n">
         <v>0</v>
       </c>
       <c r="DT17" t="n">
-        <v>45.25</v>
+        <v>45.9</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>10.75</v>
+        <v>10.8</v>
       </c>
       <c r="DW17" t="n">
-        <v>6.5</v>
+        <v>7.1</v>
       </c>
       <c r="DX17" t="n">
-        <v>4.25</v>
+        <v>3.7</v>
       </c>
       <c r="DY17" t="n">
-        <v>20.87</v>
+        <v>22</v>
       </c>
       <c r="DZ17" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="EA17" t="n">
-        <v>1.62</v>
+        <v>1.4</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Sweden_Allsvenskan_2026.xlsx
+++ b/data/teams/leagues/Averages_Sweden_Allsvenskan_2026.xlsx
@@ -1902,16 +1902,16 @@
         <v>11.43</v>
       </c>
       <c r="BB3" t="n">
-        <v>6.86</v>
+        <v>7</v>
       </c>
       <c r="BC3" t="n">
-        <v>4.57</v>
+        <v>4.43</v>
       </c>
       <c r="BD3" t="n">
         <v>20</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="BF3" t="n">
         <v>1.57</v>
@@ -2028,16 +2028,16 @@
         <v>2.87</v>
       </c>
       <c r="CR3" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CS3" t="n">
-        <v>2.83</v>
+        <v>2.75</v>
       </c>
       <c r="CT3" t="n">
-        <v>3.01</v>
+        <v>3.08</v>
       </c>
       <c r="CU3" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="CV3" t="inlineStr"/>
       <c r="CW3" t="n">
@@ -2117,16 +2117,16 @@
         <v>11.5</v>
       </c>
       <c r="DW3" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="DX3" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="DY3" t="n">
         <v>20</v>
       </c>
       <c r="DZ3" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="EA3" t="n">
         <v>1.7</v>
@@ -2421,10 +2421,10 @@
         <v>3.61</v>
       </c>
       <c r="CR4" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CS4" t="n">
-        <v>3.11</v>
+        <v>3.12</v>
       </c>
       <c r="CT4" t="n">
         <v>2.87</v>
@@ -4005,13 +4005,13 @@
         <v>3.21</v>
       </c>
       <c r="CR8" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CS8" t="n">
-        <v>2.83</v>
+        <v>2.86</v>
       </c>
       <c r="CT8" t="n">
-        <v>3.05</v>
+        <v>3.01</v>
       </c>
       <c r="CU8" t="n">
         <v>1.44</v>
@@ -4029,13 +4029,13 @@
         <v>2.07</v>
       </c>
       <c r="CZ8" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="DA8" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="DB8" t="n">
-        <v>3.33</v>
+        <v>3.38</v>
       </c>
       <c r="DC8" t="n">
         <v>0.2</v>
@@ -4429,10 +4429,10 @@
         <v>1.2</v>
       </c>
       <c r="DA9" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="DB9" t="n">
-        <v>2.63</v>
+        <v>2.61</v>
       </c>
       <c r="DC9" t="n">
         <v>0.09</v>
@@ -4823,13 +4823,13 @@
         <v>2.41</v>
       </c>
       <c r="CZ10" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="DB10" t="n">
-        <v>2.73</v>
+        <v>2.68</v>
       </c>
       <c r="DC10" t="n">
         <v>0.1</v>
@@ -5986,13 +5986,13 @@
         <v>2.84</v>
       </c>
       <c r="CR13" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CS13" t="n">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="CT13" t="n">
-        <v>3.24</v>
+        <v>3.22</v>
       </c>
       <c r="CU13" t="n">
         <v>1.48</v>
@@ -6009,10 +6009,10 @@
         <v>1.24</v>
       </c>
       <c r="DA13" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="DB13" t="n">
-        <v>2.91</v>
+        <v>2.92</v>
       </c>
       <c r="DC13" t="n">
         <v>0.1</v>
